--- a/l_r/1st.xlsx
+++ b/l_r/1st.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\l_r\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{140CD35B-97B4-49CA-B175-42589BEF58C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40365010-817B-4B98-9123-93E223287F9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1260" yWindow="0" windowWidth="13755" windowHeight="15585" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="3" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="17">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -97,6 +97,26 @@
   </si>
   <si>
     <t>D</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>B</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>C</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>pay for</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>except for</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -524,14 +544,14 @@
       </c>
       <c r="C9">
         <f>SUM(reading!C3:C42)</f>
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D9">
         <v>40</v>
       </c>
       <c r="E9" s="1">
         <f t="shared" ref="E9:E11" si="1">C9/D9</f>
-        <v>0.17499999999999999</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="10" spans="2:5">
@@ -1209,13 +1229,13 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86A9B22D-A93D-442A-B8E1-1D68266591E9}">
-  <dimension ref="A1:C102"/>
+  <dimension ref="A1:F102"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="1" spans="1:3">
       <c r="C1">
         <f>SUM(C3:C102)</f>
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -1353,116 +1373,182 @@
         <f t="shared" si="0"/>
         <v>111</v>
       </c>
+      <c r="B13" t="s">
+        <v>12</v>
+      </c>
+      <c r="C13">
+        <v>0</v>
+      </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14">
         <f t="shared" si="0"/>
         <v>112</v>
       </c>
+      <c r="B14" t="s">
+        <v>13</v>
+      </c>
+      <c r="C14">
+        <v>1</v>
+      </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15">
         <f t="shared" si="0"/>
         <v>113</v>
       </c>
+      <c r="B15" t="s">
+        <v>12</v>
+      </c>
+      <c r="C15">
+        <v>1</v>
+      </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16">
         <f t="shared" si="0"/>
         <v>114</v>
       </c>
-    </row>
-    <row r="17" spans="1:1">
+      <c r="B16" t="s">
+        <v>14</v>
+      </c>
+      <c r="C16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
       <c r="A17">
         <f t="shared" si="0"/>
         <v>115</v>
       </c>
-    </row>
-    <row r="18" spans="1:1">
+      <c r="B17" t="s">
+        <v>12</v>
+      </c>
+      <c r="C17">
+        <v>1</v>
+      </c>
+      <c r="F17" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6">
       <c r="A18">
         <f t="shared" si="0"/>
         <v>116</v>
       </c>
-    </row>
-    <row r="19" spans="1:1">
+      <c r="B18" t="s">
+        <v>13</v>
+      </c>
+      <c r="C18">
+        <v>1</v>
+      </c>
+      <c r="F18" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6">
       <c r="A19">
         <f t="shared" si="0"/>
         <v>117</v>
       </c>
-    </row>
-    <row r="20" spans="1:1">
+      <c r="B19" t="s">
+        <v>12</v>
+      </c>
+      <c r="C19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6">
       <c r="A20">
         <f t="shared" si="0"/>
         <v>118</v>
       </c>
-    </row>
-    <row r="21" spans="1:1">
+      <c r="B20" t="s">
+        <v>13</v>
+      </c>
+      <c r="C20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6">
       <c r="A21">
         <f t="shared" si="0"/>
         <v>119</v>
       </c>
-    </row>
-    <row r="22" spans="1:1">
+      <c r="B21" t="s">
+        <v>12</v>
+      </c>
+      <c r="C21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6">
       <c r="A22">
         <f t="shared" si="0"/>
         <v>120</v>
       </c>
-    </row>
-    <row r="23" spans="1:1">
+      <c r="B22" t="s">
+        <v>14</v>
+      </c>
+      <c r="C22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6">
       <c r="A23">
         <f t="shared" si="0"/>
         <v>121</v>
       </c>
     </row>
-    <row r="24" spans="1:1">
+    <row r="24" spans="1:6">
       <c r="A24">
         <f t="shared" si="0"/>
         <v>122</v>
       </c>
     </row>
-    <row r="25" spans="1:1">
+    <row r="25" spans="1:6">
       <c r="A25">
         <f t="shared" si="0"/>
         <v>123</v>
       </c>
     </row>
-    <row r="26" spans="1:1">
+    <row r="26" spans="1:6">
       <c r="A26">
         <f t="shared" si="0"/>
         <v>124</v>
       </c>
     </row>
-    <row r="27" spans="1:1">
+    <row r="27" spans="1:6">
       <c r="A27">
         <f t="shared" si="0"/>
         <v>125</v>
       </c>
     </row>
-    <row r="28" spans="1:1">
+    <row r="28" spans="1:6">
       <c r="A28">
         <f t="shared" si="0"/>
         <v>126</v>
       </c>
     </row>
-    <row r="29" spans="1:1">
+    <row r="29" spans="1:6">
       <c r="A29">
         <f t="shared" si="0"/>
         <v>127</v>
       </c>
     </row>
-    <row r="30" spans="1:1">
+    <row r="30" spans="1:6">
       <c r="A30">
         <f t="shared" si="0"/>
         <v>128</v>
       </c>
     </row>
-    <row r="31" spans="1:1">
+    <row r="31" spans="1:6">
       <c r="A31">
         <f t="shared" si="0"/>
         <v>129</v>
       </c>
     </row>
-    <row r="32" spans="1:1">
+    <row r="32" spans="1:6">
       <c r="A32">
         <f t="shared" si="0"/>
         <v>130</v>

--- a/l_r/1st.xlsx
+++ b/l_r/1st.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\l_r\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40365010-817B-4B98-9123-93E223287F9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{683801F4-D868-4BAE-95FD-BD05A8689F3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1260" yWindow="0" windowWidth="13755" windowHeight="15585" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1260" yWindow="435" windowWidth="21600" windowHeight="11295" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="3" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="21">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -117,6 +117,22 @@
   </si>
   <si>
     <t>except for</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>D</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>B</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>lucrative</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -544,14 +560,14 @@
       </c>
       <c r="C9">
         <f>SUM(reading!C3:C42)</f>
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="D9">
         <v>40</v>
       </c>
       <c r="E9" s="1">
         <f t="shared" ref="E9:E11" si="1">C9/D9</f>
-        <v>0.3</v>
+        <v>0.42499999999999999</v>
       </c>
     </row>
     <row r="10" spans="2:5">
@@ -1235,7 +1251,7 @@
     <row r="1" spans="1:3">
       <c r="C1">
         <f>SUM(C3:C102)</f>
-        <v>12</v>
+        <v>17</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -1499,59 +1515,128 @@
         <f t="shared" si="0"/>
         <v>121</v>
       </c>
+      <c r="B23" t="s">
+        <v>17</v>
+      </c>
+      <c r="C23">
+        <v>1</v>
+      </c>
     </row>
     <row r="24" spans="1:6">
       <c r="A24">
         <f t="shared" si="0"/>
         <v>122</v>
       </c>
+      <c r="B24" t="s">
+        <v>18</v>
+      </c>
+      <c r="C24">
+        <v>1</v>
+      </c>
     </row>
     <row r="25" spans="1:6">
       <c r="A25">
         <f t="shared" si="0"/>
         <v>123</v>
       </c>
+      <c r="B25" t="s">
+        <v>19</v>
+      </c>
+      <c r="C25">
+        <v>0</v>
+      </c>
     </row>
     <row r="26" spans="1:6">
       <c r="A26">
         <f t="shared" si="0"/>
         <v>124</v>
       </c>
+      <c r="B26" t="s">
+        <v>19</v>
+      </c>
+      <c r="C26">
+        <v>1</v>
+      </c>
+      <c r="F26" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="27" spans="1:6">
       <c r="A27">
         <f t="shared" si="0"/>
         <v>125</v>
       </c>
+      <c r="B27" t="s">
+        <v>19</v>
+      </c>
+      <c r="C27">
+        <v>0</v>
+      </c>
+      <c r="F27" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="28" spans="1:6">
       <c r="A28">
         <f t="shared" si="0"/>
         <v>126</v>
       </c>
+      <c r="B28" t="s">
+        <v>18</v>
+      </c>
+      <c r="C28">
+        <v>0</v>
+      </c>
+      <c r="F28" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="29" spans="1:6">
       <c r="A29">
         <f t="shared" si="0"/>
         <v>127</v>
       </c>
+      <c r="B29" t="s">
+        <v>18</v>
+      </c>
+      <c r="C29">
+        <v>1</v>
+      </c>
     </row>
     <row r="30" spans="1:6">
       <c r="A30">
         <f t="shared" si="0"/>
         <v>128</v>
       </c>
+      <c r="B30" t="s">
+        <v>19</v>
+      </c>
+      <c r="C30">
+        <v>0</v>
+      </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31">
         <f t="shared" si="0"/>
         <v>129</v>
       </c>
+      <c r="B31" t="s">
+        <v>17</v>
+      </c>
+      <c r="C31">
+        <v>1</v>
+      </c>
     </row>
     <row r="32" spans="1:6">
       <c r="A32">
         <f t="shared" si="0"/>
         <v>130</v>
+      </c>
+      <c r="B32" t="s">
+        <v>17</v>
+      </c>
+      <c r="C32">
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:1">

--- a/l_r/1st.xlsx
+++ b/l_r/1st.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\l_r\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{683801F4-D868-4BAE-95FD-BD05A8689F3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2C91971-18E9-4B24-9E6E-2C81C369A9A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1260" yWindow="435" windowWidth="21600" windowHeight="11295" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9945" yWindow="795" windowWidth="21600" windowHeight="11295" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="3" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="21">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -2073,10 +2073,10 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C7A3EDD-6597-4754-A609-A225833ECC81}">
-  <dimension ref="A2:C2"/>
+  <dimension ref="A2:D12"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:4">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -2085,12 +2085,161 @@
       </c>
       <c r="C2" t="s">
         <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3">
+        <v>101</v>
+      </c>
+      <c r="B3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4">
+        <f>A3+1</f>
+        <v>102</v>
+      </c>
+      <c r="B4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="D4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5">
+        <f t="shared" ref="A5:A12" si="0">A4+1</f>
+        <v>103</v>
+      </c>
+      <c r="B5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5">
+        <v>0</v>
+      </c>
+      <c r="D5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6">
+        <f t="shared" si="0"/>
+        <v>104</v>
+      </c>
+      <c r="B6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7">
+        <f t="shared" si="0"/>
+        <v>105</v>
+      </c>
+      <c r="B7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7">
+        <v>1</v>
+      </c>
+      <c r="D7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8">
+        <f t="shared" si="0"/>
+        <v>106</v>
+      </c>
+      <c r="B8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8">
+        <v>1</v>
+      </c>
+      <c r="D8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9">
+        <f t="shared" si="0"/>
+        <v>107</v>
+      </c>
+      <c r="B9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9">
+        <v>0</v>
+      </c>
+      <c r="D9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10">
+        <f t="shared" si="0"/>
+        <v>108</v>
+      </c>
+      <c r="B10" t="s">
+        <v>8</v>
+      </c>
+      <c r="C10">
+        <v>1</v>
+      </c>
+      <c r="D10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11">
+        <f t="shared" si="0"/>
+        <v>109</v>
+      </c>
+      <c r="B11" t="s">
+        <v>8</v>
+      </c>
+      <c r="C11">
+        <v>0</v>
+      </c>
+      <c r="D11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12">
+        <f t="shared" si="0"/>
+        <v>110</v>
+      </c>
+      <c r="B12" t="s">
+        <v>11</v>
+      </c>
+      <c r="C12">
+        <v>1</v>
+      </c>
+      <c r="D12">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B56:B59 B3:B17 B20:B32 B41:B50" xr:uid="{D8C212E3-0513-4E96-9660-7E8BB94F20D2}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B56:B59 B41:B50 B20:B32 B3:B17" xr:uid="{D8C212E3-0513-4E96-9660-7E8BB94F20D2}">
       <formula1>"A,B,C,D"</formula1>
     </dataValidation>
   </dataValidations>

--- a/l_r/1st.xlsx
+++ b/l_r/1st.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\l_r\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2C91971-18E9-4B24-9E6E-2C81C369A9A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBE03E80-9A28-4F99-8D41-52EC31FFE558}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9945" yWindow="795" windowWidth="21600" windowHeight="11295" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="3" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="21">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -2073,7 +2073,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C7A3EDD-6597-4754-A609-A225833ECC81}">
-  <dimension ref="A2:D12"/>
+  <dimension ref="A2:D22"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="2" spans="1:4">
@@ -2234,6 +2234,116 @@
       </c>
       <c r="D12">
         <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13">
+        <v>111</v>
+      </c>
+      <c r="B13" t="s">
+        <v>8</v>
+      </c>
+      <c r="C13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14">
+        <v>112</v>
+      </c>
+      <c r="B14" t="s">
+        <v>10</v>
+      </c>
+      <c r="C14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15">
+        <v>113</v>
+      </c>
+      <c r="B15" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16">
+        <v>114</v>
+      </c>
+      <c r="B16" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17">
+        <v>115</v>
+      </c>
+      <c r="B17" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18">
+        <v>116</v>
+      </c>
+      <c r="B18" t="s">
+        <v>10</v>
+      </c>
+      <c r="C18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19">
+        <v>117</v>
+      </c>
+      <c r="B19" t="s">
+        <v>11</v>
+      </c>
+      <c r="C19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20">
+        <v>118</v>
+      </c>
+      <c r="B20" t="s">
+        <v>10</v>
+      </c>
+      <c r="C20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21">
+        <v>119</v>
+      </c>
+      <c r="B21" t="s">
+        <v>9</v>
+      </c>
+      <c r="C21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22">
+        <v>120</v>
+      </c>
+      <c r="B22" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/l_r/1st.xlsx
+++ b/l_r/1st.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\l_r\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBE03E80-9A28-4F99-8D41-52EC31FFE558}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6259091-60C8-42F5-85F7-583E88B67A2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="21">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -2073,7 +2073,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C7A3EDD-6597-4754-A609-A225833ECC81}">
-  <dimension ref="A2:D22"/>
+  <dimension ref="A2:D32"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="2" spans="1:4">
@@ -2344,6 +2344,116 @@
       </c>
       <c r="C22">
         <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23">
+        <v>111</v>
+      </c>
+      <c r="B23" t="s">
+        <v>8</v>
+      </c>
+      <c r="C23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24">
+        <v>112</v>
+      </c>
+      <c r="B24" t="s">
+        <v>10</v>
+      </c>
+      <c r="C24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25">
+        <v>113</v>
+      </c>
+      <c r="B25" t="s">
+        <v>9</v>
+      </c>
+      <c r="C25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26">
+        <v>114</v>
+      </c>
+      <c r="B26" t="s">
+        <v>8</v>
+      </c>
+      <c r="C26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27">
+        <v>115</v>
+      </c>
+      <c r="B27" t="s">
+        <v>9</v>
+      </c>
+      <c r="C27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28">
+        <v>116</v>
+      </c>
+      <c r="B28" t="s">
+        <v>10</v>
+      </c>
+      <c r="C28">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3">
+      <c r="A29">
+        <v>117</v>
+      </c>
+      <c r="B29" t="s">
+        <v>11</v>
+      </c>
+      <c r="C29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3">
+      <c r="A30">
+        <v>118</v>
+      </c>
+      <c r="B30" t="s">
+        <v>8</v>
+      </c>
+      <c r="C30">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3">
+      <c r="A31">
+        <v>119</v>
+      </c>
+      <c r="B31" t="s">
+        <v>8</v>
+      </c>
+      <c r="C31">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3">
+      <c r="A32">
+        <v>120</v>
+      </c>
+      <c r="B32" t="s">
+        <v>10</v>
+      </c>
+      <c r="C32">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/l_r/1st.xlsx
+++ b/l_r/1st.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\l_r\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6259091-60C8-42F5-85F7-583E88B67A2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48AA1B3F-93BD-4C15-A83D-88C3A0EC0B03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="270" yWindow="0" windowWidth="14430" windowHeight="15585" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="3" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="25">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -133,6 +133,22 @@
   </si>
   <si>
     <t>lucrative</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>B</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>C</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>D</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -560,14 +576,14 @@
       </c>
       <c r="C9">
         <f>SUM(reading!C3:C42)</f>
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="D9">
         <v>40</v>
       </c>
       <c r="E9" s="1">
         <f t="shared" ref="E9:E11" si="1">C9/D9</f>
-        <v>0.42499999999999999</v>
+        <v>0.625</v>
       </c>
     </row>
     <row r="10" spans="2:5">
@@ -1251,7 +1267,7 @@
     <row r="1" spans="1:3">
       <c r="C1">
         <f>SUM(C3:C102)</f>
-        <v>17</v>
+        <v>25</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -1639,97 +1655,145 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:1">
+    <row r="33" spans="1:3">
       <c r="A33">
         <f t="shared" si="0"/>
         <v>131</v>
       </c>
-    </row>
-    <row r="34" spans="1:1">
+      <c r="B33" t="s">
+        <v>21</v>
+      </c>
+      <c r="C33">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3">
       <c r="A34">
         <f t="shared" si="0"/>
         <v>132</v>
       </c>
-    </row>
-    <row r="35" spans="1:1">
+      <c r="B34" t="s">
+        <v>22</v>
+      </c>
+      <c r="C34">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3">
       <c r="A35">
         <f t="shared" si="0"/>
         <v>133</v>
       </c>
-    </row>
-    <row r="36" spans="1:1">
+      <c r="B35" t="s">
+        <v>22</v>
+      </c>
+      <c r="C35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3">
       <c r="A36">
         <f t="shared" si="0"/>
         <v>134</v>
       </c>
-    </row>
-    <row r="37" spans="1:1">
+      <c r="B36" t="s">
+        <v>23</v>
+      </c>
+      <c r="C36">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3">
       <c r="A37">
         <f t="shared" si="0"/>
         <v>135</v>
       </c>
-    </row>
-    <row r="38" spans="1:1">
+      <c r="B37" t="s">
+        <v>21</v>
+      </c>
+      <c r="C37">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3">
       <c r="A38">
         <f t="shared" si="0"/>
         <v>136</v>
       </c>
-    </row>
-    <row r="39" spans="1:1">
+      <c r="B38" t="s">
+        <v>24</v>
+      </c>
+      <c r="C38">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3">
       <c r="A39">
         <f t="shared" si="0"/>
         <v>137</v>
       </c>
-    </row>
-    <row r="40" spans="1:1">
+      <c r="B39" t="s">
+        <v>24</v>
+      </c>
+      <c r="C39">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3">
       <c r="A40">
         <f t="shared" si="0"/>
         <v>138</v>
       </c>
-    </row>
-    <row r="41" spans="1:1">
+      <c r="B40" t="s">
+        <v>24</v>
+      </c>
+      <c r="C40">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3">
       <c r="A41">
         <f t="shared" si="0"/>
         <v>139</v>
       </c>
     </row>
-    <row r="42" spans="1:1">
+    <row r="42" spans="1:3">
       <c r="A42">
         <f t="shared" si="0"/>
         <v>140</v>
       </c>
     </row>
-    <row r="43" spans="1:1">
+    <row r="43" spans="1:3">
       <c r="A43">
         <f t="shared" si="0"/>
         <v>141</v>
       </c>
     </row>
-    <row r="44" spans="1:1">
+    <row r="44" spans="1:3">
       <c r="A44">
         <f t="shared" si="0"/>
         <v>142</v>
       </c>
     </row>
-    <row r="45" spans="1:1">
+    <row r="45" spans="1:3">
       <c r="A45">
         <f t="shared" si="0"/>
         <v>143</v>
       </c>
     </row>
-    <row r="46" spans="1:1">
+    <row r="46" spans="1:3">
       <c r="A46">
         <f t="shared" si="0"/>
         <v>144</v>
       </c>
     </row>
-    <row r="47" spans="1:1">
+    <row r="47" spans="1:3">
       <c r="A47">
         <f t="shared" si="0"/>
         <v>145</v>
       </c>
     </row>
-    <row r="48" spans="1:1">
+    <row r="48" spans="1:3">
       <c r="A48">
         <f t="shared" si="0"/>
         <v>146</v>

--- a/l_r/1st.xlsx
+++ b/l_r/1st.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\l_r\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48AA1B3F-93BD-4C15-A83D-88C3A0EC0B03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4044701-ED40-4A9E-AF29-B0B3F137E67E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="270" yWindow="0" windowWidth="14430" windowHeight="15585" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3915" yWindow="2790" windowWidth="15105" windowHeight="11295" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="3" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="27">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -145,6 +145,14 @@
   </si>
   <si>
     <t>C</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>D</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>A</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -576,14 +584,14 @@
       </c>
       <c r="C9">
         <f>SUM(reading!C3:C42)</f>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D9">
         <v>40</v>
       </c>
       <c r="E9" s="1">
         <f t="shared" ref="E9:E11" si="1">C9/D9</f>
-        <v>0.625</v>
+        <v>0.65</v>
       </c>
     </row>
     <row r="10" spans="2:5">
@@ -592,14 +600,14 @@
       </c>
       <c r="C10">
         <f>SUM(reading!C43:C54)</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D10">
         <v>12</v>
       </c>
       <c r="E10" s="1">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="11" spans="2:5">
@@ -1267,7 +1275,7 @@
     <row r="1" spans="1:3">
       <c r="C1">
         <f>SUM(C3:C102)</f>
-        <v>25</v>
+        <v>32</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -1756,47 +1764,95 @@
         <f t="shared" si="0"/>
         <v>139</v>
       </c>
+      <c r="B41" t="s">
+        <v>10</v>
+      </c>
+      <c r="C41">
+        <v>0</v>
+      </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42">
         <f t="shared" si="0"/>
         <v>140</v>
       </c>
+      <c r="B42" t="s">
+        <v>11</v>
+      </c>
+      <c r="C42">
+        <v>1</v>
+      </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43">
         <f t="shared" si="0"/>
         <v>141</v>
       </c>
+      <c r="B43" t="s">
+        <v>9</v>
+      </c>
+      <c r="C43">
+        <v>1</v>
+      </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44">
         <f t="shared" si="0"/>
         <v>142</v>
       </c>
+      <c r="B44" t="s">
+        <v>8</v>
+      </c>
+      <c r="C44">
+        <v>1</v>
+      </c>
     </row>
     <row r="45" spans="1:3">
       <c r="A45">
         <f t="shared" si="0"/>
         <v>143</v>
       </c>
+      <c r="B45" t="s">
+        <v>10</v>
+      </c>
+      <c r="C45">
+        <v>1</v>
+      </c>
     </row>
     <row r="46" spans="1:3">
       <c r="A46">
         <f t="shared" si="0"/>
         <v>144</v>
       </c>
+      <c r="B46" t="s">
+        <v>10</v>
+      </c>
+      <c r="C46">
+        <v>1</v>
+      </c>
     </row>
     <row r="47" spans="1:3">
       <c r="A47">
         <f t="shared" si="0"/>
         <v>145</v>
       </c>
+      <c r="B47" t="s">
+        <v>25</v>
+      </c>
+      <c r="C47">
+        <v>1</v>
+      </c>
     </row>
     <row r="48" spans="1:3">
       <c r="A48">
         <f t="shared" si="0"/>
         <v>146</v>
+      </c>
+      <c r="B48" t="s">
+        <v>26</v>
+      </c>
+      <c r="C48">
+        <v>1</v>
       </c>
     </row>
     <row r="49" spans="1:1">

--- a/l_r/1st.xlsx
+++ b/l_r/1st.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\l_r\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4044701-ED40-4A9E-AF29-B0B3F137E67E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D417C496-A69E-46AB-857D-0CCA61155FFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3915" yWindow="2790" windowWidth="15105" windowHeight="11295" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="240" windowWidth="15105" windowHeight="15225" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="3" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="27">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -2193,7 +2193,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C7A3EDD-6597-4754-A609-A225833ECC81}">
-  <dimension ref="A2:D32"/>
+  <dimension ref="A2:D40"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="2" spans="1:4">
@@ -2573,6 +2573,101 @@
         <v>10</v>
       </c>
       <c r="C32">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3">
+      <c r="A33">
+        <v>131</v>
+      </c>
+      <c r="B33" t="s">
+        <v>9</v>
+      </c>
+      <c r="C33">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3">
+      <c r="A34">
+        <f>A33+1</f>
+        <v>132</v>
+      </c>
+      <c r="B34" t="s">
+        <v>8</v>
+      </c>
+      <c r="C34">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3">
+      <c r="A35">
+        <f t="shared" ref="A35:A39" si="1">A34+1</f>
+        <v>133</v>
+      </c>
+      <c r="B35" t="s">
+        <v>8</v>
+      </c>
+      <c r="C35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3">
+      <c r="A36">
+        <f t="shared" si="1"/>
+        <v>134</v>
+      </c>
+      <c r="B36" t="s">
+        <v>10</v>
+      </c>
+      <c r="C36">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3">
+      <c r="A37">
+        <f t="shared" si="1"/>
+        <v>135</v>
+      </c>
+      <c r="B37" t="s">
+        <v>9</v>
+      </c>
+      <c r="C37">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3">
+      <c r="A38">
+        <f t="shared" si="1"/>
+        <v>136</v>
+      </c>
+      <c r="B38" t="s">
+        <v>10</v>
+      </c>
+      <c r="C38">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3">
+      <c r="A39">
+        <f t="shared" si="1"/>
+        <v>137</v>
+      </c>
+      <c r="B39" t="s">
+        <v>11</v>
+      </c>
+      <c r="C39">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3">
+      <c r="A40">
+        <f>A39+1</f>
+        <v>138</v>
+      </c>
+      <c r="B40" t="s">
+        <v>11</v>
+      </c>
+      <c r="C40">
         <v>1</v>
       </c>
     </row>

--- a/l_r/1st.xlsx
+++ b/l_r/1st.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\l_r\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D417C496-A69E-46AB-857D-0CCA61155FFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{997A867C-1588-434A-93E4-55AD55B4C3D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="240" windowWidth="15105" windowHeight="15225" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="28">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -158,6 +158,9 @@
   <si>
     <t>D</t>
     <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>C</t>
   </si>
 </sst>
 </file>
@@ -2193,7 +2196,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C7A3EDD-6597-4754-A609-A225833ECC81}">
-  <dimension ref="A2:D40"/>
+  <dimension ref="A2:D48"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="2" spans="1:4">
@@ -2668,6 +2671,102 @@
         <v>11</v>
       </c>
       <c r="C40">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3">
+      <c r="A41">
+        <f t="shared" ref="A41:A48" si="2">A40+1</f>
+        <v>139</v>
+      </c>
+      <c r="B41" t="s">
+        <v>27</v>
+      </c>
+      <c r="C41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3">
+      <c r="A42">
+        <f t="shared" si="2"/>
+        <v>140</v>
+      </c>
+      <c r="B42" t="s">
+        <v>11</v>
+      </c>
+      <c r="C42">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3">
+      <c r="A43">
+        <f t="shared" si="2"/>
+        <v>141</v>
+      </c>
+      <c r="B43" t="s">
+        <v>9</v>
+      </c>
+      <c r="C43">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3">
+      <c r="A44">
+        <f t="shared" si="2"/>
+        <v>142</v>
+      </c>
+      <c r="B44" t="s">
+        <v>8</v>
+      </c>
+      <c r="C44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3">
+      <c r="A45">
+        <f t="shared" si="2"/>
+        <v>143</v>
+      </c>
+      <c r="B45" t="s">
+        <v>10</v>
+      </c>
+      <c r="C45">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3">
+      <c r="A46">
+        <f t="shared" si="2"/>
+        <v>144</v>
+      </c>
+      <c r="B46" t="s">
+        <v>10</v>
+      </c>
+      <c r="C46">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3">
+      <c r="A47">
+        <f t="shared" si="2"/>
+        <v>145</v>
+      </c>
+      <c r="B47" t="s">
+        <v>10</v>
+      </c>
+      <c r="C47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3">
+      <c r="A48">
+        <f t="shared" si="2"/>
+        <v>146</v>
+      </c>
+      <c r="B48" t="s">
+        <v>11</v>
+      </c>
+      <c r="C48">
         <v>1</v>
       </c>
     </row>

--- a/l_r/1st.xlsx
+++ b/l_r/1st.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\l_r\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{997A867C-1588-434A-93E4-55AD55B4C3D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0117967A-1D41-4220-92B4-05151A87DCE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="240" windowWidth="15105" windowHeight="15225" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-75" yWindow="45" windowWidth="9225" windowHeight="15225" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="3" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="32">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -161,6 +161,21 @@
   </si>
   <si>
     <t>C</t>
+  </si>
+  <si>
+    <t>B</t>
+  </si>
+  <si>
+    <t>B</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>C</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>A</t>
+    <phoneticPr fontId="1"/>
   </si>
 </sst>
 </file>
@@ -603,14 +618,14 @@
       </c>
       <c r="C10">
         <f>SUM(reading!C43:C54)</f>
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D10">
         <v>12</v>
       </c>
       <c r="E10" s="1">
         <f t="shared" si="1"/>
-        <v>0.5</v>
+        <v>0.83333333333333337</v>
       </c>
     </row>
     <row r="11" spans="2:5">
@@ -1278,7 +1293,7 @@
     <row r="1" spans="1:3">
       <c r="C1">
         <f>SUM(C3:C102)</f>
-        <v>32</v>
+        <v>36</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -1858,97 +1873,133 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:1">
+    <row r="49" spans="1:3">
       <c r="A49">
         <f t="shared" si="0"/>
         <v>147</v>
       </c>
-    </row>
-    <row r="50" spans="1:1">
+      <c r="B49" t="s">
+        <v>29</v>
+      </c>
+      <c r="C49">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3">
       <c r="A50">
         <f t="shared" si="0"/>
         <v>148</v>
       </c>
-    </row>
-    <row r="51" spans="1:1">
+      <c r="B50" t="s">
+        <v>30</v>
+      </c>
+      <c r="C50">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3">
       <c r="A51">
         <f t="shared" si="0"/>
         <v>149</v>
       </c>
-    </row>
-    <row r="52" spans="1:1">
+      <c r="B51" t="s">
+        <v>30</v>
+      </c>
+      <c r="C51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3">
       <c r="A52">
         <f t="shared" si="0"/>
         <v>150</v>
       </c>
-    </row>
-    <row r="53" spans="1:1">
+      <c r="B52" t="s">
+        <v>31</v>
+      </c>
+      <c r="C52">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3">
       <c r="A53">
         <f t="shared" si="0"/>
         <v>151</v>
       </c>
-    </row>
-    <row r="54" spans="1:1">
+      <c r="B53" t="s">
+        <v>28</v>
+      </c>
+      <c r="C53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3">
       <c r="A54">
         <f t="shared" si="0"/>
         <v>152</v>
       </c>
-    </row>
-    <row r="55" spans="1:1">
+      <c r="B54" t="s">
+        <v>31</v>
+      </c>
+      <c r="C54">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3">
       <c r="A55">
         <f t="shared" si="0"/>
         <v>153</v>
       </c>
     </row>
-    <row r="56" spans="1:1">
+    <row r="56" spans="1:3">
       <c r="A56">
         <f t="shared" si="0"/>
         <v>154</v>
       </c>
     </row>
-    <row r="57" spans="1:1">
+    <row r="57" spans="1:3">
       <c r="A57">
         <f t="shared" si="0"/>
         <v>155</v>
       </c>
     </row>
-    <row r="58" spans="1:1">
+    <row r="58" spans="1:3">
       <c r="A58">
         <f t="shared" si="0"/>
         <v>156</v>
       </c>
     </row>
-    <row r="59" spans="1:1">
+    <row r="59" spans="1:3">
       <c r="A59">
         <f t="shared" si="0"/>
         <v>157</v>
       </c>
     </row>
-    <row r="60" spans="1:1">
+    <row r="60" spans="1:3">
       <c r="A60">
         <f t="shared" si="0"/>
         <v>158</v>
       </c>
     </row>
-    <row r="61" spans="1:1">
+    <row r="61" spans="1:3">
       <c r="A61">
         <f t="shared" si="0"/>
         <v>159</v>
       </c>
     </row>
-    <row r="62" spans="1:1">
+    <row r="62" spans="1:3">
       <c r="A62">
         <f t="shared" si="0"/>
         <v>160</v>
       </c>
     </row>
-    <row r="63" spans="1:1">
+    <row r="63" spans="1:3">
       <c r="A63">
         <f t="shared" si="0"/>
         <v>161</v>
       </c>
     </row>
-    <row r="64" spans="1:1">
+    <row r="64" spans="1:3">
       <c r="A64">
         <f t="shared" si="0"/>
         <v>162</v>

--- a/l_r/1st.xlsx
+++ b/l_r/1st.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\l_r\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0117967A-1D41-4220-92B4-05151A87DCE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A2ADA4A-C685-4757-935C-6076961DA7CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-75" yWindow="45" windowWidth="9225" windowHeight="15225" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-90" yWindow="330" windowWidth="11865" windowHeight="15225" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="3" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="35">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -175,6 +175,18 @@
   </si>
   <si>
     <t>A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>D</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>C</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -634,14 +646,14 @@
       </c>
       <c r="C11">
         <f>SUM(reading!C55:C102)</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D11">
         <v>48</v>
       </c>
       <c r="E11" s="1">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>8.3333333333333329E-2</v>
       </c>
     </row>
   </sheetData>
@@ -1293,7 +1305,7 @@
     <row r="1" spans="1:3">
       <c r="C1">
         <f>SUM(C3:C102)</f>
-        <v>36</v>
+        <v>40</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -1950,29 +1962,59 @@
         <f t="shared" si="0"/>
         <v>153</v>
       </c>
+      <c r="B55" t="s">
+        <v>27</v>
+      </c>
+      <c r="C55">
+        <v>1</v>
+      </c>
     </row>
     <row r="56" spans="1:3">
       <c r="A56">
         <f t="shared" si="0"/>
         <v>154</v>
       </c>
+      <c r="B56" t="s">
+        <v>32</v>
+      </c>
+      <c r="C56">
+        <v>1</v>
+      </c>
     </row>
     <row r="57" spans="1:3">
       <c r="A57">
         <f t="shared" si="0"/>
         <v>155</v>
       </c>
+      <c r="B57" t="s">
+        <v>32</v>
+      </c>
+      <c r="C57">
+        <v>0</v>
+      </c>
     </row>
     <row r="58" spans="1:3">
       <c r="A58">
         <f t="shared" si="0"/>
         <v>156</v>
       </c>
+      <c r="B58" t="s">
+        <v>33</v>
+      </c>
+      <c r="C58">
+        <v>1</v>
+      </c>
     </row>
     <row r="59" spans="1:3">
       <c r="A59">
         <f t="shared" si="0"/>
         <v>157</v>
+      </c>
+      <c r="B59" t="s">
+        <v>34</v>
+      </c>
+      <c r="C59">
+        <v>1</v>
       </c>
     </row>
     <row r="60" spans="1:3">

--- a/l_r/1st.xlsx
+++ b/l_r/1st.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\l_r\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A2ADA4A-C685-4757-935C-6076961DA7CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{896D2C87-6D58-4CFC-BA91-B646F705B876}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-90" yWindow="330" windowWidth="11865" windowHeight="15225" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="3" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="39">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -187,6 +187,22 @@
   </si>
   <si>
     <t>C</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>D</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>B</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>C</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>A</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -646,14 +662,14 @@
       </c>
       <c r="C11">
         <f>SUM(reading!C55:C102)</f>
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D11">
         <v>48</v>
       </c>
       <c r="E11" s="1">
         <f t="shared" si="1"/>
-        <v>8.3333333333333329E-2</v>
+        <v>0.14583333333333334</v>
       </c>
     </row>
   </sheetData>
@@ -1305,7 +1321,7 @@
     <row r="1" spans="1:3">
       <c r="C1">
         <f>SUM(C3:C102)</f>
-        <v>40</v>
+        <v>43</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -2022,122 +2038,158 @@
         <f t="shared" si="0"/>
         <v>158</v>
       </c>
+      <c r="B60" t="s">
+        <v>35</v>
+      </c>
+      <c r="C60">
+        <v>1</v>
+      </c>
     </row>
     <row r="61" spans="1:3">
       <c r="A61">
         <f t="shared" si="0"/>
         <v>159</v>
       </c>
+      <c r="B61" t="s">
+        <v>36</v>
+      </c>
+      <c r="C61">
+        <v>0</v>
+      </c>
     </row>
     <row r="62" spans="1:3">
       <c r="A62">
         <f t="shared" si="0"/>
         <v>160</v>
       </c>
+      <c r="B62" t="s">
+        <v>36</v>
+      </c>
+      <c r="C62">
+        <v>0</v>
+      </c>
     </row>
     <row r="63" spans="1:3">
       <c r="A63">
         <f t="shared" si="0"/>
         <v>161</v>
       </c>
+      <c r="B63" t="s">
+        <v>37</v>
+      </c>
+      <c r="C63">
+        <v>0</v>
+      </c>
     </row>
     <row r="64" spans="1:3">
       <c r="A64">
         <f t="shared" si="0"/>
         <v>162</v>
       </c>
-    </row>
-    <row r="65" spans="1:1">
+      <c r="B64" t="s">
+        <v>36</v>
+      </c>
+      <c r="C64">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3">
       <c r="A65">
         <f t="shared" si="0"/>
         <v>163</v>
       </c>
-    </row>
-    <row r="66" spans="1:1">
+      <c r="B65" t="s">
+        <v>38</v>
+      </c>
+      <c r="C65">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3">
       <c r="A66">
         <f t="shared" si="0"/>
         <v>164</v>
       </c>
     </row>
-    <row r="67" spans="1:1">
+    <row r="67" spans="1:3">
       <c r="A67">
         <f t="shared" si="0"/>
         <v>165</v>
       </c>
     </row>
-    <row r="68" spans="1:1">
+    <row r="68" spans="1:3">
       <c r="A68">
         <f t="shared" si="0"/>
         <v>166</v>
       </c>
     </row>
-    <row r="69" spans="1:1">
+    <row r="69" spans="1:3">
       <c r="A69">
         <f t="shared" ref="A69:A102" si="1">A68+1</f>
         <v>167</v>
       </c>
     </row>
-    <row r="70" spans="1:1">
+    <row r="70" spans="1:3">
       <c r="A70">
         <f t="shared" si="1"/>
         <v>168</v>
       </c>
     </row>
-    <row r="71" spans="1:1">
+    <row r="71" spans="1:3">
       <c r="A71">
         <f t="shared" si="1"/>
         <v>169</v>
       </c>
     </row>
-    <row r="72" spans="1:1">
+    <row r="72" spans="1:3">
       <c r="A72">
         <f t="shared" si="1"/>
         <v>170</v>
       </c>
     </row>
-    <row r="73" spans="1:1">
+    <row r="73" spans="1:3">
       <c r="A73">
         <f t="shared" si="1"/>
         <v>171</v>
       </c>
     </row>
-    <row r="74" spans="1:1">
+    <row r="74" spans="1:3">
       <c r="A74">
         <f t="shared" si="1"/>
         <v>172</v>
       </c>
     </row>
-    <row r="75" spans="1:1">
+    <row r="75" spans="1:3">
       <c r="A75">
         <f t="shared" si="1"/>
         <v>173</v>
       </c>
     </row>
-    <row r="76" spans="1:1">
+    <row r="76" spans="1:3">
       <c r="A76">
         <f t="shared" si="1"/>
         <v>174</v>
       </c>
     </row>
-    <row r="77" spans="1:1">
+    <row r="77" spans="1:3">
       <c r="A77">
         <f t="shared" si="1"/>
         <v>175</v>
       </c>
     </row>
-    <row r="78" spans="1:1">
+    <row r="78" spans="1:3">
       <c r="A78">
         <f t="shared" si="1"/>
         <v>176</v>
       </c>
     </row>
-    <row r="79" spans="1:1">
+    <row r="79" spans="1:3">
       <c r="A79">
         <f t="shared" si="1"/>
         <v>177</v>
       </c>
     </row>
-    <row r="80" spans="1:1">
+    <row r="80" spans="1:3">
       <c r="A80">
         <f t="shared" si="1"/>
         <v>178</v>

--- a/l_r/1st.xlsx
+++ b/l_r/1st.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\l_r\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{896D2C87-6D58-4CFC-BA91-B646F705B876}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F7AFAFE-C549-474D-9369-838E5EF9D327}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="43">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -203,6 +203,22 @@
   </si>
   <si>
     <t>A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>D</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>C</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>B</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -662,14 +678,14 @@
       </c>
       <c r="C11">
         <f>SUM(reading!C55:C102)</f>
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D11">
         <v>48</v>
       </c>
       <c r="E11" s="1">
         <f t="shared" si="1"/>
-        <v>0.14583333333333334</v>
+        <v>0.22916666666666666</v>
       </c>
     </row>
   </sheetData>
@@ -1321,7 +1337,7 @@
     <row r="1" spans="1:3">
       <c r="C1">
         <f>SUM(C3:C102)</f>
-        <v>43</v>
+        <v>47</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -2110,23 +2126,47 @@
         <f t="shared" si="0"/>
         <v>164</v>
       </c>
+      <c r="B66" t="s">
+        <v>39</v>
+      </c>
+      <c r="C66">
+        <v>1</v>
+      </c>
     </row>
     <row r="67" spans="1:3">
       <c r="A67">
         <f t="shared" si="0"/>
         <v>165</v>
       </c>
+      <c r="B67" t="s">
+        <v>40</v>
+      </c>
+      <c r="C67">
+        <v>1</v>
+      </c>
     </row>
     <row r="68" spans="1:3">
       <c r="A68">
         <f t="shared" si="0"/>
         <v>166</v>
+      </c>
+      <c r="B68" t="s">
+        <v>41</v>
+      </c>
+      <c r="C68">
+        <v>1</v>
       </c>
     </row>
     <row r="69" spans="1:3">
       <c r="A69">
         <f t="shared" ref="A69:A102" si="1">A68+1</f>
         <v>167</v>
+      </c>
+      <c r="B69" t="s">
+        <v>42</v>
+      </c>
+      <c r="C69">
+        <v>1</v>
       </c>
     </row>
     <row r="70" spans="1:3">

--- a/l_r/1st.xlsx
+++ b/l_r/1st.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\l_r\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F7AFAFE-C549-474D-9369-838E5EF9D327}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{791BD2CD-EA7A-4AE0-8FF4-B43804FC4E1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="210" yWindow="150" windowWidth="15450" windowHeight="15225" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="3" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="47">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -219,6 +219,22 @@
   </si>
   <si>
     <t>B</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>C</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>B</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>D</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>A</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -678,14 +694,14 @@
       </c>
       <c r="C11">
         <f>SUM(reading!C55:C102)</f>
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="D11">
         <v>48</v>
       </c>
       <c r="E11" s="1">
         <f t="shared" si="1"/>
-        <v>0.22916666666666666</v>
+        <v>0.39583333333333331</v>
       </c>
     </row>
   </sheetData>
@@ -1337,7 +1353,7 @@
     <row r="1" spans="1:3">
       <c r="C1">
         <f>SUM(C3:C102)</f>
-        <v>47</v>
+        <v>55</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -2174,47 +2190,95 @@
         <f t="shared" si="1"/>
         <v>168</v>
       </c>
+      <c r="B70" t="s">
+        <v>43</v>
+      </c>
+      <c r="C70">
+        <v>1</v>
+      </c>
     </row>
     <row r="71" spans="1:3">
       <c r="A71">
         <f t="shared" si="1"/>
         <v>169</v>
       </c>
+      <c r="B71" t="s">
+        <v>45</v>
+      </c>
+      <c r="C71">
+        <v>1</v>
+      </c>
     </row>
     <row r="72" spans="1:3">
       <c r="A72">
         <f t="shared" si="1"/>
         <v>170</v>
       </c>
+      <c r="B72" t="s">
+        <v>44</v>
+      </c>
+      <c r="C72">
+        <v>1</v>
+      </c>
     </row>
     <row r="73" spans="1:3">
       <c r="A73">
         <f t="shared" si="1"/>
         <v>171</v>
       </c>
+      <c r="B73" t="s">
+        <v>44</v>
+      </c>
+      <c r="C73">
+        <v>1</v>
+      </c>
     </row>
     <row r="74" spans="1:3">
       <c r="A74">
         <f t="shared" si="1"/>
         <v>172</v>
       </c>
+      <c r="B74" t="s">
+        <v>46</v>
+      </c>
+      <c r="C74">
+        <v>1</v>
+      </c>
     </row>
     <row r="75" spans="1:3">
       <c r="A75">
         <f t="shared" si="1"/>
         <v>173</v>
       </c>
+      <c r="B75" t="s">
+        <v>43</v>
+      </c>
+      <c r="C75">
+        <v>1</v>
+      </c>
     </row>
     <row r="76" spans="1:3">
       <c r="A76">
         <f t="shared" si="1"/>
         <v>174</v>
       </c>
+      <c r="B76" t="s">
+        <v>46</v>
+      </c>
+      <c r="C76">
+        <v>1</v>
+      </c>
     </row>
     <row r="77" spans="1:3">
       <c r="A77">
         <f t="shared" si="1"/>
         <v>175</v>
+      </c>
+      <c r="B77" t="s">
+        <v>45</v>
+      </c>
+      <c r="C77">
+        <v>1</v>
       </c>
     </row>
     <row r="78" spans="1:3">

--- a/l_r/1st.xlsx
+++ b/l_r/1st.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\l_r\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{791BD2CD-EA7A-4AE0-8FF4-B43804FC4E1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEE7BDC1-524E-43D4-930A-7C663F394681}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="210" yWindow="150" windowWidth="15450" windowHeight="15225" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="345" yWindow="585" windowWidth="15450" windowHeight="15225" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="3" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="51">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -235,6 +235,22 @@
   </si>
   <si>
     <t>A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>C</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>B</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>D</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -694,14 +710,14 @@
       </c>
       <c r="C11">
         <f>SUM(reading!C55:C102)</f>
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="D11">
         <v>48</v>
       </c>
       <c r="E11" s="1">
         <f t="shared" si="1"/>
-        <v>0.39583333333333331</v>
+        <v>0.60416666666666663</v>
       </c>
     </row>
   </sheetData>
@@ -1353,7 +1369,7 @@
     <row r="1" spans="1:3">
       <c r="C1">
         <f>SUM(C3:C102)</f>
-        <v>55</v>
+        <v>65</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -2286,110 +2302,170 @@
         <f t="shared" si="1"/>
         <v>176</v>
       </c>
+      <c r="B78" t="s">
+        <v>47</v>
+      </c>
+      <c r="C78">
+        <v>1</v>
+      </c>
     </row>
     <row r="79" spans="1:3">
       <c r="A79">
         <f t="shared" si="1"/>
         <v>177</v>
       </c>
+      <c r="B79" t="s">
+        <v>48</v>
+      </c>
+      <c r="C79">
+        <v>1</v>
+      </c>
     </row>
     <row r="80" spans="1:3">
       <c r="A80">
         <f t="shared" si="1"/>
         <v>178</v>
       </c>
-    </row>
-    <row r="81" spans="1:1">
+      <c r="B80" t="s">
+        <v>49</v>
+      </c>
+      <c r="C80">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3">
       <c r="A81">
         <f t="shared" si="1"/>
         <v>179</v>
       </c>
-    </row>
-    <row r="82" spans="1:1">
+      <c r="B81" t="s">
+        <v>47</v>
+      </c>
+      <c r="C81">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3">
       <c r="A82">
         <f t="shared" si="1"/>
         <v>180</v>
       </c>
-    </row>
-    <row r="83" spans="1:1">
+      <c r="B82" t="s">
+        <v>49</v>
+      </c>
+      <c r="C82">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3">
       <c r="A83">
         <f t="shared" si="1"/>
         <v>181</v>
       </c>
-    </row>
-    <row r="84" spans="1:1">
+      <c r="B83" t="s">
+        <v>49</v>
+      </c>
+      <c r="C83">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3">
       <c r="A84">
         <f t="shared" si="1"/>
         <v>182</v>
       </c>
-    </row>
-    <row r="85" spans="1:1">
+      <c r="B84" t="s">
+        <v>50</v>
+      </c>
+      <c r="C84">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3">
       <c r="A85">
         <f t="shared" si="1"/>
         <v>183</v>
       </c>
-    </row>
-    <row r="86" spans="1:1">
+      <c r="B85" t="s">
+        <v>48</v>
+      </c>
+      <c r="C85">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3">
       <c r="A86">
         <f t="shared" si="1"/>
         <v>184</v>
       </c>
-    </row>
-    <row r="87" spans="1:1">
+      <c r="B86" t="s">
+        <v>50</v>
+      </c>
+      <c r="C86">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3">
       <c r="A87">
         <f t="shared" si="1"/>
         <v>185</v>
       </c>
-    </row>
-    <row r="88" spans="1:1">
+      <c r="B87" t="s">
+        <v>47</v>
+      </c>
+      <c r="C87">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3">
       <c r="A88">
         <f t="shared" si="1"/>
         <v>186</v>
       </c>
     </row>
-    <row r="89" spans="1:1">
+    <row r="89" spans="1:3">
       <c r="A89">
         <f t="shared" si="1"/>
         <v>187</v>
       </c>
     </row>
-    <row r="90" spans="1:1">
+    <row r="90" spans="1:3">
       <c r="A90">
         <f t="shared" si="1"/>
         <v>188</v>
       </c>
     </row>
-    <row r="91" spans="1:1">
+    <row r="91" spans="1:3">
       <c r="A91">
         <f t="shared" si="1"/>
         <v>189</v>
       </c>
     </row>
-    <row r="92" spans="1:1">
+    <row r="92" spans="1:3">
       <c r="A92">
         <f t="shared" si="1"/>
         <v>190</v>
       </c>
     </row>
-    <row r="93" spans="1:1">
+    <row r="93" spans="1:3">
       <c r="A93">
         <f t="shared" si="1"/>
         <v>191</v>
       </c>
     </row>
-    <row r="94" spans="1:1">
+    <row r="94" spans="1:3">
       <c r="A94">
         <f t="shared" si="1"/>
         <v>192</v>
       </c>
     </row>
-    <row r="95" spans="1:1">
+    <row r="95" spans="1:3">
       <c r="A95">
         <f t="shared" si="1"/>
         <v>193</v>
       </c>
     </row>
-    <row r="96" spans="1:1">
+    <row r="96" spans="1:3">
       <c r="A96">
         <f t="shared" si="1"/>
         <v>194</v>

--- a/l_r/1st.xlsx
+++ b/l_r/1st.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\l_r\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEE7BDC1-524E-43D4-930A-7C663F394681}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{148ED916-8A87-4A1E-9C30-975AA9FA489E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="345" yWindow="585" windowWidth="15450" windowHeight="15225" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="13470" yWindow="540" windowWidth="15450" windowHeight="15225" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="3" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="55">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -251,6 +251,22 @@
   </si>
   <si>
     <t>D</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>C</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>D</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>B</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>A</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -710,14 +726,14 @@
       </c>
       <c r="C11">
         <f>SUM(reading!C55:C102)</f>
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="D11">
         <v>48</v>
       </c>
       <c r="E11" s="1">
         <f t="shared" si="1"/>
-        <v>0.60416666666666663</v>
+        <v>0.77083333333333337</v>
       </c>
     </row>
   </sheetData>
@@ -1369,7 +1385,7 @@
     <row r="1" spans="1:3">
       <c r="C1">
         <f>SUM(C3:C102)</f>
-        <v>65</v>
+        <v>73</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -2422,86 +2438,146 @@
         <f t="shared" si="1"/>
         <v>186</v>
       </c>
+      <c r="B88" t="s">
+        <v>51</v>
+      </c>
+      <c r="C88">
+        <v>1</v>
+      </c>
     </row>
     <row r="89" spans="1:3">
       <c r="A89">
         <f t="shared" si="1"/>
         <v>187</v>
       </c>
+      <c r="B89" t="s">
+        <v>52</v>
+      </c>
+      <c r="C89">
+        <v>1</v>
+      </c>
     </row>
     <row r="90" spans="1:3">
       <c r="A90">
         <f t="shared" si="1"/>
         <v>188</v>
       </c>
+      <c r="B90" t="s">
+        <v>51</v>
+      </c>
+      <c r="C90">
+        <v>0</v>
+      </c>
     </row>
     <row r="91" spans="1:3">
       <c r="A91">
         <f t="shared" si="1"/>
         <v>189</v>
       </c>
+      <c r="B91" t="s">
+        <v>53</v>
+      </c>
+      <c r="C91">
+        <v>1</v>
+      </c>
     </row>
     <row r="92" spans="1:3">
       <c r="A92">
         <f t="shared" si="1"/>
         <v>190</v>
       </c>
+      <c r="B92" t="s">
+        <v>52</v>
+      </c>
+      <c r="C92">
+        <v>0</v>
+      </c>
     </row>
     <row r="93" spans="1:3">
       <c r="A93">
         <f t="shared" si="1"/>
         <v>191</v>
       </c>
+      <c r="B93" t="s">
+        <v>51</v>
+      </c>
+      <c r="C93">
+        <v>1</v>
+      </c>
     </row>
     <row r="94" spans="1:3">
       <c r="A94">
         <f t="shared" si="1"/>
         <v>192</v>
       </c>
+      <c r="B94" t="s">
+        <v>52</v>
+      </c>
+      <c r="C94">
+        <v>1</v>
+      </c>
     </row>
     <row r="95" spans="1:3">
       <c r="A95">
         <f t="shared" si="1"/>
         <v>193</v>
       </c>
+      <c r="B95" t="s">
+        <v>53</v>
+      </c>
+      <c r="C95">
+        <v>1</v>
+      </c>
     </row>
     <row r="96" spans="1:3">
       <c r="A96">
         <f t="shared" si="1"/>
         <v>194</v>
       </c>
-    </row>
-    <row r="97" spans="1:1">
+      <c r="B96" t="s">
+        <v>52</v>
+      </c>
+      <c r="C96">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3">
       <c r="A97">
         <f t="shared" si="1"/>
         <v>195</v>
       </c>
-    </row>
-    <row r="98" spans="1:1">
+      <c r="B97" t="s">
+        <v>54</v>
+      </c>
+      <c r="C97">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3">
       <c r="A98">
         <f t="shared" si="1"/>
         <v>196</v>
       </c>
     </row>
-    <row r="99" spans="1:1">
+    <row r="99" spans="1:3">
       <c r="A99">
         <f t="shared" si="1"/>
         <v>197</v>
       </c>
     </row>
-    <row r="100" spans="1:1">
+    <row r="100" spans="1:3">
       <c r="A100">
         <f t="shared" si="1"/>
         <v>198</v>
       </c>
     </row>
-    <row r="101" spans="1:1">
+    <row r="101" spans="1:3">
       <c r="A101">
         <f t="shared" si="1"/>
         <v>199</v>
       </c>
     </row>
-    <row r="102" spans="1:1">
+    <row r="102" spans="1:3">
       <c r="A102">
         <f t="shared" si="1"/>
         <v>200</v>

--- a/l_r/1st.xlsx
+++ b/l_r/1st.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\l_r\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{148ED916-8A87-4A1E-9C30-975AA9FA489E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C0CB192-E948-42FD-8342-3F01D28F2B55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13470" yWindow="540" windowWidth="15450" windowHeight="15225" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="3" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="57">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -267,6 +267,14 @@
   </si>
   <si>
     <t>A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>C</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>B</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -726,14 +734,14 @@
       </c>
       <c r="C11">
         <f>SUM(reading!C55:C102)</f>
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="D11">
         <v>48</v>
       </c>
       <c r="E11" s="1">
         <f t="shared" si="1"/>
-        <v>0.77083333333333337</v>
+        <v>0.83333333333333337</v>
       </c>
     </row>
   </sheetData>
@@ -1385,7 +1393,7 @@
     <row r="1" spans="1:3">
       <c r="C1">
         <f>SUM(C3:C102)</f>
-        <v>73</v>
+        <v>76</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -2558,29 +2566,59 @@
         <f t="shared" si="1"/>
         <v>196</v>
       </c>
+      <c r="B98" t="s">
+        <v>55</v>
+      </c>
+      <c r="C98">
+        <v>0</v>
+      </c>
     </row>
     <row r="99" spans="1:3">
       <c r="A99">
         <f t="shared" si="1"/>
         <v>197</v>
       </c>
+      <c r="B99" t="s">
+        <v>55</v>
+      </c>
+      <c r="C99">
+        <v>1</v>
+      </c>
     </row>
     <row r="100" spans="1:3">
       <c r="A100">
         <f t="shared" si="1"/>
         <v>198</v>
       </c>
+      <c r="B100" t="s">
+        <v>55</v>
+      </c>
+      <c r="C100">
+        <v>1</v>
+      </c>
     </row>
     <row r="101" spans="1:3">
       <c r="A101">
         <f t="shared" si="1"/>
         <v>199</v>
       </c>
+      <c r="B101" t="s">
+        <v>56</v>
+      </c>
+      <c r="C101">
+        <v>1</v>
+      </c>
     </row>
     <row r="102" spans="1:3">
       <c r="A102">
         <f t="shared" si="1"/>
         <v>200</v>
+      </c>
+      <c r="B102" t="s">
+        <v>56</v>
+      </c>
+      <c r="C102">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/l_r/1st.xlsx
+++ b/l_r/1st.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\l_r\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C0CB192-E948-42FD-8342-3F01D28F2B55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E801556-26B7-4C95-B7E9-55DA643C2DC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="3" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="57">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -2635,7 +2635,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C7A3EDD-6597-4754-A609-A225833ECC81}">
-  <dimension ref="A2:D48"/>
+  <dimension ref="A2:D54"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="2" spans="1:4">
@@ -3207,6 +3207,54 @@
       </c>
       <c r="C48">
         <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3">
+      <c r="A49">
+        <v>155</v>
+      </c>
+      <c r="B49" t="s">
+        <v>9</v>
+      </c>
+      <c r="C49">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3">
+      <c r="A50">
+        <v>156</v>
+      </c>
+      <c r="B50" t="s">
+        <v>8</v>
+      </c>
+      <c r="C50">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3">
+      <c r="A51">
+        <v>157</v>
+      </c>
+      <c r="B51" t="s">
+        <v>10</v>
+      </c>
+      <c r="C51">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3">
+      <c r="A52">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3">
+      <c r="A53">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3">
+      <c r="A54">
+        <v>160</v>
       </c>
     </row>
   </sheetData>

--- a/l_r/1st.xlsx
+++ b/l_r/1st.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\l_r\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E801556-26B7-4C95-B7E9-55DA643C2DC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D45411B-2A5B-4498-8507-999C84B01042}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="57">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -3246,15 +3246,33 @@
       <c r="A52">
         <v>158</v>
       </c>
+      <c r="B52" t="s">
+        <v>11</v>
+      </c>
+      <c r="C52">
+        <v>1</v>
+      </c>
     </row>
     <row r="53" spans="1:3">
       <c r="A53">
         <v>159</v>
       </c>
+      <c r="B53" t="s">
+        <v>9</v>
+      </c>
+      <c r="C53">
+        <v>0</v>
+      </c>
     </row>
     <row r="54" spans="1:3">
       <c r="A54">
         <v>160</v>
+      </c>
+      <c r="B54" t="s">
+        <v>11</v>
+      </c>
+      <c r="C54">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/l_r/1st.xlsx
+++ b/l_r/1st.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\l_r\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D45411B-2A5B-4498-8507-999C84B01042}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F28EA945-6DB3-4E5E-8AA2-EC22ACA1CF2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="57">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -2635,7 +2635,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C7A3EDD-6597-4754-A609-A225833ECC81}">
-  <dimension ref="A2:D54"/>
+  <dimension ref="A2:D57"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="2" spans="1:4">
@@ -3272,6 +3272,39 @@
         <v>11</v>
       </c>
       <c r="C54">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3">
+      <c r="A55">
+        <v>161</v>
+      </c>
+      <c r="B55" t="s">
+        <v>11</v>
+      </c>
+      <c r="C55">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3">
+      <c r="A56">
+        <v>162</v>
+      </c>
+      <c r="B56" t="s">
+        <v>9</v>
+      </c>
+      <c r="C56">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3">
+      <c r="A57">
+        <v>163</v>
+      </c>
+      <c r="B57" t="s">
+        <v>8</v>
+      </c>
+      <c r="C57">
         <v>1</v>
       </c>
     </row>

--- a/l_r/1st.xlsx
+++ b/l_r/1st.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\l_r\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F28EA945-6DB3-4E5E-8AA2-EC22ACA1CF2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A80FDDF-8D08-4292-A800-AC5DF8D6CC87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="405" yWindow="210" windowWidth="15450" windowHeight="15225" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="3" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="57">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -2635,7 +2635,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C7A3EDD-6597-4754-A609-A225833ECC81}">
-  <dimension ref="A2:D57"/>
+  <dimension ref="A2:D61"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="2" spans="1:4">
@@ -3305,6 +3305,50 @@
         <v>8</v>
       </c>
       <c r="C57">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3">
+      <c r="A58">
+        <v>164</v>
+      </c>
+      <c r="B58" t="s">
+        <v>11</v>
+      </c>
+      <c r="C58">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3">
+      <c r="A59">
+        <v>165</v>
+      </c>
+      <c r="B59" t="s">
+        <v>8</v>
+      </c>
+      <c r="C59">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3">
+      <c r="A60">
+        <v>166</v>
+      </c>
+      <c r="B60" t="s">
+        <v>10</v>
+      </c>
+      <c r="C60">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3">
+      <c r="A61">
+        <v>167</v>
+      </c>
+      <c r="B61" t="s">
+        <v>9</v>
+      </c>
+      <c r="C61">
         <v>1</v>
       </c>
     </row>

--- a/l_r/1st.xlsx
+++ b/l_r/1st.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\l_r\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A80FDDF-8D08-4292-A800-AC5DF8D6CC87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{561103BE-3BD1-4003-87E6-7F5BBBFFF83F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="405" yWindow="210" windowWidth="15450" windowHeight="15225" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="270" yWindow="450" windowWidth="13395" windowHeight="13515" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="3" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="57">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -2635,7 +2635,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C7A3EDD-6597-4754-A609-A225833ECC81}">
-  <dimension ref="A2:D61"/>
+  <dimension ref="A2:D69"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="2" spans="1:4">
@@ -3350,6 +3350,70 @@
       </c>
       <c r="C61">
         <v>1</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3">
+      <c r="A62">
+        <v>168</v>
+      </c>
+      <c r="B62" t="s">
+        <v>10</v>
+      </c>
+      <c r="C62">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3">
+      <c r="A63">
+        <v>169</v>
+      </c>
+      <c r="B63" t="s">
+        <v>11</v>
+      </c>
+      <c r="C63">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3">
+      <c r="A64">
+        <v>170</v>
+      </c>
+      <c r="B64" t="s">
+        <v>9</v>
+      </c>
+      <c r="C64">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3">
+      <c r="A65">
+        <v>171</v>
+      </c>
+      <c r="B65" t="s">
+        <v>9</v>
+      </c>
+      <c r="C65">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3">
+      <c r="A66">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3">
+      <c r="A67">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3">
+      <c r="A68">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3">
+      <c r="A69">
+        <v>175</v>
       </c>
     </row>
   </sheetData>

--- a/l_r/1st.xlsx
+++ b/l_r/1st.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\l_r\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{561103BE-3BD1-4003-87E6-7F5BBBFFF83F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58813285-8071-4D66-921B-086882A038D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="270" yWindow="450" windowWidth="13395" windowHeight="13515" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="630" yWindow="1200" windowWidth="13395" windowHeight="13515" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="3" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="57">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -3400,20 +3400,44 @@
       <c r="A66">
         <v>172</v>
       </c>
+      <c r="B66" t="s">
+        <v>9</v>
+      </c>
+      <c r="C66">
+        <v>0</v>
+      </c>
     </row>
     <row r="67" spans="1:3">
       <c r="A67">
         <v>173</v>
       </c>
+      <c r="B67" t="s">
+        <v>10</v>
+      </c>
+      <c r="C67">
+        <v>1</v>
+      </c>
     </row>
     <row r="68" spans="1:3">
       <c r="A68">
         <v>174</v>
       </c>
+      <c r="B68" t="s">
+        <v>8</v>
+      </c>
+      <c r="C68">
+        <v>1</v>
+      </c>
     </row>
     <row r="69" spans="1:3">
       <c r="A69">
         <v>175</v>
+      </c>
+      <c r="B69" t="s">
+        <v>11</v>
+      </c>
+      <c r="C69">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/l_r/1st.xlsx
+++ b/l_r/1st.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\l_r\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58813285-8071-4D66-921B-086882A038D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54F5FF43-6A78-4D5B-B797-94BD0B40728E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="630" yWindow="1200" windowWidth="13395" windowHeight="13515" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9000" yWindow="2430" windowWidth="13395" windowHeight="13515" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="3" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="57">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -2635,7 +2635,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C7A3EDD-6597-4754-A609-A225833ECC81}">
-  <dimension ref="A2:D69"/>
+  <dimension ref="A2:D79"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="2" spans="1:4">
@@ -3437,6 +3437,121 @@
         <v>11</v>
       </c>
       <c r="C69">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3">
+      <c r="A70">
+        <v>176</v>
+      </c>
+      <c r="B70" t="s">
+        <v>10</v>
+      </c>
+      <c r="C70">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3">
+      <c r="A71">
+        <v>177</v>
+      </c>
+      <c r="B71" t="s">
+        <v>8</v>
+      </c>
+      <c r="C71">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3">
+      <c r="A72">
+        <v>178</v>
+      </c>
+      <c r="B72" t="s">
+        <v>9</v>
+      </c>
+      <c r="C72">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3">
+      <c r="A73">
+        <v>179</v>
+      </c>
+      <c r="B73" t="s">
+        <v>10</v>
+      </c>
+      <c r="C73">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3">
+      <c r="A74">
+        <v>180</v>
+      </c>
+      <c r="B74" t="s">
+        <v>9</v>
+      </c>
+      <c r="C74">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3">
+      <c r="A75">
+        <f>A74+1</f>
+        <v>181</v>
+      </c>
+      <c r="B75" t="s">
+        <v>8</v>
+      </c>
+      <c r="C75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3">
+      <c r="A76">
+        <f t="shared" ref="A76:A81" si="3">A75+1</f>
+        <v>182</v>
+      </c>
+      <c r="B76" t="s">
+        <v>11</v>
+      </c>
+      <c r="C76">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3">
+      <c r="A77">
+        <f t="shared" si="3"/>
+        <v>183</v>
+      </c>
+      <c r="B77" t="s">
+        <v>8</v>
+      </c>
+      <c r="C77">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3">
+      <c r="A78">
+        <f t="shared" si="3"/>
+        <v>184</v>
+      </c>
+      <c r="B78" t="s">
+        <v>11</v>
+      </c>
+      <c r="C78">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3">
+      <c r="A79">
+        <f t="shared" si="3"/>
+        <v>185</v>
+      </c>
+      <c r="B79" t="s">
+        <v>10</v>
+      </c>
+      <c r="C79">
         <v>1</v>
       </c>
     </row>

--- a/l_r/1st.xlsx
+++ b/l_r/1st.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\l_r\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54F5FF43-6A78-4D5B-B797-94BD0B40728E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE4EFB8B-6A1D-46F5-80D1-DFCC10EA2633}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9000" yWindow="2430" windowWidth="13395" windowHeight="13515" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="780" windowWidth="13395" windowHeight="13515" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="3" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="57">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -2635,7 +2635,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C7A3EDD-6597-4754-A609-A225833ECC81}">
-  <dimension ref="A2:D79"/>
+  <dimension ref="A2:D84"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="2" spans="1:4">
@@ -3509,7 +3509,7 @@
     </row>
     <row r="76" spans="1:3">
       <c r="A76">
-        <f t="shared" ref="A76:A81" si="3">A75+1</f>
+        <f t="shared" ref="A76:A84" si="3">A75+1</f>
         <v>182</v>
       </c>
       <c r="B76" t="s">
@@ -3552,6 +3552,66 @@
         <v>10</v>
       </c>
       <c r="C79">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3">
+      <c r="A80">
+        <f t="shared" si="3"/>
+        <v>186</v>
+      </c>
+      <c r="B80" t="s">
+        <v>10</v>
+      </c>
+      <c r="C80">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3">
+      <c r="A81">
+        <f t="shared" si="3"/>
+        <v>187</v>
+      </c>
+      <c r="B81" t="s">
+        <v>11</v>
+      </c>
+      <c r="C81">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3">
+      <c r="A82">
+        <f t="shared" si="3"/>
+        <v>188</v>
+      </c>
+      <c r="B82" t="s">
+        <v>9</v>
+      </c>
+      <c r="C82">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3">
+      <c r="A83">
+        <f t="shared" si="3"/>
+        <v>189</v>
+      </c>
+      <c r="B83" t="s">
+        <v>9</v>
+      </c>
+      <c r="C83">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3">
+      <c r="A84">
+        <f t="shared" si="3"/>
+        <v>190</v>
+      </c>
+      <c r="B84" t="s">
+        <v>8</v>
+      </c>
+      <c r="C84">
         <v>1</v>
       </c>
     </row>

--- a/l_r/1st.xlsx
+++ b/l_r/1st.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\l_r\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE4EFB8B-6A1D-46F5-80D1-DFCC10EA2633}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91074836-1E6F-4693-A891-0D17B7A7083F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="780" windowWidth="13395" windowHeight="13515" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="570" yWindow="615" windowWidth="13395" windowHeight="13515" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="3" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="57">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -2635,7 +2635,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C7A3EDD-6597-4754-A609-A225833ECC81}">
-  <dimension ref="A2:D84"/>
+  <dimension ref="A2:D89"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="2" spans="1:4">
@@ -3509,7 +3509,7 @@
     </row>
     <row r="76" spans="1:3">
       <c r="A76">
-        <f t="shared" ref="A76:A84" si="3">A75+1</f>
+        <f t="shared" ref="A76:A89" si="3">A75+1</f>
         <v>182</v>
       </c>
       <c r="B76" t="s">
@@ -3612,6 +3612,62 @@
         <v>8</v>
       </c>
       <c r="C84">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3">
+      <c r="A85">
+        <v>191</v>
+      </c>
+      <c r="B85" t="s">
+        <v>10</v>
+      </c>
+      <c r="C85">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3">
+      <c r="A86">
+        <v>192</v>
+      </c>
+      <c r="B86" t="s">
+        <v>11</v>
+      </c>
+      <c r="C86">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3">
+      <c r="A87">
+        <v>193</v>
+      </c>
+      <c r="B87" t="s">
+        <v>9</v>
+      </c>
+      <c r="C87">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3">
+      <c r="A88">
+        <v>194</v>
+      </c>
+      <c r="B88" t="s">
+        <v>11</v>
+      </c>
+      <c r="C88">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3">
+      <c r="A89">
+        <f t="shared" si="3"/>
+        <v>195</v>
+      </c>
+      <c r="B89" t="s">
+        <v>8</v>
+      </c>
+      <c r="C89">
         <v>1</v>
       </c>
     </row>

--- a/l_r/1st.xlsx
+++ b/l_r/1st.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\l_r\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91074836-1E6F-4693-A891-0D17B7A7083F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9DC835F-3350-42CE-A999-07648249458B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="570" yWindow="615" windowWidth="13395" windowHeight="13515" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="57">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -2635,7 +2635,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C7A3EDD-6597-4754-A609-A225833ECC81}">
-  <dimension ref="A2:D89"/>
+  <dimension ref="A2:D94"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="2" spans="1:4">
@@ -3668,6 +3668,61 @@
         <v>8</v>
       </c>
       <c r="C89">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3">
+      <c r="A90">
+        <v>196</v>
+      </c>
+      <c r="B90" t="s">
+        <v>8</v>
+      </c>
+      <c r="C90">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3">
+      <c r="A91">
+        <v>197</v>
+      </c>
+      <c r="B91" t="s">
+        <v>10</v>
+      </c>
+      <c r="C91">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3">
+      <c r="A92">
+        <v>198</v>
+      </c>
+      <c r="B92" t="s">
+        <v>9</v>
+      </c>
+      <c r="C92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3">
+      <c r="A93">
+        <v>199</v>
+      </c>
+      <c r="B93" t="s">
+        <v>9</v>
+      </c>
+      <c r="C93">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3">
+      <c r="A94">
+        <v>200</v>
+      </c>
+      <c r="B94" t="s">
+        <v>11</v>
+      </c>
+      <c r="C94">
         <v>1</v>
       </c>
     </row>

--- a/l_r/1st.xlsx
+++ b/l_r/1st.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\l_r\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9DC835F-3350-42CE-A999-07648249458B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6687D8BA-5E28-4A8B-95CF-FEB358CEC11B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="570" yWindow="615" windowWidth="13395" windowHeight="13515" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14100" yWindow="195" windowWidth="13395" windowHeight="13515" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="3" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="57">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -2635,7 +2635,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C7A3EDD-6597-4754-A609-A225833ECC81}">
-  <dimension ref="A2:D94"/>
+  <dimension ref="A2:D104"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="2" spans="1:4">
@@ -3723,6 +3723,116 @@
         <v>11</v>
       </c>
       <c r="C94">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3">
+      <c r="A95">
+        <v>101</v>
+      </c>
+      <c r="B95" t="s">
+        <v>8</v>
+      </c>
+      <c r="C95">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3">
+      <c r="A96">
+        <v>102</v>
+      </c>
+      <c r="B96" t="s">
+        <v>9</v>
+      </c>
+      <c r="C96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3">
+      <c r="A97">
+        <v>103</v>
+      </c>
+      <c r="B97" t="s">
+        <v>10</v>
+      </c>
+      <c r="C97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3">
+      <c r="A98">
+        <v>104</v>
+      </c>
+      <c r="B98" t="s">
+        <v>11</v>
+      </c>
+      <c r="C98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3">
+      <c r="A99">
+        <v>105</v>
+      </c>
+      <c r="B99" t="s">
+        <v>10</v>
+      </c>
+      <c r="C99">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3">
+      <c r="A100">
+        <v>106</v>
+      </c>
+      <c r="B100" t="s">
+        <v>10</v>
+      </c>
+      <c r="C100">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3">
+      <c r="A101">
+        <v>107</v>
+      </c>
+      <c r="B101" t="s">
+        <v>11</v>
+      </c>
+      <c r="C101">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3">
+      <c r="A102">
+        <v>108</v>
+      </c>
+      <c r="B102" t="s">
+        <v>8</v>
+      </c>
+      <c r="C102">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3">
+      <c r="A103">
+        <v>109</v>
+      </c>
+      <c r="B103" t="s">
+        <v>11</v>
+      </c>
+      <c r="C103">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3">
+      <c r="A104">
+        <v>110</v>
+      </c>
+      <c r="B104" t="s">
+        <v>11</v>
+      </c>
+      <c r="C104">
         <v>1</v>
       </c>
     </row>

--- a/l_r/1st.xlsx
+++ b/l_r/1st.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\l_r\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6687D8BA-5E28-4A8B-95CF-FEB358CEC11B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C7130E2-1C51-478E-B168-08ED7B9D2DDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14100" yWindow="195" windowWidth="13395" windowHeight="13515" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="57">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -2635,7 +2635,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C7A3EDD-6597-4754-A609-A225833ECC81}">
-  <dimension ref="A2:D104"/>
+  <dimension ref="A2:D114"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="2" spans="1:4">
@@ -3833,6 +3833,126 @@
         <v>11</v>
       </c>
       <c r="C104">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3">
+      <c r="A105">
+        <f>A104+1</f>
+        <v>111</v>
+      </c>
+      <c r="B105" t="s">
+        <v>9</v>
+      </c>
+      <c r="C105">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3">
+      <c r="A106">
+        <f t="shared" ref="A106:A114" si="4">A105+1</f>
+        <v>112</v>
+      </c>
+      <c r="B106" t="s">
+        <v>10</v>
+      </c>
+      <c r="C106">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3">
+      <c r="A107">
+        <f t="shared" si="4"/>
+        <v>113</v>
+      </c>
+      <c r="B107" t="s">
+        <v>9</v>
+      </c>
+      <c r="C107">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3">
+      <c r="A108">
+        <f t="shared" si="4"/>
+        <v>114</v>
+      </c>
+      <c r="B108" t="s">
+        <v>8</v>
+      </c>
+      <c r="C108">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3">
+      <c r="A109">
+        <f t="shared" si="4"/>
+        <v>115</v>
+      </c>
+      <c r="B109" t="s">
+        <v>8</v>
+      </c>
+      <c r="C109">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3">
+      <c r="A110">
+        <f t="shared" si="4"/>
+        <v>116</v>
+      </c>
+      <c r="B110" t="s">
+        <v>11</v>
+      </c>
+      <c r="C110">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3">
+      <c r="A111">
+        <f t="shared" si="4"/>
+        <v>117</v>
+      </c>
+      <c r="B111" t="s">
+        <v>9</v>
+      </c>
+      <c r="C111">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3">
+      <c r="A112">
+        <f t="shared" si="4"/>
+        <v>118</v>
+      </c>
+      <c r="B112" t="s">
+        <v>8</v>
+      </c>
+      <c r="C112">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3">
+      <c r="A113">
+        <f t="shared" si="4"/>
+        <v>119</v>
+      </c>
+      <c r="B113" t="s">
+        <v>8</v>
+      </c>
+      <c r="C113">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3">
+      <c r="A114">
+        <f t="shared" si="4"/>
+        <v>120</v>
+      </c>
+      <c r="B114" t="s">
+        <v>10</v>
+      </c>
+      <c r="C114">
         <v>1</v>
       </c>
     </row>

--- a/l_r/1st.xlsx
+++ b/l_r/1st.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\l_r\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C7130E2-1C51-478E-B168-08ED7B9D2DDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B358EF73-1CF8-4621-8A9B-0BE3B3A63384}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14100" yWindow="195" windowWidth="13395" windowHeight="13515" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="3" r:id="rId1"/>
     <sheet name="listening" sheetId="1" r:id="rId2"/>
     <sheet name="reading" sheetId="2" r:id="rId3"/>
     <sheet name="review" sheetId="4" r:id="rId4"/>
+    <sheet name="Sheet1" sheetId="5" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">listening!$A$2:$C$102</definedName>
@@ -32,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="58">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -277,6 +278,10 @@
     <t>B</t>
     <phoneticPr fontId="1"/>
   </si>
+  <si>
+    <t>x</t>
+    <phoneticPr fontId="1"/>
+  </si>
 </sst>
 </file>
 
@@ -336,6 +341,2711 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ja-JP"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ja-JP"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Sheet1!$B$5:$B$309</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="305"/>
+                <c:pt idx="0">
+                  <c:v>0.1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.30000000000000004</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.6</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.7</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.79999999999999993</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.89999999999999991</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.99999999999999989</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>1.0999999999999999</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>1.2</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>1.3</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>1.4000000000000001</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>1.5000000000000002</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>1.6000000000000003</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>1.7000000000000004</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>1.8000000000000005</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>1.9000000000000006</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>2.0000000000000004</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>2.1000000000000005</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>2.2000000000000006</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>2.3000000000000007</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>2.4000000000000008</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>2.5000000000000009</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>2.600000000000001</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>2.7000000000000011</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>2.8000000000000012</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>2.9000000000000012</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>3.0000000000000013</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>3.1000000000000014</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>3.2000000000000015</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>3.3000000000000016</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>3.4000000000000017</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>3.5000000000000018</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>3.6000000000000019</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>3.700000000000002</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>3.800000000000002</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>3.9000000000000021</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>4.0000000000000018</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>4.1000000000000014</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>4.2000000000000011</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>4.3000000000000007</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>4.4000000000000004</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>4.5</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>4.5999999999999996</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>4.6999999999999993</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>4.7999999999999989</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>4.8999999999999986</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>4.9999999999999982</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>5.0999999999999979</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>5.1999999999999975</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>5.2999999999999972</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>5.3999999999999968</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>5.4999999999999964</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>5.5999999999999961</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>5.6999999999999957</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>5.7999999999999954</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>5.899999999999995</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>5.9999999999999947</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>6.0999999999999943</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>6.199999999999994</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>6.2999999999999936</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>6.3999999999999932</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>6.4999999999999929</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>6.5999999999999925</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>6.6999999999999922</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>6.7999999999999918</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>6.8999999999999915</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>6.9999999999999911</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>7.0999999999999908</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>7.1999999999999904</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>7.2999999999999901</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>7.3999999999999897</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>7.4999999999999893</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>7.599999999999989</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>7.6999999999999886</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>7.7999999999999883</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>7.8999999999999879</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>7.9999999999999876</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>8.0999999999999872</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>8.1999999999999869</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>8.2999999999999865</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>8.3999999999999861</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>8.4999999999999858</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>8.5999999999999854</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>8.6999999999999851</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>8.7999999999999847</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>8.8999999999999844</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>8.999999999999984</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>9.0999999999999837</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>9.1999999999999833</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>9.2999999999999829</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>9.3999999999999826</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>9.4999999999999822</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>9.5999999999999819</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>9.6999999999999815</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>9.7999999999999812</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>9.8999999999999808</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>9.9999999999999805</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>10.09999999999998</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>10.19999999999998</c:v>
+                </c:pt>
+                <c:pt idx="102">
+                  <c:v>10.299999999999979</c:v>
+                </c:pt>
+                <c:pt idx="103">
+                  <c:v>10.399999999999979</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>10.499999999999979</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>10.599999999999978</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>10.699999999999978</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>10.799999999999978</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>10.899999999999977</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>10.999999999999977</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>11.099999999999977</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>11.199999999999976</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>11.299999999999976</c:v>
+                </c:pt>
+                <c:pt idx="113">
+                  <c:v>11.399999999999975</c:v>
+                </c:pt>
+                <c:pt idx="114">
+                  <c:v>11.499999999999975</c:v>
+                </c:pt>
+                <c:pt idx="115">
+                  <c:v>11.599999999999975</c:v>
+                </c:pt>
+                <c:pt idx="116">
+                  <c:v>11.699999999999974</c:v>
+                </c:pt>
+                <c:pt idx="117">
+                  <c:v>11.799999999999974</c:v>
+                </c:pt>
+                <c:pt idx="118">
+                  <c:v>11.899999999999974</c:v>
+                </c:pt>
+                <c:pt idx="119">
+                  <c:v>11.999999999999973</c:v>
+                </c:pt>
+                <c:pt idx="120">
+                  <c:v>12.099999999999973</c:v>
+                </c:pt>
+                <c:pt idx="121">
+                  <c:v>12.199999999999973</c:v>
+                </c:pt>
+                <c:pt idx="122">
+                  <c:v>12.299999999999972</c:v>
+                </c:pt>
+                <c:pt idx="123">
+                  <c:v>12.399999999999972</c:v>
+                </c:pt>
+                <c:pt idx="124">
+                  <c:v>12.499999999999972</c:v>
+                </c:pt>
+                <c:pt idx="125">
+                  <c:v>12.599999999999971</c:v>
+                </c:pt>
+                <c:pt idx="126">
+                  <c:v>12.699999999999971</c:v>
+                </c:pt>
+                <c:pt idx="127">
+                  <c:v>12.799999999999971</c:v>
+                </c:pt>
+                <c:pt idx="128">
+                  <c:v>12.89999999999997</c:v>
+                </c:pt>
+                <c:pt idx="129">
+                  <c:v>12.99999999999997</c:v>
+                </c:pt>
+                <c:pt idx="130">
+                  <c:v>13.099999999999969</c:v>
+                </c:pt>
+                <c:pt idx="131">
+                  <c:v>13.199999999999969</c:v>
+                </c:pt>
+                <c:pt idx="132">
+                  <c:v>13.299999999999969</c:v>
+                </c:pt>
+                <c:pt idx="133">
+                  <c:v>13.399999999999968</c:v>
+                </c:pt>
+                <c:pt idx="134">
+                  <c:v>13.499999999999968</c:v>
+                </c:pt>
+                <c:pt idx="135">
+                  <c:v>13.599999999999968</c:v>
+                </c:pt>
+                <c:pt idx="136">
+                  <c:v>13.699999999999967</c:v>
+                </c:pt>
+                <c:pt idx="137">
+                  <c:v>13.799999999999967</c:v>
+                </c:pt>
+                <c:pt idx="138">
+                  <c:v>13.899999999999967</c:v>
+                </c:pt>
+                <c:pt idx="139">
+                  <c:v>13.999999999999966</c:v>
+                </c:pt>
+                <c:pt idx="140">
+                  <c:v>14.099999999999966</c:v>
+                </c:pt>
+                <c:pt idx="141">
+                  <c:v>14.199999999999966</c:v>
+                </c:pt>
+                <c:pt idx="142">
+                  <c:v>14.299999999999965</c:v>
+                </c:pt>
+                <c:pt idx="143">
+                  <c:v>14.399999999999965</c:v>
+                </c:pt>
+                <c:pt idx="144">
+                  <c:v>14.499999999999964</c:v>
+                </c:pt>
+                <c:pt idx="145">
+                  <c:v>14.599999999999964</c:v>
+                </c:pt>
+                <c:pt idx="146">
+                  <c:v>14.699999999999964</c:v>
+                </c:pt>
+                <c:pt idx="147">
+                  <c:v>14.799999999999963</c:v>
+                </c:pt>
+                <c:pt idx="148">
+                  <c:v>14.899999999999963</c:v>
+                </c:pt>
+                <c:pt idx="149">
+                  <c:v>14.999999999999963</c:v>
+                </c:pt>
+                <c:pt idx="150">
+                  <c:v>15.099999999999962</c:v>
+                </c:pt>
+                <c:pt idx="151">
+                  <c:v>15.199999999999962</c:v>
+                </c:pt>
+                <c:pt idx="152">
+                  <c:v>15.299999999999962</c:v>
+                </c:pt>
+                <c:pt idx="153">
+                  <c:v>15.399999999999961</c:v>
+                </c:pt>
+                <c:pt idx="154">
+                  <c:v>15.499999999999961</c:v>
+                </c:pt>
+                <c:pt idx="155">
+                  <c:v>15.599999999999961</c:v>
+                </c:pt>
+                <c:pt idx="156">
+                  <c:v>15.69999999999996</c:v>
+                </c:pt>
+                <c:pt idx="157">
+                  <c:v>15.79999999999996</c:v>
+                </c:pt>
+                <c:pt idx="158">
+                  <c:v>15.899999999999959</c:v>
+                </c:pt>
+                <c:pt idx="159">
+                  <c:v>15.999999999999959</c:v>
+                </c:pt>
+                <c:pt idx="160">
+                  <c:v>16.099999999999959</c:v>
+                </c:pt>
+                <c:pt idx="161">
+                  <c:v>16.19999999999996</c:v>
+                </c:pt>
+                <c:pt idx="162">
+                  <c:v>16.299999999999962</c:v>
+                </c:pt>
+                <c:pt idx="163">
+                  <c:v>16.399999999999963</c:v>
+                </c:pt>
+                <c:pt idx="164">
+                  <c:v>16.499999999999964</c:v>
+                </c:pt>
+                <c:pt idx="165">
+                  <c:v>16.599999999999966</c:v>
+                </c:pt>
+                <c:pt idx="166">
+                  <c:v>16.699999999999967</c:v>
+                </c:pt>
+                <c:pt idx="167">
+                  <c:v>16.799999999999969</c:v>
+                </c:pt>
+                <c:pt idx="168">
+                  <c:v>16.89999999999997</c:v>
+                </c:pt>
+                <c:pt idx="169">
+                  <c:v>16.999999999999972</c:v>
+                </c:pt>
+                <c:pt idx="170">
+                  <c:v>17.099999999999973</c:v>
+                </c:pt>
+                <c:pt idx="171">
+                  <c:v>17.199999999999974</c:v>
+                </c:pt>
+                <c:pt idx="172">
+                  <c:v>17.299999999999976</c:v>
+                </c:pt>
+                <c:pt idx="173">
+                  <c:v>17.399999999999977</c:v>
+                </c:pt>
+                <c:pt idx="174">
+                  <c:v>17.499999999999979</c:v>
+                </c:pt>
+                <c:pt idx="175">
+                  <c:v>17.59999999999998</c:v>
+                </c:pt>
+                <c:pt idx="176">
+                  <c:v>17.699999999999982</c:v>
+                </c:pt>
+                <c:pt idx="177">
+                  <c:v>17.799999999999983</c:v>
+                </c:pt>
+                <c:pt idx="178">
+                  <c:v>17.899999999999984</c:v>
+                </c:pt>
+                <c:pt idx="179">
+                  <c:v>17.999999999999986</c:v>
+                </c:pt>
+                <c:pt idx="180">
+                  <c:v>18.099999999999987</c:v>
+                </c:pt>
+                <c:pt idx="181">
+                  <c:v>18.199999999999989</c:v>
+                </c:pt>
+                <c:pt idx="182">
+                  <c:v>18.29999999999999</c:v>
+                </c:pt>
+                <c:pt idx="183">
+                  <c:v>18.399999999999991</c:v>
+                </c:pt>
+                <c:pt idx="184">
+                  <c:v>18.499999999999993</c:v>
+                </c:pt>
+                <c:pt idx="185">
+                  <c:v>18.599999999999994</c:v>
+                </c:pt>
+                <c:pt idx="186">
+                  <c:v>18.699999999999996</c:v>
+                </c:pt>
+                <c:pt idx="187">
+                  <c:v>18.799999999999997</c:v>
+                </c:pt>
+                <c:pt idx="188">
+                  <c:v>18.899999999999999</c:v>
+                </c:pt>
+                <c:pt idx="189">
+                  <c:v>19</c:v>
+                </c:pt>
+                <c:pt idx="190">
+                  <c:v>19.100000000000001</c:v>
+                </c:pt>
+                <c:pt idx="191">
+                  <c:v>19.200000000000003</c:v>
+                </c:pt>
+                <c:pt idx="192">
+                  <c:v>19.300000000000004</c:v>
+                </c:pt>
+                <c:pt idx="193">
+                  <c:v>19.400000000000006</c:v>
+                </c:pt>
+                <c:pt idx="194">
+                  <c:v>19.500000000000007</c:v>
+                </c:pt>
+                <c:pt idx="195">
+                  <c:v>19.600000000000009</c:v>
+                </c:pt>
+                <c:pt idx="196">
+                  <c:v>19.70000000000001</c:v>
+                </c:pt>
+                <c:pt idx="197">
+                  <c:v>19.800000000000011</c:v>
+                </c:pt>
+                <c:pt idx="198">
+                  <c:v>19.900000000000013</c:v>
+                </c:pt>
+                <c:pt idx="199">
+                  <c:v>20.000000000000014</c:v>
+                </c:pt>
+                <c:pt idx="200">
+                  <c:v>20.100000000000016</c:v>
+                </c:pt>
+                <c:pt idx="201">
+                  <c:v>20.200000000000017</c:v>
+                </c:pt>
+                <c:pt idx="202">
+                  <c:v>20.300000000000018</c:v>
+                </c:pt>
+                <c:pt idx="203">
+                  <c:v>20.40000000000002</c:v>
+                </c:pt>
+                <c:pt idx="204">
+                  <c:v>20.500000000000021</c:v>
+                </c:pt>
+                <c:pt idx="205">
+                  <c:v>20.600000000000023</c:v>
+                </c:pt>
+                <c:pt idx="206">
+                  <c:v>20.700000000000024</c:v>
+                </c:pt>
+                <c:pt idx="207">
+                  <c:v>20.800000000000026</c:v>
+                </c:pt>
+                <c:pt idx="208">
+                  <c:v>20.900000000000027</c:v>
+                </c:pt>
+                <c:pt idx="209">
+                  <c:v>21.000000000000028</c:v>
+                </c:pt>
+                <c:pt idx="210">
+                  <c:v>21.10000000000003</c:v>
+                </c:pt>
+                <c:pt idx="211">
+                  <c:v>21.200000000000031</c:v>
+                </c:pt>
+                <c:pt idx="212">
+                  <c:v>21.300000000000033</c:v>
+                </c:pt>
+                <c:pt idx="213">
+                  <c:v>21.400000000000034</c:v>
+                </c:pt>
+                <c:pt idx="214">
+                  <c:v>21.500000000000036</c:v>
+                </c:pt>
+                <c:pt idx="215">
+                  <c:v>21.600000000000037</c:v>
+                </c:pt>
+                <c:pt idx="216">
+                  <c:v>21.700000000000038</c:v>
+                </c:pt>
+                <c:pt idx="217">
+                  <c:v>21.80000000000004</c:v>
+                </c:pt>
+                <c:pt idx="218">
+                  <c:v>21.900000000000041</c:v>
+                </c:pt>
+                <c:pt idx="219">
+                  <c:v>22.000000000000043</c:v>
+                </c:pt>
+                <c:pt idx="220">
+                  <c:v>22.100000000000044</c:v>
+                </c:pt>
+                <c:pt idx="221">
+                  <c:v>22.200000000000045</c:v>
+                </c:pt>
+                <c:pt idx="222">
+                  <c:v>22.300000000000047</c:v>
+                </c:pt>
+                <c:pt idx="223">
+                  <c:v>22.400000000000048</c:v>
+                </c:pt>
+                <c:pt idx="224">
+                  <c:v>22.50000000000005</c:v>
+                </c:pt>
+                <c:pt idx="225">
+                  <c:v>22.600000000000051</c:v>
+                </c:pt>
+                <c:pt idx="226">
+                  <c:v>22.700000000000053</c:v>
+                </c:pt>
+                <c:pt idx="227">
+                  <c:v>22.800000000000054</c:v>
+                </c:pt>
+                <c:pt idx="228">
+                  <c:v>22.900000000000055</c:v>
+                </c:pt>
+                <c:pt idx="229">
+                  <c:v>23.000000000000057</c:v>
+                </c:pt>
+                <c:pt idx="230">
+                  <c:v>23.100000000000058</c:v>
+                </c:pt>
+                <c:pt idx="231">
+                  <c:v>23.20000000000006</c:v>
+                </c:pt>
+                <c:pt idx="232">
+                  <c:v>23.300000000000061</c:v>
+                </c:pt>
+                <c:pt idx="233">
+                  <c:v>23.400000000000063</c:v>
+                </c:pt>
+                <c:pt idx="234">
+                  <c:v>23.500000000000064</c:v>
+                </c:pt>
+                <c:pt idx="235">
+                  <c:v>23.600000000000065</c:v>
+                </c:pt>
+                <c:pt idx="236">
+                  <c:v>23.700000000000067</c:v>
+                </c:pt>
+                <c:pt idx="237">
+                  <c:v>23.800000000000068</c:v>
+                </c:pt>
+                <c:pt idx="238">
+                  <c:v>23.90000000000007</c:v>
+                </c:pt>
+                <c:pt idx="239">
+                  <c:v>24.000000000000071</c:v>
+                </c:pt>
+                <c:pt idx="240">
+                  <c:v>24.100000000000072</c:v>
+                </c:pt>
+                <c:pt idx="241">
+                  <c:v>24.200000000000074</c:v>
+                </c:pt>
+                <c:pt idx="242">
+                  <c:v>24.300000000000075</c:v>
+                </c:pt>
+                <c:pt idx="243">
+                  <c:v>24.400000000000077</c:v>
+                </c:pt>
+                <c:pt idx="244">
+                  <c:v>24.500000000000078</c:v>
+                </c:pt>
+                <c:pt idx="245">
+                  <c:v>24.60000000000008</c:v>
+                </c:pt>
+                <c:pt idx="246">
+                  <c:v>24.700000000000081</c:v>
+                </c:pt>
+                <c:pt idx="247">
+                  <c:v>24.800000000000082</c:v>
+                </c:pt>
+                <c:pt idx="248">
+                  <c:v>24.900000000000084</c:v>
+                </c:pt>
+                <c:pt idx="249">
+                  <c:v>25.000000000000085</c:v>
+                </c:pt>
+                <c:pt idx="250">
+                  <c:v>25.100000000000087</c:v>
+                </c:pt>
+                <c:pt idx="251">
+                  <c:v>25.200000000000088</c:v>
+                </c:pt>
+                <c:pt idx="252">
+                  <c:v>25.30000000000009</c:v>
+                </c:pt>
+                <c:pt idx="253">
+                  <c:v>25.400000000000091</c:v>
+                </c:pt>
+                <c:pt idx="254">
+                  <c:v>25.500000000000092</c:v>
+                </c:pt>
+                <c:pt idx="255">
+                  <c:v>25.600000000000094</c:v>
+                </c:pt>
+                <c:pt idx="256">
+                  <c:v>25.700000000000095</c:v>
+                </c:pt>
+                <c:pt idx="257">
+                  <c:v>25.800000000000097</c:v>
+                </c:pt>
+                <c:pt idx="258">
+                  <c:v>25.900000000000098</c:v>
+                </c:pt>
+                <c:pt idx="259">
+                  <c:v>26.000000000000099</c:v>
+                </c:pt>
+                <c:pt idx="260">
+                  <c:v>26.100000000000101</c:v>
+                </c:pt>
+                <c:pt idx="261">
+                  <c:v>26.200000000000102</c:v>
+                </c:pt>
+                <c:pt idx="262">
+                  <c:v>26.300000000000104</c:v>
+                </c:pt>
+                <c:pt idx="263">
+                  <c:v>26.400000000000105</c:v>
+                </c:pt>
+                <c:pt idx="264">
+                  <c:v>26.500000000000107</c:v>
+                </c:pt>
+                <c:pt idx="265">
+                  <c:v>26.600000000000108</c:v>
+                </c:pt>
+                <c:pt idx="266">
+                  <c:v>26.700000000000109</c:v>
+                </c:pt>
+                <c:pt idx="267">
+                  <c:v>26.800000000000111</c:v>
+                </c:pt>
+                <c:pt idx="268">
+                  <c:v>26.900000000000112</c:v>
+                </c:pt>
+                <c:pt idx="269">
+                  <c:v>27.000000000000114</c:v>
+                </c:pt>
+                <c:pt idx="270">
+                  <c:v>27.100000000000115</c:v>
+                </c:pt>
+                <c:pt idx="271">
+                  <c:v>27.200000000000117</c:v>
+                </c:pt>
+                <c:pt idx="272">
+                  <c:v>27.300000000000118</c:v>
+                </c:pt>
+                <c:pt idx="273">
+                  <c:v>27.400000000000119</c:v>
+                </c:pt>
+                <c:pt idx="274">
+                  <c:v>27.500000000000121</c:v>
+                </c:pt>
+                <c:pt idx="275">
+                  <c:v>27.600000000000122</c:v>
+                </c:pt>
+                <c:pt idx="276">
+                  <c:v>27.700000000000124</c:v>
+                </c:pt>
+                <c:pt idx="277">
+                  <c:v>27.800000000000125</c:v>
+                </c:pt>
+                <c:pt idx="278">
+                  <c:v>27.900000000000126</c:v>
+                </c:pt>
+                <c:pt idx="279">
+                  <c:v>28.000000000000128</c:v>
+                </c:pt>
+                <c:pt idx="280">
+                  <c:v>28.100000000000129</c:v>
+                </c:pt>
+                <c:pt idx="281">
+                  <c:v>28.200000000000131</c:v>
+                </c:pt>
+                <c:pt idx="282">
+                  <c:v>28.300000000000132</c:v>
+                </c:pt>
+                <c:pt idx="283">
+                  <c:v>28.400000000000134</c:v>
+                </c:pt>
+                <c:pt idx="284">
+                  <c:v>28.500000000000135</c:v>
+                </c:pt>
+                <c:pt idx="285">
+                  <c:v>28.600000000000136</c:v>
+                </c:pt>
+                <c:pt idx="286">
+                  <c:v>28.700000000000138</c:v>
+                </c:pt>
+                <c:pt idx="287">
+                  <c:v>28.800000000000139</c:v>
+                </c:pt>
+                <c:pt idx="288">
+                  <c:v>28.900000000000141</c:v>
+                </c:pt>
+                <c:pt idx="289">
+                  <c:v>29.000000000000142</c:v>
+                </c:pt>
+                <c:pt idx="290">
+                  <c:v>29.100000000000144</c:v>
+                </c:pt>
+                <c:pt idx="291">
+                  <c:v>29.200000000000145</c:v>
+                </c:pt>
+                <c:pt idx="292">
+                  <c:v>29.300000000000146</c:v>
+                </c:pt>
+                <c:pt idx="293">
+                  <c:v>29.400000000000148</c:v>
+                </c:pt>
+                <c:pt idx="294">
+                  <c:v>29.500000000000149</c:v>
+                </c:pt>
+                <c:pt idx="295">
+                  <c:v>29.600000000000151</c:v>
+                </c:pt>
+                <c:pt idx="296">
+                  <c:v>29.700000000000152</c:v>
+                </c:pt>
+                <c:pt idx="297">
+                  <c:v>29.800000000000153</c:v>
+                </c:pt>
+                <c:pt idx="298">
+                  <c:v>29.900000000000155</c:v>
+                </c:pt>
+                <c:pt idx="299">
+                  <c:v>30.000000000000156</c:v>
+                </c:pt>
+                <c:pt idx="300">
+                  <c:v>30.100000000000158</c:v>
+                </c:pt>
+                <c:pt idx="301">
+                  <c:v>30.200000000000159</c:v>
+                </c:pt>
+                <c:pt idx="302">
+                  <c:v>30.300000000000161</c:v>
+                </c:pt>
+                <c:pt idx="303">
+                  <c:v>30.400000000000162</c:v>
+                </c:pt>
+                <c:pt idx="304">
+                  <c:v>30.500000000000163</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Sheet1!$C$5:$C$309</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="305"/>
+                <c:pt idx="0">
+                  <c:v>1000000.0628318531</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>500000.25132741226</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>333333.89882001089</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>250001.00530964916</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>200001.57079632679</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>166668.92861337727</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>142860.22161794337</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>125004.02123859662</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>111116.20049120994</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>100006.2831853072</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>90916.693563312612</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>83342.381120175676</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>76933.695506246062</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>71440.886471773498</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>66680.803833607817</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>62516.084954386366</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>58841.687817302438</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>55575.913075950804</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>52654.261246327325</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>50025.132741228706</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>47646.756466252264</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>45484.956071432192</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>43511.498919840182</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>41702.857814036004</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>40039.269908169859</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>38504.012794214977</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>37082.841457926363</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>35763.545887093991</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>34535.600209123018</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>33389.88200109794</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>32318.44592693101</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>31314.339817545504</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>30371.454191025474</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>29484.398328033334</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>28648.39759144151</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>27859.207859358812</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>27113.043833882301</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>26406.518669519868</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>25736.592889547828</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>25100.530964914862</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>24495.864247452704</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>23920.359198342449</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>23371.990049818116</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>22848.915194819721</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>22349.456724692609</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>21872.082635882532</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>21415.39130811645</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>20978.097922810757</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>20559.022544531508</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>20157.079632679495</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>19771.26878709465</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>19400.666561475377</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>19044.419203580572</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>18701.736202075885</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>18371.884537360376</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>18054.183548376022</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>17748.000339753085</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>17452.74566407836</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>17167.870222915819</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>16892.861337725146</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>16627.239948230988</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>16370.557901272514</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>16122.395497857846</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>15882.359270182093</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>15650.079963843738</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>15425.21070349591</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>15207.425322767667</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>14996.416841545179</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>14791.896075663244</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>14593.590365766104</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>14401.242413588461</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>14214.609215213095</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>14033.461082005919</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>13857.580740934685</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>13686.762506862204</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>13520.811520184818</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>13359.543043875683</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>13202.781814601645</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>13050.361443122361</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>12902.123859659512</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>12757.918800349749</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>12617.603331274286</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>12481.041406895958</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>12348.103460036515</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>12218.666020796683</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>12092.611362063206</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>11969.827169463661</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>11850.206233824369</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>11733.646164361488</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>11620.049120992677</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>11509.321564298549</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>11401.374021791002</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>11296.120869260991</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>11193.480126082832</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>11093.37326344666</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>10995.725024576355</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>10900.463256068009</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>10807.518749554605</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>10716.82509296679</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>10628.318530717976</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>10541.937832195308</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>10457.624167986432</c:v>
+                </c:pt>
+                <c:pt idx="102">
+                  <c:v>10375.320993316369</c:v>
+                </c:pt>
+                <c:pt idx="103">
+                  <c:v>10294.973938209176</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>10216.53070392609</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>10139.940965265658</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>10065.156278342371</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>9992.1299934887029</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>9920.817172951527</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>9851.1745130778363</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>9783.1602707066231</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>9716.7341935040513</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>9651.8574539976707</c:v>
+                </c:pt>
+                <c:pt idx="113">
+                  <c:v>9588.4925870824791</c:v>
+                </c:pt>
+                <c:pt idx="114">
+                  <c:v>9526.6034307875598</c:v>
+                </c:pt>
+                <c:pt idx="115">
+                  <c:v>9466.1550701065153</c:v>
+                </c:pt>
+                <c:pt idx="116">
+                  <c:v>9407.1137837083752</c:v>
+                </c:pt>
+                <c:pt idx="117">
+                  <c:v>9349.4469933581404</c:v>
+                </c:pt>
+                <c:pt idx="118">
+                  <c:v>9293.1232158875318</c:v>
+                </c:pt>
+                <c:pt idx="119">
+                  <c:v>9238.1120175672077</c:v>
+                </c:pt>
+                <c:pt idx="120">
+                  <c:v>9184.3839707415318</c:v>
+                </c:pt>
+                <c:pt idx="121">
+                  <c:v>9131.9106125960334</c:v>
+                </c:pt>
+                <c:pt idx="122">
+                  <c:v>9080.6644059362225</c:v>
+                </c:pt>
+                <c:pt idx="123">
+                  <c:v>9030.6187018642049</c:v>
+                </c:pt>
+                <c:pt idx="124">
+                  <c:v>8981.7477042468236</c:v>
+                </c:pt>
+                <c:pt idx="125">
+                  <c:v>8934.0264358757813</c:v>
+                </c:pt>
+                <c:pt idx="126">
+                  <c:v>8887.4307062265052</c:v>
+                </c:pt>
+                <c:pt idx="127">
+                  <c:v>8841.9370807283158</c:v>
+                </c:pt>
+                <c:pt idx="128">
+                  <c:v>8797.5228514638929</c:v>
+                </c:pt>
+                <c:pt idx="129">
+                  <c:v>8754.166009221055</c:v>
+                </c:pt>
+                <c:pt idx="130">
+                  <c:v>8711.845216824644</c:v>
+                </c:pt>
+                <c:pt idx="131">
+                  <c:v>8670.5397836805587</c:v>
+                </c:pt>
+                <c:pt idx="132">
+                  <c:v>8630.2296414682132</c:v>
+                </c:pt>
+                <c:pt idx="133">
+                  <c:v>8590.8953209213578</c:v>
+                </c:pt>
+                <c:pt idx="134">
+                  <c:v>8552.5179296408987</c:v>
+                </c:pt>
+                <c:pt idx="135">
+                  <c:v>8515.0791308865373</c:v>
+                </c:pt>
+                <c:pt idx="136">
+                  <c:v>8478.5611232972497</c:v>
+                </c:pt>
+                <c:pt idx="137">
+                  <c:v>8442.9466214934946</c:v>
+                </c:pt>
+                <c:pt idx="138">
+                  <c:v>8408.2188375167261</c:v>
+                </c:pt>
+                <c:pt idx="139">
+                  <c:v>8374.3614630643533</c:v>
+                </c:pt>
+                <c:pt idx="140">
+                  <c:v>8341.3586524806688</c:v>
+                </c:pt>
+                <c:pt idx="141">
+                  <c:v>8309.1950064664634</c:v>
+                </c:pt>
+                <c:pt idx="142">
+                  <c:v>8277.8555564721573</c:v>
+                </c:pt>
+                <c:pt idx="143">
+                  <c:v>8247.3257497412142</c:v>
+                </c:pt>
+                <c:pt idx="144">
+                  <c:v>8217.5914349724499</c:v>
+                </c:pt>
+                <c:pt idx="145">
+                  <c:v>8188.6388485715615</c:v>
+                </c:pt>
+                <c:pt idx="146">
+                  <c:v>8160.4546014638208</c:v>
+                </c:pt>
+                <c:pt idx="147">
+                  <c:v>8133.0256664413828</c:v>
+                </c:pt>
+                <c:pt idx="148">
+                  <c:v>8106.3393660201036</c:v>
+                </c:pt>
+                <c:pt idx="149">
+                  <c:v>8080.3833607820834</c:v>
+                </c:pt>
+                <c:pt idx="150">
+                  <c:v>8055.1456381814169</c:v>
+                </c:pt>
+                <c:pt idx="151">
+                  <c:v>8030.6145017918334</c:v>
+                </c:pt>
+                <c:pt idx="152">
+                  <c:v>8006.7785609759785</c:v>
+                </c:pt>
+                <c:pt idx="153">
+                  <c:v>7983.6267209572134</c:v>
+                </c:pt>
+                <c:pt idx="154">
+                  <c:v>7961.1481732757102</c:v>
+                </c:pt>
+                <c:pt idx="155">
+                  <c:v>7939.3323866116425</c:v>
+                </c:pt>
+                <c:pt idx="156">
+                  <c:v>7918.1690979590612</c:v>
+                </c:pt>
+                <c:pt idx="157">
+                  <c:v>7897.6483041349529</c:v>
+                </c:pt>
+                <c:pt idx="158">
+                  <c:v>7877.7602536087088</c:v>
+                </c:pt>
+                <c:pt idx="159">
+                  <c:v>7858.4954386379823</c:v>
+                </c:pt>
+                <c:pt idx="160">
+                  <c:v>7839.8445876976311</c:v>
+                </c:pt>
+                <c:pt idx="161">
+                  <c:v>7821.7986581890564</c:v>
+                </c:pt>
+                <c:pt idx="162">
+                  <c:v>7804.3488294179251</c:v>
+                </c:pt>
+                <c:pt idx="163">
+                  <c:v>7787.4864958287835</c:v>
+                </c:pt>
+                <c:pt idx="164">
+                  <c:v>7771.2032604857086</c:v>
+                </c:pt>
+                <c:pt idx="165">
+                  <c:v>7755.4909287885812</c:v>
+                </c:pt>
+                <c:pt idx="166">
+                  <c:v>7740.3415024151282</c:v>
+                </c:pt>
+                <c:pt idx="167">
+                  <c:v>7725.7471734793235</c:v>
+                </c:pt>
+                <c:pt idx="168">
+                  <c:v>7711.7003188971748</c:v>
+                </c:pt>
+                <c:pt idx="169">
+                  <c:v>7698.1934949513743</c:v>
+                </c:pt>
+                <c:pt idx="170">
+                  <c:v>7685.2194320466551</c:v>
+                </c:pt>
+                <c:pt idx="171">
+                  <c:v>7672.7710296481055</c:v>
+                </c:pt>
+                <c:pt idx="172">
+                  <c:v>7660.8413513950291</c:v>
+                </c:pt>
+                <c:pt idx="173">
+                  <c:v>7649.4236203833034</c:v>
+                </c:pt>
+                <c:pt idx="174">
+                  <c:v>7638.5112146094652</c:v>
+                </c:pt>
+                <c:pt idx="175">
+                  <c:v>7628.0976625701323</c:v>
+                </c:pt>
+                <c:pt idx="176">
+                  <c:v>7618.1766390105877</c:v>
+                </c:pt>
+                <c:pt idx="177">
+                  <c:v>7608.7419608166692</c:v>
+                </c:pt>
+                <c:pt idx="178">
+                  <c:v>7599.7875830443627</c:v>
+                </c:pt>
+                <c:pt idx="179">
+                  <c:v>7591.3075950817429</c:v>
+                </c:pt>
+                <c:pt idx="180">
+                  <c:v>7583.2962169381444</c:v>
+                </c:pt>
+                <c:pt idx="181">
+                  <c:v>7575.7477956556613</c:v>
+                </c:pt>
+                <c:pt idx="182">
+                  <c:v>7568.6568018383132</c:v>
+                </c:pt>
+                <c:pt idx="183">
+                  <c:v>7562.0178262943737</c:v>
+                </c:pt>
+                <c:pt idx="184">
+                  <c:v>7555.8255767876199</c:v>
+                </c:pt>
+                <c:pt idx="185">
+                  <c:v>7550.0748748933547</c:v>
+                </c:pt>
+                <c:pt idx="186">
+                  <c:v>7544.7606529553304</c:v>
+                </c:pt>
+                <c:pt idx="187">
+                  <c:v>7539.8779511397661</c:v>
+                </c:pt>
+                <c:pt idx="188">
+                  <c:v>7535.421914582912</c:v>
+                </c:pt>
+                <c:pt idx="189">
+                  <c:v>7531.3877906286725</c:v>
+                </c:pt>
+                <c:pt idx="190">
+                  <c:v>7527.7709261530235</c:v>
+                </c:pt>
+                <c:pt idx="191">
+                  <c:v>7524.5667649720153</c:v>
+                </c:pt>
+                <c:pt idx="192">
+                  <c:v>7521.7708453303912</c:v>
+                </c:pt>
+                <c:pt idx="193">
+                  <c:v>7519.3787974678407</c:v>
+                </c:pt>
+                <c:pt idx="194">
+                  <c:v>7517.3863412601659</c:v>
+                </c:pt>
+                <c:pt idx="195">
+                  <c:v>7515.7892839326396</c:v>
+                </c:pt>
+                <c:pt idx="196">
+                  <c:v>7514.5835178430207</c:v>
+                </c:pt>
+                <c:pt idx="197">
+                  <c:v>7513.7650183317355</c:v>
+                </c:pt>
+                <c:pt idx="198">
+                  <c:v>7513.3298416368916</c:v>
+                </c:pt>
+                <c:pt idx="199">
+                  <c:v>7513.2741228718351</c:v>
+                </c:pt>
+                <c:pt idx="200">
+                  <c:v>7513.5940740630776</c:v>
+                </c:pt>
+                <c:pt idx="201">
+                  <c:v>7514.2859822465089</c:v>
+                </c:pt>
+                <c:pt idx="202">
+                  <c:v>7515.3462076198721</c:v>
+                </c:pt>
+                <c:pt idx="203">
+                  <c:v>7516.7711817495829</c:v>
+                </c:pt>
+                <c:pt idx="204">
+                  <c:v>7518.5574058300263</c:v>
+                </c:pt>
+                <c:pt idx="205">
+                  <c:v>7520.7014489935646</c:v>
+                </c:pt>
+                <c:pt idx="206">
+                  <c:v>7523.1999466695161</c:v>
+                </c:pt>
+                <c:pt idx="207">
+                  <c:v>7526.0495989904848</c:v>
+                </c:pt>
+                <c:pt idx="208">
+                  <c:v>7529.2471692444269</c:v>
+                </c:pt>
+                <c:pt idx="209">
+                  <c:v>7532.7894823709603</c:v>
+                </c:pt>
+                <c:pt idx="210">
+                  <c:v>7536.6734235004205</c:v>
+                </c:pt>
+                <c:pt idx="211">
+                  <c:v>7540.8959365342653</c:v>
+                </c:pt>
+                <c:pt idx="212">
+                  <c:v>7545.4540227654816</c:v>
+                </c:pt>
+                <c:pt idx="213">
+                  <c:v>7550.3447395376479</c:v>
+                </c:pt>
+                <c:pt idx="214">
+                  <c:v>7555.56519894144</c:v>
+                </c:pt>
+                <c:pt idx="215">
+                  <c:v>7561.1125665473392</c:v>
+                </c:pt>
+                <c:pt idx="216">
+                  <c:v>7566.984060173374</c:v>
+                </c:pt>
+                <c:pt idx="217">
+                  <c:v>7573.1769486867815</c:v>
+                </c:pt>
+                <c:pt idx="218">
+                  <c:v>7579.6885508385049</c:v>
+                </c:pt>
+                <c:pt idx="219">
+                  <c:v>7586.516234129469</c:v>
+                </c:pt>
+                <c:pt idx="220">
+                  <c:v>7593.6574137076395</c:v>
+                </c:pt>
+                <c:pt idx="221">
+                  <c:v>7601.1095512948959</c:v>
+                </c:pt>
+                <c:pt idx="222">
+                  <c:v>7608.8701541427654</c:v>
+                </c:pt>
+                <c:pt idx="223">
+                  <c:v>7616.936774016147</c:v>
+                </c:pt>
+                <c:pt idx="224">
+                  <c:v>7625.3070062041133</c:v>
+                </c:pt>
+                <c:pt idx="225">
+                  <c:v>7633.978488556997</c:v>
+                </c:pt>
+                <c:pt idx="226">
+                  <c:v>7642.9489005489086</c:v>
+                </c:pt>
+                <c:pt idx="227">
+                  <c:v>7652.2159623649422</c:v>
+                </c:pt>
+                <c:pt idx="228">
+                  <c:v>7661.7774340122887</c:v>
+                </c:pt>
+                <c:pt idx="229">
+                  <c:v>7671.6311144545289</c:v>
+                </c:pt>
+                <c:pt idx="230">
+                  <c:v>7681.7748407684339</c:v>
+                </c:pt>
+                <c:pt idx="231">
+                  <c:v>7692.2064873225536</c:v>
+                </c:pt>
+                <c:pt idx="232">
+                  <c:v>7702.9239649769643</c:v>
+                </c:pt>
+                <c:pt idx="233">
+                  <c:v>7713.9252203035348</c:v>
+                </c:pt>
+                <c:pt idx="234">
+                  <c:v>7725.2082348261038</c:v>
+                </c:pt>
+                <c:pt idx="235">
+                  <c:v>7736.7710242799703</c:v>
+                </c:pt>
+                <c:pt idx="236">
+                  <c:v>7748.6116378901315</c:v>
+                </c:pt>
+                <c:pt idx="237">
+                  <c:v>7760.7281576677206</c:v>
+                </c:pt>
+                <c:pt idx="238">
+                  <c:v>7773.1186977241014</c:v>
+                </c:pt>
+                <c:pt idx="239">
+                  <c:v>7785.7814036021173</c:v>
+                </c:pt>
+                <c:pt idx="240">
+                  <c:v>7798.7144516239805</c:v>
+                </c:pt>
+                <c:pt idx="241">
+                  <c:v>7811.9160482553407</c:v>
+                </c:pt>
+                <c:pt idx="242">
+                  <c:v>7825.3844294850433</c:v>
+                </c:pt>
+                <c:pt idx="243">
+                  <c:v>7839.1178602201544</c:v>
+                </c:pt>
+                <c:pt idx="244">
+                  <c:v>7853.1146336957827</c:v>
+                </c:pt>
+                <c:pt idx="245">
+                  <c:v>7867.3730708993135</c:v>
+                </c:pt>
+                <c:pt idx="246">
+                  <c:v>7881.891520008623</c:v>
+                </c:pt>
+                <c:pt idx="247">
+                  <c:v>7896.6683558438745</c:v>
+                </c:pt>
+                <c:pt idx="248">
+                  <c:v>7911.7019793325398</c:v>
+                </c:pt>
+                <c:pt idx="249">
+                  <c:v>7926.9908169872542</c:v>
+                </c:pt>
+                <c:pt idx="250">
+                  <c:v>7942.5333203961445</c:v>
+                </c:pt>
+                <c:pt idx="251">
+                  <c:v>7958.3279657253061</c:v>
+                </c:pt>
+                <c:pt idx="252">
+                  <c:v>7974.3732532330705</c:v>
+                </c:pt>
+                <c:pt idx="253">
+                  <c:v>7990.6677067957453</c:v>
+                </c:pt>
+                <c:pt idx="254">
+                  <c:v>8007.2098734445217</c:v>
+                </c:pt>
+                <c:pt idx="255">
+                  <c:v>8023.9983229132304</c:v>
+                </c:pt>
+                <c:pt idx="256">
+                  <c:v>8041.0316471966489</c:v>
+                </c:pt>
+                <c:pt idx="257">
+                  <c:v>8058.3084601190985</c:v>
+                </c:pt>
+                <c:pt idx="258">
+                  <c:v>8075.8273969130169</c:v>
+                </c:pt>
+                <c:pt idx="259">
+                  <c:v>8093.5871138072653</c:v>
+                </c:pt>
+                <c:pt idx="260">
+                  <c:v>8111.5862876248975</c:v>
+                </c:pt>
+                <c:pt idx="261">
+                  <c:v>8129.8236153901453</c:v>
+                </c:pt>
+                <c:pt idx="262">
+                  <c:v>8148.2978139443603</c:v>
+                </c:pt>
+                <c:pt idx="263">
+                  <c:v>8167.0076195706934</c:v>
+                </c:pt>
+                <c:pt idx="264">
+                  <c:v>8185.9517876272621</c:v>
+                </c:pt>
+                <c:pt idx="265">
+                  <c:v>8205.1290921886102</c:v>
+                </c:pt>
+                <c:pt idx="266">
+                  <c:v>8224.5383256952009</c:v>
+                </c:pt>
+                <c:pt idx="267">
+                  <c:v>8244.1782986107773</c:v>
+                </c:pt>
+                <c:pt idx="268">
+                  <c:v>8264.0478390873504</c:v>
+                </c:pt>
+                <c:pt idx="269">
+                  <c:v>8284.1457926376461</c:v>
+                </c:pt>
+                <c:pt idx="270">
+                  <c:v>8304.4710218147866</c:v>
+                </c:pt>
+                <c:pt idx="271">
+                  <c:v>8325.0224058990625</c:v>
+                </c:pt>
+                <c:pt idx="272">
+                  <c:v>8345.7988405915621</c:v>
+                </c:pt>
+                <c:pt idx="273">
+                  <c:v>8366.799237714522</c:v>
+                </c:pt>
+                <c:pt idx="274">
+                  <c:v>8388.022524918224</c:v>
+                </c:pt>
+                <c:pt idx="275">
+                  <c:v>8409.4676453942484</c:v>
+                </c:pt>
+                <c:pt idx="276">
+                  <c:v>8431.1335575949488</c:v>
+                </c:pt>
+                <c:pt idx="277">
+                  <c:v>8453.0192349589724</c:v>
+                </c:pt>
+                <c:pt idx="278">
+                  <c:v>8475.1236656426918</c:v>
+                </c:pt>
+                <c:pt idx="279">
+                  <c:v>8497.445852257395</c:v>
+                </c:pt>
+                <c:pt idx="280">
+                  <c:v>8519.9848116120666</c:v>
+                </c:pt>
+                <c:pt idx="281">
+                  <c:v>8542.7395744616661</c:v>
+                </c:pt>
+                <c:pt idx="282">
+                  <c:v>8565.70918526073</c:v>
+                </c:pt>
+                <c:pt idx="283">
+                  <c:v>8588.8927019221774</c:v>
+                </c:pt>
+                <c:pt idx="284">
+                  <c:v>8612.289195581212</c:v>
+                </c:pt>
+                <c:pt idx="285">
+                  <c:v>8635.8977503641436</c:v>
+                </c:pt>
+                <c:pt idx="286">
+                  <c:v>8659.7174631620765</c:v>
+                </c:pt>
+                <c:pt idx="287">
+                  <c:v>8683.747443409291</c:v>
+                </c:pt>
+                <c:pt idx="288">
+                  <c:v>8707.9868128662438</c:v>
+                </c:pt>
+                <c:pt idx="289">
+                  <c:v>8732.4347054070331</c:v>
+                </c:pt>
+                <c:pt idx="290">
+                  <c:v>8757.0902668112685</c:v>
+                </c:pt>
+                <c:pt idx="291">
+                  <c:v>8781.9526545602148</c:v>
+                </c:pt>
+                <c:pt idx="292">
+                  <c:v>8807.0210376370906</c:v>
+                </c:pt>
+                <c:pt idx="293">
+                  <c:v>8832.2945963314723</c:v>
+                </c:pt>
+                <c:pt idx="294">
+                  <c:v>8857.7725220476495</c:v>
+                </c:pt>
+                <c:pt idx="295">
+                  <c:v>8883.4540171168846</c:v>
+                </c:pt>
+                <c:pt idx="296">
+                  <c:v>8909.3382946134479</c:v>
+                </c:pt>
+                <c:pt idx="297">
+                  <c:v>8935.4245781743775</c:v>
+                </c:pt>
+                <c:pt idx="298">
+                  <c:v>8961.7121018228336</c:v>
+                </c:pt>
+                <c:pt idx="299">
+                  <c:v>8988.2001097950015</c:v>
+                </c:pt>
+                <c:pt idx="300">
+                  <c:v>9014.8878563704438</c:v>
+                </c:pt>
+                <c:pt idx="301">
+                  <c:v>9041.7746057058084</c:v>
+                </c:pt>
+                <c:pt idx="302">
+                  <c:v>9068.8596316718504</c:v>
+                </c:pt>
+                <c:pt idx="303">
+                  <c:v>9096.1422176936576</c:v>
+                </c:pt>
+                <c:pt idx="304">
+                  <c:v>9123.6216565940194</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-06DA-4758-8272-195AE8D909F6}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="1462445376"/>
+        <c:axId val="1462445856"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="1462445376"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ja-JP"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1462445856"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1462445856"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="10000"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ja-JP"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1462445376"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="ja-JP"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>446226</xdr:colOff>
+      <xdr:row>290</xdr:row>
+      <xdr:rowOff>51765</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>215969</xdr:colOff>
+      <xdr:row>301</xdr:row>
+      <xdr:rowOff>177661</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="グラフ 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2C6AFFE5-582C-EAB3-8892-36E97CFCB620}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2635,7 +5345,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C7A3EDD-6597-4754-A609-A225833ECC81}">
-  <dimension ref="A2:D114"/>
+  <dimension ref="A2:H122"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="2" spans="1:4">
@@ -3748,7 +6458,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:3">
+    <row r="97" spans="1:8">
       <c r="A97">
         <v>103</v>
       </c>
@@ -3759,7 +6469,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:3">
+    <row r="98" spans="1:8">
       <c r="A98">
         <v>104</v>
       </c>
@@ -3770,7 +6480,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:3">
+    <row r="99" spans="1:8">
       <c r="A99">
         <v>105</v>
       </c>
@@ -3781,7 +6491,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="100" spans="1:3">
+    <row r="100" spans="1:8">
       <c r="A100">
         <v>106</v>
       </c>
@@ -3792,7 +6502,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="101" spans="1:3">
+    <row r="101" spans="1:8">
       <c r="A101">
         <v>107</v>
       </c>
@@ -3803,7 +6513,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="102" spans="1:3">
+    <row r="102" spans="1:8">
       <c r="A102">
         <v>108</v>
       </c>
@@ -3814,7 +6524,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="103" spans="1:3">
+    <row r="103" spans="1:8">
       <c r="A103">
         <v>109</v>
       </c>
@@ -3825,7 +6535,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:3">
+    <row r="104" spans="1:8">
       <c r="A104">
         <v>110</v>
       </c>
@@ -3836,7 +6546,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="105" spans="1:3">
+    <row r="105" spans="1:8">
       <c r="A105">
         <f>A104+1</f>
         <v>111</v>
@@ -3848,7 +6558,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:3">
+    <row r="106" spans="1:8">
       <c r="A106">
         <f t="shared" ref="A106:A114" si="4">A105+1</f>
         <v>112</v>
@@ -3860,7 +6570,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="107" spans="1:3">
+    <row r="107" spans="1:8">
       <c r="A107">
         <f t="shared" si="4"/>
         <v>113</v>
@@ -3872,7 +6582,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="108" spans="1:3">
+    <row r="108" spans="1:8">
       <c r="A108">
         <f t="shared" si="4"/>
         <v>114</v>
@@ -3884,7 +6594,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="109" spans="1:3">
+    <row r="109" spans="1:8">
       <c r="A109">
         <f t="shared" si="4"/>
         <v>115</v>
@@ -3895,8 +6605,12 @@
       <c r="C109">
         <v>0</v>
       </c>
-    </row>
-    <row r="110" spans="1:3">
+      <c r="H109">
+        <f>10*(50/PI())^(1/3)</f>
+        <v>25.153979958021793</v>
+      </c>
+    </row>
+    <row r="110" spans="1:8">
       <c r="A110">
         <f t="shared" si="4"/>
         <v>116</v>
@@ -3908,7 +6622,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:3">
+    <row r="111" spans="1:8">
       <c r="A111">
         <f t="shared" si="4"/>
         <v>117</v>
@@ -3920,7 +6634,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:3">
+    <row r="112" spans="1:8">
       <c r="A112">
         <f t="shared" si="4"/>
         <v>118</v>
@@ -3953,6 +6667,94 @@
         <v>10</v>
       </c>
       <c r="C114">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3">
+      <c r="A115">
+        <v>102</v>
+      </c>
+      <c r="B115" t="s">
+        <v>9</v>
+      </c>
+      <c r="C115">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3">
+      <c r="A116">
+        <v>103</v>
+      </c>
+      <c r="B116" t="s">
+        <v>11</v>
+      </c>
+      <c r="C116">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3">
+      <c r="A117">
+        <v>104</v>
+      </c>
+      <c r="B117" t="s">
+        <v>9</v>
+      </c>
+      <c r="C117">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3">
+      <c r="A118">
+        <v>109</v>
+      </c>
+      <c r="B118" t="s">
+        <v>9</v>
+      </c>
+      <c r="C118">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3">
+      <c r="A119">
+        <v>111</v>
+      </c>
+      <c r="B119" t="s">
+        <v>8</v>
+      </c>
+      <c r="C119">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3">
+      <c r="A120">
+        <v>115</v>
+      </c>
+      <c r="B120" t="s">
+        <v>9</v>
+      </c>
+      <c r="C120">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3">
+      <c r="A121">
+        <v>116</v>
+      </c>
+      <c r="B121" t="s">
+        <v>10</v>
+      </c>
+      <c r="C121">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3">
+      <c r="A122">
+        <v>117</v>
+      </c>
+      <c r="B122" t="s">
+        <v>11</v>
+      </c>
+      <c r="C122">
         <v>1</v>
       </c>
     </row>
@@ -3965,4 +6767,3080 @@
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FEFFE552-009D-4D4B-934A-7747BFA9A308}">
+  <dimension ref="B3:C309"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetData>
+    <row r="3" spans="2:3">
+      <c r="B3" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="4" spans="2:3">
+      <c r="B4">
+        <v>0</v>
+      </c>
+      <c r="C4" t="e">
+        <f>2*PI()*B4^2+10000/B4</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="5" spans="2:3">
+      <c r="B5">
+        <f>B4+0.1</f>
+        <v>0.1</v>
+      </c>
+      <c r="C5">
+        <f>2*PI()*B5^2+100000/B5</f>
+        <v>1000000.0628318531</v>
+      </c>
+    </row>
+    <row r="6" spans="2:3">
+      <c r="B6">
+        <f t="shared" ref="B6:B69" si="0">B5+0.1</f>
+        <v>0.2</v>
+      </c>
+      <c r="C6">
+        <f t="shared" ref="C6:C69" si="1">2*PI()*B6^2+100000/B6</f>
+        <v>500000.25132741226</v>
+      </c>
+    </row>
+    <row r="7" spans="2:3">
+      <c r="B7">
+        <f t="shared" si="0"/>
+        <v>0.30000000000000004</v>
+      </c>
+      <c r="C7">
+        <f t="shared" si="1"/>
+        <v>333333.89882001089</v>
+      </c>
+    </row>
+    <row r="8" spans="2:3">
+      <c r="B8">
+        <f t="shared" si="0"/>
+        <v>0.4</v>
+      </c>
+      <c r="C8">
+        <f t="shared" si="1"/>
+        <v>250001.00530964916</v>
+      </c>
+    </row>
+    <row r="9" spans="2:3">
+      <c r="B9">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+      <c r="C9">
+        <f t="shared" si="1"/>
+        <v>200001.57079632679</v>
+      </c>
+    </row>
+    <row r="10" spans="2:3">
+      <c r="B10">
+        <f t="shared" si="0"/>
+        <v>0.6</v>
+      </c>
+      <c r="C10">
+        <f t="shared" si="1"/>
+        <v>166668.92861337727</v>
+      </c>
+    </row>
+    <row r="11" spans="2:3">
+      <c r="B11">
+        <f t="shared" si="0"/>
+        <v>0.7</v>
+      </c>
+      <c r="C11">
+        <f t="shared" si="1"/>
+        <v>142860.22161794337</v>
+      </c>
+    </row>
+    <row r="12" spans="2:3">
+      <c r="B12">
+        <f t="shared" si="0"/>
+        <v>0.79999999999999993</v>
+      </c>
+      <c r="C12">
+        <f t="shared" si="1"/>
+        <v>125004.02123859662</v>
+      </c>
+    </row>
+    <row r="13" spans="2:3">
+      <c r="B13">
+        <f t="shared" si="0"/>
+        <v>0.89999999999999991</v>
+      </c>
+      <c r="C13">
+        <f t="shared" si="1"/>
+        <v>111116.20049120994</v>
+      </c>
+    </row>
+    <row r="14" spans="2:3">
+      <c r="B14">
+        <f t="shared" si="0"/>
+        <v>0.99999999999999989</v>
+      </c>
+      <c r="C14">
+        <f t="shared" si="1"/>
+        <v>100006.2831853072</v>
+      </c>
+    </row>
+    <row r="15" spans="2:3">
+      <c r="B15">
+        <f t="shared" si="0"/>
+        <v>1.0999999999999999</v>
+      </c>
+      <c r="C15">
+        <f t="shared" si="1"/>
+        <v>90916.693563312612</v>
+      </c>
+    </row>
+    <row r="16" spans="2:3">
+      <c r="B16">
+        <f t="shared" si="0"/>
+        <v>1.2</v>
+      </c>
+      <c r="C16">
+        <f t="shared" si="1"/>
+        <v>83342.381120175676</v>
+      </c>
+    </row>
+    <row r="17" spans="2:3">
+      <c r="B17">
+        <f t="shared" si="0"/>
+        <v>1.3</v>
+      </c>
+      <c r="C17">
+        <f t="shared" si="1"/>
+        <v>76933.695506246062</v>
+      </c>
+    </row>
+    <row r="18" spans="2:3">
+      <c r="B18">
+        <f t="shared" si="0"/>
+        <v>1.4000000000000001</v>
+      </c>
+      <c r="C18">
+        <f t="shared" si="1"/>
+        <v>71440.886471773498</v>
+      </c>
+    </row>
+    <row r="19" spans="2:3">
+      <c r="B19">
+        <f t="shared" si="0"/>
+        <v>1.5000000000000002</v>
+      </c>
+      <c r="C19">
+        <f t="shared" si="1"/>
+        <v>66680.803833607817</v>
+      </c>
+    </row>
+    <row r="20" spans="2:3">
+      <c r="B20">
+        <f t="shared" si="0"/>
+        <v>1.6000000000000003</v>
+      </c>
+      <c r="C20">
+        <f t="shared" si="1"/>
+        <v>62516.084954386366</v>
+      </c>
+    </row>
+    <row r="21" spans="2:3">
+      <c r="B21">
+        <f t="shared" si="0"/>
+        <v>1.7000000000000004</v>
+      </c>
+      <c r="C21">
+        <f t="shared" si="1"/>
+        <v>58841.687817302438</v>
+      </c>
+    </row>
+    <row r="22" spans="2:3">
+      <c r="B22">
+        <f t="shared" si="0"/>
+        <v>1.8000000000000005</v>
+      </c>
+      <c r="C22">
+        <f t="shared" si="1"/>
+        <v>55575.913075950804</v>
+      </c>
+    </row>
+    <row r="23" spans="2:3">
+      <c r="B23">
+        <f t="shared" si="0"/>
+        <v>1.9000000000000006</v>
+      </c>
+      <c r="C23">
+        <f t="shared" si="1"/>
+        <v>52654.261246327325</v>
+      </c>
+    </row>
+    <row r="24" spans="2:3">
+      <c r="B24">
+        <f t="shared" si="0"/>
+        <v>2.0000000000000004</v>
+      </c>
+      <c r="C24">
+        <f t="shared" si="1"/>
+        <v>50025.132741228706</v>
+      </c>
+    </row>
+    <row r="25" spans="2:3">
+      <c r="B25">
+        <f t="shared" si="0"/>
+        <v>2.1000000000000005</v>
+      </c>
+      <c r="C25">
+        <f t="shared" si="1"/>
+        <v>47646.756466252264</v>
+      </c>
+    </row>
+    <row r="26" spans="2:3">
+      <c r="B26">
+        <f t="shared" si="0"/>
+        <v>2.2000000000000006</v>
+      </c>
+      <c r="C26">
+        <f t="shared" si="1"/>
+        <v>45484.956071432192</v>
+      </c>
+    </row>
+    <row r="27" spans="2:3">
+      <c r="B27">
+        <f t="shared" si="0"/>
+        <v>2.3000000000000007</v>
+      </c>
+      <c r="C27">
+        <f t="shared" si="1"/>
+        <v>43511.498919840182</v>
+      </c>
+    </row>
+    <row r="28" spans="2:3">
+      <c r="B28">
+        <f t="shared" si="0"/>
+        <v>2.4000000000000008</v>
+      </c>
+      <c r="C28">
+        <f t="shared" si="1"/>
+        <v>41702.857814036004</v>
+      </c>
+    </row>
+    <row r="29" spans="2:3">
+      <c r="B29">
+        <f t="shared" si="0"/>
+        <v>2.5000000000000009</v>
+      </c>
+      <c r="C29">
+        <f t="shared" si="1"/>
+        <v>40039.269908169859</v>
+      </c>
+    </row>
+    <row r="30" spans="2:3">
+      <c r="B30">
+        <f t="shared" si="0"/>
+        <v>2.600000000000001</v>
+      </c>
+      <c r="C30">
+        <f t="shared" si="1"/>
+        <v>38504.012794214977</v>
+      </c>
+    </row>
+    <row r="31" spans="2:3">
+      <c r="B31">
+        <f t="shared" si="0"/>
+        <v>2.7000000000000011</v>
+      </c>
+      <c r="C31">
+        <f t="shared" si="1"/>
+        <v>37082.841457926363</v>
+      </c>
+    </row>
+    <row r="32" spans="2:3">
+      <c r="B32">
+        <f t="shared" si="0"/>
+        <v>2.8000000000000012</v>
+      </c>
+      <c r="C32">
+        <f t="shared" si="1"/>
+        <v>35763.545887093991</v>
+      </c>
+    </row>
+    <row r="33" spans="2:3">
+      <c r="B33">
+        <f t="shared" si="0"/>
+        <v>2.9000000000000012</v>
+      </c>
+      <c r="C33">
+        <f t="shared" si="1"/>
+        <v>34535.600209123018</v>
+      </c>
+    </row>
+    <row r="34" spans="2:3">
+      <c r="B34">
+        <f t="shared" si="0"/>
+        <v>3.0000000000000013</v>
+      </c>
+      <c r="C34">
+        <f t="shared" si="1"/>
+        <v>33389.88200109794</v>
+      </c>
+    </row>
+    <row r="35" spans="2:3">
+      <c r="B35">
+        <f t="shared" si="0"/>
+        <v>3.1000000000000014</v>
+      </c>
+      <c r="C35">
+        <f t="shared" si="1"/>
+        <v>32318.44592693101</v>
+      </c>
+    </row>
+    <row r="36" spans="2:3">
+      <c r="B36">
+        <f t="shared" si="0"/>
+        <v>3.2000000000000015</v>
+      </c>
+      <c r="C36">
+        <f t="shared" si="1"/>
+        <v>31314.339817545504</v>
+      </c>
+    </row>
+    <row r="37" spans="2:3">
+      <c r="B37">
+        <f t="shared" si="0"/>
+        <v>3.3000000000000016</v>
+      </c>
+      <c r="C37">
+        <f t="shared" si="1"/>
+        <v>30371.454191025474</v>
+      </c>
+    </row>
+    <row r="38" spans="2:3">
+      <c r="B38">
+        <f t="shared" si="0"/>
+        <v>3.4000000000000017</v>
+      </c>
+      <c r="C38">
+        <f t="shared" si="1"/>
+        <v>29484.398328033334</v>
+      </c>
+    </row>
+    <row r="39" spans="2:3">
+      <c r="B39">
+        <f t="shared" si="0"/>
+        <v>3.5000000000000018</v>
+      </c>
+      <c r="C39">
+        <f t="shared" si="1"/>
+        <v>28648.39759144151</v>
+      </c>
+    </row>
+    <row r="40" spans="2:3">
+      <c r="B40">
+        <f t="shared" si="0"/>
+        <v>3.6000000000000019</v>
+      </c>
+      <c r="C40">
+        <f t="shared" si="1"/>
+        <v>27859.207859358812</v>
+      </c>
+    </row>
+    <row r="41" spans="2:3">
+      <c r="B41">
+        <f t="shared" si="0"/>
+        <v>3.700000000000002</v>
+      </c>
+      <c r="C41">
+        <f t="shared" si="1"/>
+        <v>27113.043833882301</v>
+      </c>
+    </row>
+    <row r="42" spans="2:3">
+      <c r="B42">
+        <f t="shared" si="0"/>
+        <v>3.800000000000002</v>
+      </c>
+      <c r="C42">
+        <f t="shared" si="1"/>
+        <v>26406.518669519868</v>
+      </c>
+    </row>
+    <row r="43" spans="2:3">
+      <c r="B43">
+        <f t="shared" si="0"/>
+        <v>3.9000000000000021</v>
+      </c>
+      <c r="C43">
+        <f t="shared" si="1"/>
+        <v>25736.592889547828</v>
+      </c>
+    </row>
+    <row r="44" spans="2:3">
+      <c r="B44">
+        <f t="shared" si="0"/>
+        <v>4.0000000000000018</v>
+      </c>
+      <c r="C44">
+        <f t="shared" si="1"/>
+        <v>25100.530964914862</v>
+      </c>
+    </row>
+    <row r="45" spans="2:3">
+      <c r="B45">
+        <f t="shared" si="0"/>
+        <v>4.1000000000000014</v>
+      </c>
+      <c r="C45">
+        <f t="shared" si="1"/>
+        <v>24495.864247452704</v>
+      </c>
+    </row>
+    <row r="46" spans="2:3">
+      <c r="B46">
+        <f t="shared" si="0"/>
+        <v>4.2000000000000011</v>
+      </c>
+      <c r="C46">
+        <f t="shared" si="1"/>
+        <v>23920.359198342449</v>
+      </c>
+    </row>
+    <row r="47" spans="2:3">
+      <c r="B47">
+        <f t="shared" si="0"/>
+        <v>4.3000000000000007</v>
+      </c>
+      <c r="C47">
+        <f t="shared" si="1"/>
+        <v>23371.990049818116</v>
+      </c>
+    </row>
+    <row r="48" spans="2:3">
+      <c r="B48">
+        <f t="shared" si="0"/>
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="C48">
+        <f t="shared" si="1"/>
+        <v>22848.915194819721</v>
+      </c>
+    </row>
+    <row r="49" spans="2:3">
+      <c r="B49">
+        <f t="shared" si="0"/>
+        <v>4.5</v>
+      </c>
+      <c r="C49">
+        <f t="shared" si="1"/>
+        <v>22349.456724692609</v>
+      </c>
+    </row>
+    <row r="50" spans="2:3">
+      <c r="B50">
+        <f t="shared" si="0"/>
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="C50">
+        <f t="shared" si="1"/>
+        <v>21872.082635882532</v>
+      </c>
+    </row>
+    <row r="51" spans="2:3">
+      <c r="B51">
+        <f t="shared" si="0"/>
+        <v>4.6999999999999993</v>
+      </c>
+      <c r="C51">
+        <f t="shared" si="1"/>
+        <v>21415.39130811645</v>
+      </c>
+    </row>
+    <row r="52" spans="2:3">
+      <c r="B52">
+        <f t="shared" si="0"/>
+        <v>4.7999999999999989</v>
+      </c>
+      <c r="C52">
+        <f t="shared" si="1"/>
+        <v>20978.097922810757</v>
+      </c>
+    </row>
+    <row r="53" spans="2:3">
+      <c r="B53">
+        <f t="shared" si="0"/>
+        <v>4.8999999999999986</v>
+      </c>
+      <c r="C53">
+        <f t="shared" si="1"/>
+        <v>20559.022544531508</v>
+      </c>
+    </row>
+    <row r="54" spans="2:3">
+      <c r="B54">
+        <f t="shared" si="0"/>
+        <v>4.9999999999999982</v>
+      </c>
+      <c r="C54">
+        <f t="shared" si="1"/>
+        <v>20157.079632679495</v>
+      </c>
+    </row>
+    <row r="55" spans="2:3">
+      <c r="B55">
+        <f t="shared" si="0"/>
+        <v>5.0999999999999979</v>
+      </c>
+      <c r="C55">
+        <f t="shared" si="1"/>
+        <v>19771.26878709465</v>
+      </c>
+    </row>
+    <row r="56" spans="2:3">
+      <c r="B56">
+        <f t="shared" si="0"/>
+        <v>5.1999999999999975</v>
+      </c>
+      <c r="C56">
+        <f t="shared" si="1"/>
+        <v>19400.666561475377</v>
+      </c>
+    </row>
+    <row r="57" spans="2:3">
+      <c r="B57">
+        <f t="shared" si="0"/>
+        <v>5.2999999999999972</v>
+      </c>
+      <c r="C57">
+        <f t="shared" si="1"/>
+        <v>19044.419203580572</v>
+      </c>
+    </row>
+    <row r="58" spans="2:3">
+      <c r="B58">
+        <f t="shared" si="0"/>
+        <v>5.3999999999999968</v>
+      </c>
+      <c r="C58">
+        <f t="shared" si="1"/>
+        <v>18701.736202075885</v>
+      </c>
+    </row>
+    <row r="59" spans="2:3">
+      <c r="B59">
+        <f t="shared" si="0"/>
+        <v>5.4999999999999964</v>
+      </c>
+      <c r="C59">
+        <f t="shared" si="1"/>
+        <v>18371.884537360376</v>
+      </c>
+    </row>
+    <row r="60" spans="2:3">
+      <c r="B60">
+        <f t="shared" si="0"/>
+        <v>5.5999999999999961</v>
+      </c>
+      <c r="C60">
+        <f t="shared" si="1"/>
+        <v>18054.183548376022</v>
+      </c>
+    </row>
+    <row r="61" spans="2:3">
+      <c r="B61">
+        <f t="shared" si="0"/>
+        <v>5.6999999999999957</v>
+      </c>
+      <c r="C61">
+        <f t="shared" si="1"/>
+        <v>17748.000339753085</v>
+      </c>
+    </row>
+    <row r="62" spans="2:3">
+      <c r="B62">
+        <f t="shared" si="0"/>
+        <v>5.7999999999999954</v>
+      </c>
+      <c r="C62">
+        <f t="shared" si="1"/>
+        <v>17452.74566407836</v>
+      </c>
+    </row>
+    <row r="63" spans="2:3">
+      <c r="B63">
+        <f t="shared" si="0"/>
+        <v>5.899999999999995</v>
+      </c>
+      <c r="C63">
+        <f t="shared" si="1"/>
+        <v>17167.870222915819</v>
+      </c>
+    </row>
+    <row r="64" spans="2:3">
+      <c r="B64">
+        <f t="shared" si="0"/>
+        <v>5.9999999999999947</v>
+      </c>
+      <c r="C64">
+        <f t="shared" si="1"/>
+        <v>16892.861337725146</v>
+      </c>
+    </row>
+    <row r="65" spans="2:3">
+      <c r="B65">
+        <f t="shared" si="0"/>
+        <v>6.0999999999999943</v>
+      </c>
+      <c r="C65">
+        <f t="shared" si="1"/>
+        <v>16627.239948230988</v>
+      </c>
+    </row>
+    <row r="66" spans="2:3">
+      <c r="B66">
+        <f t="shared" si="0"/>
+        <v>6.199999999999994</v>
+      </c>
+      <c r="C66">
+        <f t="shared" si="1"/>
+        <v>16370.557901272514</v>
+      </c>
+    </row>
+    <row r="67" spans="2:3">
+      <c r="B67">
+        <f t="shared" si="0"/>
+        <v>6.2999999999999936</v>
+      </c>
+      <c r="C67">
+        <f t="shared" si="1"/>
+        <v>16122.395497857846</v>
+      </c>
+    </row>
+    <row r="68" spans="2:3">
+      <c r="B68">
+        <f t="shared" si="0"/>
+        <v>6.3999999999999932</v>
+      </c>
+      <c r="C68">
+        <f t="shared" si="1"/>
+        <v>15882.359270182093</v>
+      </c>
+    </row>
+    <row r="69" spans="2:3">
+      <c r="B69">
+        <f t="shared" si="0"/>
+        <v>6.4999999999999929</v>
+      </c>
+      <c r="C69">
+        <f t="shared" si="1"/>
+        <v>15650.079963843738</v>
+      </c>
+    </row>
+    <row r="70" spans="2:3">
+      <c r="B70">
+        <f t="shared" ref="B70:B71" si="2">B69+0.1</f>
+        <v>6.5999999999999925</v>
+      </c>
+      <c r="C70">
+        <f t="shared" ref="C70:C133" si="3">2*PI()*B70^2+100000/B70</f>
+        <v>15425.21070349591</v>
+      </c>
+    </row>
+    <row r="71" spans="2:3">
+      <c r="B71">
+        <f t="shared" si="2"/>
+        <v>6.6999999999999922</v>
+      </c>
+      <c r="C71">
+        <f t="shared" si="3"/>
+        <v>15207.425322767667</v>
+      </c>
+    </row>
+    <row r="72" spans="2:3">
+      <c r="B72">
+        <f t="shared" ref="B72:B135" si="4">B71+0.1</f>
+        <v>6.7999999999999918</v>
+      </c>
+      <c r="C72">
+        <f t="shared" si="3"/>
+        <v>14996.416841545179</v>
+      </c>
+    </row>
+    <row r="73" spans="2:3">
+      <c r="B73">
+        <f t="shared" si="4"/>
+        <v>6.8999999999999915</v>
+      </c>
+      <c r="C73">
+        <f t="shared" si="3"/>
+        <v>14791.896075663244</v>
+      </c>
+    </row>
+    <row r="74" spans="2:3">
+      <c r="B74">
+        <f t="shared" si="4"/>
+        <v>6.9999999999999911</v>
+      </c>
+      <c r="C74">
+        <f t="shared" si="3"/>
+        <v>14593.590365766104</v>
+      </c>
+    </row>
+    <row r="75" spans="2:3">
+      <c r="B75">
+        <f t="shared" si="4"/>
+        <v>7.0999999999999908</v>
+      </c>
+      <c r="C75">
+        <f t="shared" si="3"/>
+        <v>14401.242413588461</v>
+      </c>
+    </row>
+    <row r="76" spans="2:3">
+      <c r="B76">
+        <f t="shared" si="4"/>
+        <v>7.1999999999999904</v>
+      </c>
+      <c r="C76">
+        <f t="shared" si="3"/>
+        <v>14214.609215213095</v>
+      </c>
+    </row>
+    <row r="77" spans="2:3">
+      <c r="B77">
+        <f t="shared" si="4"/>
+        <v>7.2999999999999901</v>
+      </c>
+      <c r="C77">
+        <f t="shared" si="3"/>
+        <v>14033.461082005919</v>
+      </c>
+    </row>
+    <row r="78" spans="2:3">
+      <c r="B78">
+        <f t="shared" si="4"/>
+        <v>7.3999999999999897</v>
+      </c>
+      <c r="C78">
+        <f t="shared" si="3"/>
+        <v>13857.580740934685</v>
+      </c>
+    </row>
+    <row r="79" spans="2:3">
+      <c r="B79">
+        <f t="shared" si="4"/>
+        <v>7.4999999999999893</v>
+      </c>
+      <c r="C79">
+        <f t="shared" si="3"/>
+        <v>13686.762506862204</v>
+      </c>
+    </row>
+    <row r="80" spans="2:3">
+      <c r="B80">
+        <f t="shared" si="4"/>
+        <v>7.599999999999989</v>
+      </c>
+      <c r="C80">
+        <f t="shared" si="3"/>
+        <v>13520.811520184818</v>
+      </c>
+    </row>
+    <row r="81" spans="2:3">
+      <c r="B81">
+        <f t="shared" si="4"/>
+        <v>7.6999999999999886</v>
+      </c>
+      <c r="C81">
+        <f t="shared" si="3"/>
+        <v>13359.543043875683</v>
+      </c>
+    </row>
+    <row r="82" spans="2:3">
+      <c r="B82">
+        <f t="shared" si="4"/>
+        <v>7.7999999999999883</v>
+      </c>
+      <c r="C82">
+        <f t="shared" si="3"/>
+        <v>13202.781814601645</v>
+      </c>
+    </row>
+    <row r="83" spans="2:3">
+      <c r="B83">
+        <f t="shared" si="4"/>
+        <v>7.8999999999999879</v>
+      </c>
+      <c r="C83">
+        <f t="shared" si="3"/>
+        <v>13050.361443122361</v>
+      </c>
+    </row>
+    <row r="84" spans="2:3">
+      <c r="B84">
+        <f t="shared" si="4"/>
+        <v>7.9999999999999876</v>
+      </c>
+      <c r="C84">
+        <f t="shared" si="3"/>
+        <v>12902.123859659512</v>
+      </c>
+    </row>
+    <row r="85" spans="2:3">
+      <c r="B85">
+        <f t="shared" si="4"/>
+        <v>8.0999999999999872</v>
+      </c>
+      <c r="C85">
+        <f t="shared" si="3"/>
+        <v>12757.918800349749</v>
+      </c>
+    </row>
+    <row r="86" spans="2:3">
+      <c r="B86">
+        <f t="shared" si="4"/>
+        <v>8.1999999999999869</v>
+      </c>
+      <c r="C86">
+        <f t="shared" si="3"/>
+        <v>12617.603331274286</v>
+      </c>
+    </row>
+    <row r="87" spans="2:3">
+      <c r="B87">
+        <f t="shared" si="4"/>
+        <v>8.2999999999999865</v>
+      </c>
+      <c r="C87">
+        <f t="shared" si="3"/>
+        <v>12481.041406895958</v>
+      </c>
+    </row>
+    <row r="88" spans="2:3">
+      <c r="B88">
+        <f t="shared" si="4"/>
+        <v>8.3999999999999861</v>
+      </c>
+      <c r="C88">
+        <f t="shared" si="3"/>
+        <v>12348.103460036515</v>
+      </c>
+    </row>
+    <row r="89" spans="2:3">
+      <c r="B89">
+        <f t="shared" si="4"/>
+        <v>8.4999999999999858</v>
+      </c>
+      <c r="C89">
+        <f t="shared" si="3"/>
+        <v>12218.666020796683</v>
+      </c>
+    </row>
+    <row r="90" spans="2:3">
+      <c r="B90">
+        <f t="shared" si="4"/>
+        <v>8.5999999999999854</v>
+      </c>
+      <c r="C90">
+        <f t="shared" si="3"/>
+        <v>12092.611362063206</v>
+      </c>
+    </row>
+    <row r="91" spans="2:3">
+      <c r="B91">
+        <f t="shared" si="4"/>
+        <v>8.6999999999999851</v>
+      </c>
+      <c r="C91">
+        <f t="shared" si="3"/>
+        <v>11969.827169463661</v>
+      </c>
+    </row>
+    <row r="92" spans="2:3">
+      <c r="B92">
+        <f t="shared" si="4"/>
+        <v>8.7999999999999847</v>
+      </c>
+      <c r="C92">
+        <f t="shared" si="3"/>
+        <v>11850.206233824369</v>
+      </c>
+    </row>
+    <row r="93" spans="2:3">
+      <c r="B93">
+        <f t="shared" si="4"/>
+        <v>8.8999999999999844</v>
+      </c>
+      <c r="C93">
+        <f t="shared" si="3"/>
+        <v>11733.646164361488</v>
+      </c>
+    </row>
+    <row r="94" spans="2:3">
+      <c r="B94">
+        <f t="shared" si="4"/>
+        <v>8.999999999999984</v>
+      </c>
+      <c r="C94">
+        <f t="shared" si="3"/>
+        <v>11620.049120992677</v>
+      </c>
+    </row>
+    <row r="95" spans="2:3">
+      <c r="B95">
+        <f t="shared" si="4"/>
+        <v>9.0999999999999837</v>
+      </c>
+      <c r="C95">
+        <f t="shared" si="3"/>
+        <v>11509.321564298549</v>
+      </c>
+    </row>
+    <row r="96" spans="2:3">
+      <c r="B96">
+        <f t="shared" si="4"/>
+        <v>9.1999999999999833</v>
+      </c>
+      <c r="C96">
+        <f t="shared" si="3"/>
+        <v>11401.374021791002</v>
+      </c>
+    </row>
+    <row r="97" spans="2:3">
+      <c r="B97">
+        <f t="shared" si="4"/>
+        <v>9.2999999999999829</v>
+      </c>
+      <c r="C97">
+        <f t="shared" si="3"/>
+        <v>11296.120869260991</v>
+      </c>
+    </row>
+    <row r="98" spans="2:3">
+      <c r="B98">
+        <f t="shared" si="4"/>
+        <v>9.3999999999999826</v>
+      </c>
+      <c r="C98">
+        <f t="shared" si="3"/>
+        <v>11193.480126082832</v>
+      </c>
+    </row>
+    <row r="99" spans="2:3">
+      <c r="B99">
+        <f t="shared" si="4"/>
+        <v>9.4999999999999822</v>
+      </c>
+      <c r="C99">
+        <f t="shared" si="3"/>
+        <v>11093.37326344666</v>
+      </c>
+    </row>
+    <row r="100" spans="2:3">
+      <c r="B100">
+        <f t="shared" si="4"/>
+        <v>9.5999999999999819</v>
+      </c>
+      <c r="C100">
+        <f t="shared" si="3"/>
+        <v>10995.725024576355</v>
+      </c>
+    </row>
+    <row r="101" spans="2:3">
+      <c r="B101">
+        <f t="shared" si="4"/>
+        <v>9.6999999999999815</v>
+      </c>
+      <c r="C101">
+        <f t="shared" si="3"/>
+        <v>10900.463256068009</v>
+      </c>
+    </row>
+    <row r="102" spans="2:3">
+      <c r="B102">
+        <f t="shared" si="4"/>
+        <v>9.7999999999999812</v>
+      </c>
+      <c r="C102">
+        <f t="shared" si="3"/>
+        <v>10807.518749554605</v>
+      </c>
+    </row>
+    <row r="103" spans="2:3">
+      <c r="B103">
+        <f t="shared" si="4"/>
+        <v>9.8999999999999808</v>
+      </c>
+      <c r="C103">
+        <f t="shared" si="3"/>
+        <v>10716.82509296679</v>
+      </c>
+    </row>
+    <row r="104" spans="2:3">
+      <c r="B104">
+        <f t="shared" si="4"/>
+        <v>9.9999999999999805</v>
+      </c>
+      <c r="C104">
+        <f t="shared" si="3"/>
+        <v>10628.318530717976</v>
+      </c>
+    </row>
+    <row r="105" spans="2:3">
+      <c r="B105">
+        <f t="shared" si="4"/>
+        <v>10.09999999999998</v>
+      </c>
+      <c r="C105">
+        <f t="shared" si="3"/>
+        <v>10541.937832195308</v>
+      </c>
+    </row>
+    <row r="106" spans="2:3">
+      <c r="B106">
+        <f t="shared" si="4"/>
+        <v>10.19999999999998</v>
+      </c>
+      <c r="C106">
+        <f t="shared" si="3"/>
+        <v>10457.624167986432</v>
+      </c>
+    </row>
+    <row r="107" spans="2:3">
+      <c r="B107">
+        <f t="shared" si="4"/>
+        <v>10.299999999999979</v>
+      </c>
+      <c r="C107">
+        <f t="shared" si="3"/>
+        <v>10375.320993316369</v>
+      </c>
+    </row>
+    <row r="108" spans="2:3">
+      <c r="B108">
+        <f t="shared" si="4"/>
+        <v>10.399999999999979</v>
+      </c>
+      <c r="C108">
+        <f t="shared" si="3"/>
+        <v>10294.973938209176</v>
+      </c>
+    </row>
+    <row r="109" spans="2:3">
+      <c r="B109">
+        <f t="shared" si="4"/>
+        <v>10.499999999999979</v>
+      </c>
+      <c r="C109">
+        <f t="shared" si="3"/>
+        <v>10216.53070392609</v>
+      </c>
+    </row>
+    <row r="110" spans="2:3">
+      <c r="B110">
+        <f t="shared" si="4"/>
+        <v>10.599999999999978</v>
+      </c>
+      <c r="C110">
+        <f t="shared" si="3"/>
+        <v>10139.940965265658</v>
+      </c>
+    </row>
+    <row r="111" spans="2:3">
+      <c r="B111">
+        <f t="shared" si="4"/>
+        <v>10.699999999999978</v>
+      </c>
+      <c r="C111">
+        <f t="shared" si="3"/>
+        <v>10065.156278342371</v>
+      </c>
+    </row>
+    <row r="112" spans="2:3">
+      <c r="B112">
+        <f t="shared" si="4"/>
+        <v>10.799999999999978</v>
+      </c>
+      <c r="C112">
+        <f t="shared" si="3"/>
+        <v>9992.1299934887029</v>
+      </c>
+    </row>
+    <row r="113" spans="2:3">
+      <c r="B113">
+        <f t="shared" si="4"/>
+        <v>10.899999999999977</v>
+      </c>
+      <c r="C113">
+        <f t="shared" si="3"/>
+        <v>9920.817172951527</v>
+      </c>
+    </row>
+    <row r="114" spans="2:3">
+      <c r="B114">
+        <f t="shared" si="4"/>
+        <v>10.999999999999977</v>
+      </c>
+      <c r="C114">
+        <f t="shared" si="3"/>
+        <v>9851.1745130778363</v>
+      </c>
+    </row>
+    <row r="115" spans="2:3">
+      <c r="B115">
+        <f t="shared" si="4"/>
+        <v>11.099999999999977</v>
+      </c>
+      <c r="C115">
+        <f t="shared" si="3"/>
+        <v>9783.1602707066231</v>
+      </c>
+    </row>
+    <row r="116" spans="2:3">
+      <c r="B116">
+        <f t="shared" si="4"/>
+        <v>11.199999999999976</v>
+      </c>
+      <c r="C116">
+        <f t="shared" si="3"/>
+        <v>9716.7341935040513</v>
+      </c>
+    </row>
+    <row r="117" spans="2:3">
+      <c r="B117">
+        <f t="shared" si="4"/>
+        <v>11.299999999999976</v>
+      </c>
+      <c r="C117">
+        <f t="shared" si="3"/>
+        <v>9651.8574539976707</v>
+      </c>
+    </row>
+    <row r="118" spans="2:3">
+      <c r="B118">
+        <f t="shared" si="4"/>
+        <v>11.399999999999975</v>
+      </c>
+      <c r="C118">
+        <f t="shared" si="3"/>
+        <v>9588.4925870824791</v>
+      </c>
+    </row>
+    <row r="119" spans="2:3">
+      <c r="B119">
+        <f t="shared" si="4"/>
+        <v>11.499999999999975</v>
+      </c>
+      <c r="C119">
+        <f t="shared" si="3"/>
+        <v>9526.6034307875598</v>
+      </c>
+    </row>
+    <row r="120" spans="2:3">
+      <c r="B120">
+        <f t="shared" si="4"/>
+        <v>11.599999999999975</v>
+      </c>
+      <c r="C120">
+        <f t="shared" si="3"/>
+        <v>9466.1550701065153</v>
+      </c>
+    </row>
+    <row r="121" spans="2:3">
+      <c r="B121">
+        <f t="shared" si="4"/>
+        <v>11.699999999999974</v>
+      </c>
+      <c r="C121">
+        <f t="shared" si="3"/>
+        <v>9407.1137837083752</v>
+      </c>
+    </row>
+    <row r="122" spans="2:3">
+      <c r="B122">
+        <f t="shared" si="4"/>
+        <v>11.799999999999974</v>
+      </c>
+      <c r="C122">
+        <f t="shared" si="3"/>
+        <v>9349.4469933581404</v>
+      </c>
+    </row>
+    <row r="123" spans="2:3">
+      <c r="B123">
+        <f t="shared" si="4"/>
+        <v>11.899999999999974</v>
+      </c>
+      <c r="C123">
+        <f t="shared" si="3"/>
+        <v>9293.1232158875318</v>
+      </c>
+    </row>
+    <row r="124" spans="2:3">
+      <c r="B124">
+        <f t="shared" si="4"/>
+        <v>11.999999999999973</v>
+      </c>
+      <c r="C124">
+        <f t="shared" si="3"/>
+        <v>9238.1120175672077</v>
+      </c>
+    </row>
+    <row r="125" spans="2:3">
+      <c r="B125">
+        <f t="shared" si="4"/>
+        <v>12.099999999999973</v>
+      </c>
+      <c r="C125">
+        <f t="shared" si="3"/>
+        <v>9184.3839707415318</v>
+      </c>
+    </row>
+    <row r="126" spans="2:3">
+      <c r="B126">
+        <f t="shared" si="4"/>
+        <v>12.199999999999973</v>
+      </c>
+      <c r="C126">
+        <f t="shared" si="3"/>
+        <v>9131.9106125960334</v>
+      </c>
+    </row>
+    <row r="127" spans="2:3">
+      <c r="B127">
+        <f t="shared" si="4"/>
+        <v>12.299999999999972</v>
+      </c>
+      <c r="C127">
+        <f t="shared" si="3"/>
+        <v>9080.6644059362225</v>
+      </c>
+    </row>
+    <row r="128" spans="2:3">
+      <c r="B128">
+        <f t="shared" si="4"/>
+        <v>12.399999999999972</v>
+      </c>
+      <c r="C128">
+        <f t="shared" si="3"/>
+        <v>9030.6187018642049</v>
+      </c>
+    </row>
+    <row r="129" spans="2:3">
+      <c r="B129">
+        <f t="shared" si="4"/>
+        <v>12.499999999999972</v>
+      </c>
+      <c r="C129">
+        <f t="shared" si="3"/>
+        <v>8981.7477042468236</v>
+      </c>
+    </row>
+    <row r="130" spans="2:3">
+      <c r="B130">
+        <f t="shared" si="4"/>
+        <v>12.599999999999971</v>
+      </c>
+      <c r="C130">
+        <f t="shared" si="3"/>
+        <v>8934.0264358757813</v>
+      </c>
+    </row>
+    <row r="131" spans="2:3">
+      <c r="B131">
+        <f t="shared" si="4"/>
+        <v>12.699999999999971</v>
+      </c>
+      <c r="C131">
+        <f t="shared" si="3"/>
+        <v>8887.4307062265052</v>
+      </c>
+    </row>
+    <row r="132" spans="2:3">
+      <c r="B132">
+        <f t="shared" si="4"/>
+        <v>12.799999999999971</v>
+      </c>
+      <c r="C132">
+        <f t="shared" si="3"/>
+        <v>8841.9370807283158</v>
+      </c>
+    </row>
+    <row r="133" spans="2:3">
+      <c r="B133">
+        <f t="shared" si="4"/>
+        <v>12.89999999999997</v>
+      </c>
+      <c r="C133">
+        <f t="shared" si="3"/>
+        <v>8797.5228514638929</v>
+      </c>
+    </row>
+    <row r="134" spans="2:3">
+      <c r="B134">
+        <f t="shared" si="4"/>
+        <v>12.99999999999997</v>
+      </c>
+      <c r="C134">
+        <f t="shared" ref="C134:C197" si="5">2*PI()*B134^2+100000/B134</f>
+        <v>8754.166009221055</v>
+      </c>
+    </row>
+    <row r="135" spans="2:3">
+      <c r="B135">
+        <f t="shared" si="4"/>
+        <v>13.099999999999969</v>
+      </c>
+      <c r="C135">
+        <f t="shared" si="5"/>
+        <v>8711.845216824644</v>
+      </c>
+    </row>
+    <row r="136" spans="2:3">
+      <c r="B136">
+        <f t="shared" ref="B136:B199" si="6">B135+0.1</f>
+        <v>13.199999999999969</v>
+      </c>
+      <c r="C136">
+        <f t="shared" si="5"/>
+        <v>8670.5397836805587</v>
+      </c>
+    </row>
+    <row r="137" spans="2:3">
+      <c r="B137">
+        <f t="shared" si="6"/>
+        <v>13.299999999999969</v>
+      </c>
+      <c r="C137">
+        <f t="shared" si="5"/>
+        <v>8630.2296414682132</v>
+      </c>
+    </row>
+    <row r="138" spans="2:3">
+      <c r="B138">
+        <f t="shared" si="6"/>
+        <v>13.399999999999968</v>
+      </c>
+      <c r="C138">
+        <f t="shared" si="5"/>
+        <v>8590.8953209213578</v>
+      </c>
+    </row>
+    <row r="139" spans="2:3">
+      <c r="B139">
+        <f t="shared" si="6"/>
+        <v>13.499999999999968</v>
+      </c>
+      <c r="C139">
+        <f t="shared" si="5"/>
+        <v>8552.5179296408987</v>
+      </c>
+    </row>
+    <row r="140" spans="2:3">
+      <c r="B140">
+        <f t="shared" si="6"/>
+        <v>13.599999999999968</v>
+      </c>
+      <c r="C140">
+        <f t="shared" si="5"/>
+        <v>8515.0791308865373</v>
+      </c>
+    </row>
+    <row r="141" spans="2:3">
+      <c r="B141">
+        <f t="shared" si="6"/>
+        <v>13.699999999999967</v>
+      </c>
+      <c r="C141">
+        <f t="shared" si="5"/>
+        <v>8478.5611232972497</v>
+      </c>
+    </row>
+    <row r="142" spans="2:3">
+      <c r="B142">
+        <f t="shared" si="6"/>
+        <v>13.799999999999967</v>
+      </c>
+      <c r="C142">
+        <f t="shared" si="5"/>
+        <v>8442.9466214934946</v>
+      </c>
+    </row>
+    <row r="143" spans="2:3">
+      <c r="B143">
+        <f t="shared" si="6"/>
+        <v>13.899999999999967</v>
+      </c>
+      <c r="C143">
+        <f t="shared" si="5"/>
+        <v>8408.2188375167261</v>
+      </c>
+    </row>
+    <row r="144" spans="2:3">
+      <c r="B144">
+        <f t="shared" si="6"/>
+        <v>13.999999999999966</v>
+      </c>
+      <c r="C144">
+        <f t="shared" si="5"/>
+        <v>8374.3614630643533</v>
+      </c>
+    </row>
+    <row r="145" spans="2:3">
+      <c r="B145">
+        <f t="shared" si="6"/>
+        <v>14.099999999999966</v>
+      </c>
+      <c r="C145">
+        <f t="shared" si="5"/>
+        <v>8341.3586524806688</v>
+      </c>
+    </row>
+    <row r="146" spans="2:3">
+      <c r="B146">
+        <f t="shared" si="6"/>
+        <v>14.199999999999966</v>
+      </c>
+      <c r="C146">
+        <f t="shared" si="5"/>
+        <v>8309.1950064664634</v>
+      </c>
+    </row>
+    <row r="147" spans="2:3">
+      <c r="B147">
+        <f t="shared" si="6"/>
+        <v>14.299999999999965</v>
+      </c>
+      <c r="C147">
+        <f t="shared" si="5"/>
+        <v>8277.8555564721573</v>
+      </c>
+    </row>
+    <row r="148" spans="2:3">
+      <c r="B148">
+        <f t="shared" si="6"/>
+        <v>14.399999999999965</v>
+      </c>
+      <c r="C148">
+        <f t="shared" si="5"/>
+        <v>8247.3257497412142</v>
+      </c>
+    </row>
+    <row r="149" spans="2:3">
+      <c r="B149">
+        <f t="shared" si="6"/>
+        <v>14.499999999999964</v>
+      </c>
+      <c r="C149">
+        <f t="shared" si="5"/>
+        <v>8217.5914349724499</v>
+      </c>
+    </row>
+    <row r="150" spans="2:3">
+      <c r="B150">
+        <f t="shared" si="6"/>
+        <v>14.599999999999964</v>
+      </c>
+      <c r="C150">
+        <f t="shared" si="5"/>
+        <v>8188.6388485715615</v>
+      </c>
+    </row>
+    <row r="151" spans="2:3">
+      <c r="B151">
+        <f t="shared" si="6"/>
+        <v>14.699999999999964</v>
+      </c>
+      <c r="C151">
+        <f t="shared" si="5"/>
+        <v>8160.4546014638208</v>
+      </c>
+    </row>
+    <row r="152" spans="2:3">
+      <c r="B152">
+        <f t="shared" si="6"/>
+        <v>14.799999999999963</v>
+      </c>
+      <c r="C152">
+        <f t="shared" si="5"/>
+        <v>8133.0256664413828</v>
+      </c>
+    </row>
+    <row r="153" spans="2:3">
+      <c r="B153">
+        <f t="shared" si="6"/>
+        <v>14.899999999999963</v>
+      </c>
+      <c r="C153">
+        <f t="shared" si="5"/>
+        <v>8106.3393660201036</v>
+      </c>
+    </row>
+    <row r="154" spans="2:3">
+      <c r="B154">
+        <f t="shared" si="6"/>
+        <v>14.999999999999963</v>
+      </c>
+      <c r="C154">
+        <f t="shared" si="5"/>
+        <v>8080.3833607820834</v>
+      </c>
+    </row>
+    <row r="155" spans="2:3">
+      <c r="B155">
+        <f t="shared" si="6"/>
+        <v>15.099999999999962</v>
+      </c>
+      <c r="C155">
+        <f t="shared" si="5"/>
+        <v>8055.1456381814169</v>
+      </c>
+    </row>
+    <row r="156" spans="2:3">
+      <c r="B156">
+        <f t="shared" si="6"/>
+        <v>15.199999999999962</v>
+      </c>
+      <c r="C156">
+        <f t="shared" si="5"/>
+        <v>8030.6145017918334</v>
+      </c>
+    </row>
+    <row r="157" spans="2:3">
+      <c r="B157">
+        <f t="shared" si="6"/>
+        <v>15.299999999999962</v>
+      </c>
+      <c r="C157">
+        <f t="shared" si="5"/>
+        <v>8006.7785609759785</v>
+      </c>
+    </row>
+    <row r="158" spans="2:3">
+      <c r="B158">
+        <f t="shared" si="6"/>
+        <v>15.399999999999961</v>
+      </c>
+      <c r="C158">
+        <f t="shared" si="5"/>
+        <v>7983.6267209572134</v>
+      </c>
+    </row>
+    <row r="159" spans="2:3">
+      <c r="B159">
+        <f t="shared" si="6"/>
+        <v>15.499999999999961</v>
+      </c>
+      <c r="C159">
+        <f t="shared" si="5"/>
+        <v>7961.1481732757102</v>
+      </c>
+    </row>
+    <row r="160" spans="2:3">
+      <c r="B160">
+        <f t="shared" si="6"/>
+        <v>15.599999999999961</v>
+      </c>
+      <c r="C160">
+        <f t="shared" si="5"/>
+        <v>7939.3323866116425</v>
+      </c>
+    </row>
+    <row r="161" spans="2:3">
+      <c r="B161">
+        <f t="shared" si="6"/>
+        <v>15.69999999999996</v>
+      </c>
+      <c r="C161">
+        <f t="shared" si="5"/>
+        <v>7918.1690979590612</v>
+      </c>
+    </row>
+    <row r="162" spans="2:3">
+      <c r="B162">
+        <f t="shared" si="6"/>
+        <v>15.79999999999996</v>
+      </c>
+      <c r="C162">
+        <f t="shared" si="5"/>
+        <v>7897.6483041349529</v>
+      </c>
+    </row>
+    <row r="163" spans="2:3">
+      <c r="B163">
+        <f t="shared" si="6"/>
+        <v>15.899999999999959</v>
+      </c>
+      <c r="C163">
+        <f t="shared" si="5"/>
+        <v>7877.7602536087088</v>
+      </c>
+    </row>
+    <row r="164" spans="2:3">
+      <c r="B164">
+        <f t="shared" si="6"/>
+        <v>15.999999999999959</v>
+      </c>
+      <c r="C164">
+        <f t="shared" si="5"/>
+        <v>7858.4954386379823</v>
+      </c>
+    </row>
+    <row r="165" spans="2:3">
+      <c r="B165">
+        <f t="shared" si="6"/>
+        <v>16.099999999999959</v>
+      </c>
+      <c r="C165">
+        <f t="shared" si="5"/>
+        <v>7839.8445876976311</v>
+      </c>
+    </row>
+    <row r="166" spans="2:3">
+      <c r="B166">
+        <f t="shared" si="6"/>
+        <v>16.19999999999996</v>
+      </c>
+      <c r="C166">
+        <f t="shared" si="5"/>
+        <v>7821.7986581890564</v>
+      </c>
+    </row>
+    <row r="167" spans="2:3">
+      <c r="B167">
+        <f t="shared" si="6"/>
+        <v>16.299999999999962</v>
+      </c>
+      <c r="C167">
+        <f t="shared" si="5"/>
+        <v>7804.3488294179251</v>
+      </c>
+    </row>
+    <row r="168" spans="2:3">
+      <c r="B168">
+        <f t="shared" si="6"/>
+        <v>16.399999999999963</v>
+      </c>
+      <c r="C168">
+        <f t="shared" si="5"/>
+        <v>7787.4864958287835</v>
+      </c>
+    </row>
+    <row r="169" spans="2:3">
+      <c r="B169">
+        <f t="shared" si="6"/>
+        <v>16.499999999999964</v>
+      </c>
+      <c r="C169">
+        <f t="shared" si="5"/>
+        <v>7771.2032604857086</v>
+      </c>
+    </row>
+    <row r="170" spans="2:3">
+      <c r="B170">
+        <f t="shared" si="6"/>
+        <v>16.599999999999966</v>
+      </c>
+      <c r="C170">
+        <f t="shared" si="5"/>
+        <v>7755.4909287885812</v>
+      </c>
+    </row>
+    <row r="171" spans="2:3">
+      <c r="B171">
+        <f t="shared" si="6"/>
+        <v>16.699999999999967</v>
+      </c>
+      <c r="C171">
+        <f t="shared" si="5"/>
+        <v>7740.3415024151282</v>
+      </c>
+    </row>
+    <row r="172" spans="2:3">
+      <c r="B172">
+        <f t="shared" si="6"/>
+        <v>16.799999999999969</v>
+      </c>
+      <c r="C172">
+        <f t="shared" si="5"/>
+        <v>7725.7471734793235</v>
+      </c>
+    </row>
+    <row r="173" spans="2:3">
+      <c r="B173">
+        <f t="shared" si="6"/>
+        <v>16.89999999999997</v>
+      </c>
+      <c r="C173">
+        <f t="shared" si="5"/>
+        <v>7711.7003188971748</v>
+      </c>
+    </row>
+    <row r="174" spans="2:3">
+      <c r="B174">
+        <f t="shared" si="6"/>
+        <v>16.999999999999972</v>
+      </c>
+      <c r="C174">
+        <f t="shared" si="5"/>
+        <v>7698.1934949513743</v>
+      </c>
+    </row>
+    <row r="175" spans="2:3">
+      <c r="B175">
+        <f t="shared" si="6"/>
+        <v>17.099999999999973</v>
+      </c>
+      <c r="C175">
+        <f t="shared" si="5"/>
+        <v>7685.2194320466551</v>
+      </c>
+    </row>
+    <row r="176" spans="2:3">
+      <c r="B176">
+        <f t="shared" si="6"/>
+        <v>17.199999999999974</v>
+      </c>
+      <c r="C176">
+        <f t="shared" si="5"/>
+        <v>7672.7710296481055</v>
+      </c>
+    </row>
+    <row r="177" spans="2:3">
+      <c r="B177">
+        <f t="shared" si="6"/>
+        <v>17.299999999999976</v>
+      </c>
+      <c r="C177">
+        <f t="shared" si="5"/>
+        <v>7660.8413513950291</v>
+      </c>
+    </row>
+    <row r="178" spans="2:3">
+      <c r="B178">
+        <f t="shared" si="6"/>
+        <v>17.399999999999977</v>
+      </c>
+      <c r="C178">
+        <f t="shared" si="5"/>
+        <v>7649.4236203833034</v>
+      </c>
+    </row>
+    <row r="179" spans="2:3">
+      <c r="B179">
+        <f t="shared" si="6"/>
+        <v>17.499999999999979</v>
+      </c>
+      <c r="C179">
+        <f t="shared" si="5"/>
+        <v>7638.5112146094652</v>
+      </c>
+    </row>
+    <row r="180" spans="2:3">
+      <c r="B180">
+        <f t="shared" si="6"/>
+        <v>17.59999999999998</v>
+      </c>
+      <c r="C180">
+        <f t="shared" si="5"/>
+        <v>7628.0976625701323</v>
+      </c>
+    </row>
+    <row r="181" spans="2:3">
+      <c r="B181">
+        <f t="shared" si="6"/>
+        <v>17.699999999999982</v>
+      </c>
+      <c r="C181">
+        <f t="shared" si="5"/>
+        <v>7618.1766390105877</v>
+      </c>
+    </row>
+    <row r="182" spans="2:3">
+      <c r="B182">
+        <f t="shared" si="6"/>
+        <v>17.799999999999983</v>
+      </c>
+      <c r="C182">
+        <f t="shared" si="5"/>
+        <v>7608.7419608166692</v>
+      </c>
+    </row>
+    <row r="183" spans="2:3">
+      <c r="B183">
+        <f t="shared" si="6"/>
+        <v>17.899999999999984</v>
+      </c>
+      <c r="C183">
+        <f t="shared" si="5"/>
+        <v>7599.7875830443627</v>
+      </c>
+    </row>
+    <row r="184" spans="2:3">
+      <c r="B184">
+        <f t="shared" si="6"/>
+        <v>17.999999999999986</v>
+      </c>
+      <c r="C184">
+        <f t="shared" si="5"/>
+        <v>7591.3075950817429</v>
+      </c>
+    </row>
+    <row r="185" spans="2:3">
+      <c r="B185">
+        <f t="shared" si="6"/>
+        <v>18.099999999999987</v>
+      </c>
+      <c r="C185">
+        <f t="shared" si="5"/>
+        <v>7583.2962169381444</v>
+      </c>
+    </row>
+    <row r="186" spans="2:3">
+      <c r="B186">
+        <f t="shared" si="6"/>
+        <v>18.199999999999989</v>
+      </c>
+      <c r="C186">
+        <f t="shared" si="5"/>
+        <v>7575.7477956556613</v>
+      </c>
+    </row>
+    <row r="187" spans="2:3">
+      <c r="B187">
+        <f t="shared" si="6"/>
+        <v>18.29999999999999</v>
+      </c>
+      <c r="C187">
+        <f t="shared" si="5"/>
+        <v>7568.6568018383132</v>
+      </c>
+    </row>
+    <row r="188" spans="2:3">
+      <c r="B188">
+        <f t="shared" si="6"/>
+        <v>18.399999999999991</v>
+      </c>
+      <c r="C188">
+        <f t="shared" si="5"/>
+        <v>7562.0178262943737</v>
+      </c>
+    </row>
+    <row r="189" spans="2:3">
+      <c r="B189">
+        <f t="shared" si="6"/>
+        <v>18.499999999999993</v>
+      </c>
+      <c r="C189">
+        <f t="shared" si="5"/>
+        <v>7555.8255767876199</v>
+      </c>
+    </row>
+    <row r="190" spans="2:3">
+      <c r="B190">
+        <f t="shared" si="6"/>
+        <v>18.599999999999994</v>
+      </c>
+      <c r="C190">
+        <f t="shared" si="5"/>
+        <v>7550.0748748933547</v>
+      </c>
+    </row>
+    <row r="191" spans="2:3">
+      <c r="B191">
+        <f t="shared" si="6"/>
+        <v>18.699999999999996</v>
+      </c>
+      <c r="C191">
+        <f t="shared" si="5"/>
+        <v>7544.7606529553304</v>
+      </c>
+    </row>
+    <row r="192" spans="2:3">
+      <c r="B192">
+        <f t="shared" si="6"/>
+        <v>18.799999999999997</v>
+      </c>
+      <c r="C192">
+        <f t="shared" si="5"/>
+        <v>7539.8779511397661</v>
+      </c>
+    </row>
+    <row r="193" spans="2:3">
+      <c r="B193">
+        <f t="shared" si="6"/>
+        <v>18.899999999999999</v>
+      </c>
+      <c r="C193">
+        <f t="shared" si="5"/>
+        <v>7535.421914582912</v>
+      </c>
+    </row>
+    <row r="194" spans="2:3">
+      <c r="B194">
+        <f t="shared" si="6"/>
+        <v>19</v>
+      </c>
+      <c r="C194">
+        <f t="shared" si="5"/>
+        <v>7531.3877906286725</v>
+      </c>
+    </row>
+    <row r="195" spans="2:3">
+      <c r="B195">
+        <f t="shared" si="6"/>
+        <v>19.100000000000001</v>
+      </c>
+      <c r="C195">
+        <f t="shared" si="5"/>
+        <v>7527.7709261530235</v>
+      </c>
+    </row>
+    <row r="196" spans="2:3">
+      <c r="B196">
+        <f t="shared" si="6"/>
+        <v>19.200000000000003</v>
+      </c>
+      <c r="C196">
+        <f t="shared" si="5"/>
+        <v>7524.5667649720153</v>
+      </c>
+    </row>
+    <row r="197" spans="2:3">
+      <c r="B197">
+        <f t="shared" si="6"/>
+        <v>19.300000000000004</v>
+      </c>
+      <c r="C197">
+        <f t="shared" si="5"/>
+        <v>7521.7708453303912</v>
+      </c>
+    </row>
+    <row r="198" spans="2:3">
+      <c r="B198">
+        <f t="shared" si="6"/>
+        <v>19.400000000000006</v>
+      </c>
+      <c r="C198">
+        <f t="shared" ref="C198:C261" si="7">2*PI()*B198^2+100000/B198</f>
+        <v>7519.3787974678407</v>
+      </c>
+    </row>
+    <row r="199" spans="2:3">
+      <c r="B199">
+        <f t="shared" si="6"/>
+        <v>19.500000000000007</v>
+      </c>
+      <c r="C199">
+        <f t="shared" si="7"/>
+        <v>7517.3863412601659</v>
+      </c>
+    </row>
+    <row r="200" spans="2:3">
+      <c r="B200">
+        <f t="shared" ref="B200:B263" si="8">B199+0.1</f>
+        <v>19.600000000000009</v>
+      </c>
+      <c r="C200">
+        <f t="shared" si="7"/>
+        <v>7515.7892839326396</v>
+      </c>
+    </row>
+    <row r="201" spans="2:3">
+      <c r="B201">
+        <f t="shared" si="8"/>
+        <v>19.70000000000001</v>
+      </c>
+      <c r="C201">
+        <f t="shared" si="7"/>
+        <v>7514.5835178430207</v>
+      </c>
+    </row>
+    <row r="202" spans="2:3">
+      <c r="B202">
+        <f t="shared" si="8"/>
+        <v>19.800000000000011</v>
+      </c>
+      <c r="C202">
+        <f t="shared" si="7"/>
+        <v>7513.7650183317355</v>
+      </c>
+    </row>
+    <row r="203" spans="2:3">
+      <c r="B203">
+        <f t="shared" si="8"/>
+        <v>19.900000000000013</v>
+      </c>
+      <c r="C203">
+        <f t="shared" si="7"/>
+        <v>7513.3298416368916</v>
+      </c>
+    </row>
+    <row r="204" spans="2:3">
+      <c r="B204">
+        <f t="shared" si="8"/>
+        <v>20.000000000000014</v>
+      </c>
+      <c r="C204">
+        <f t="shared" si="7"/>
+        <v>7513.2741228718351</v>
+      </c>
+    </row>
+    <row r="205" spans="2:3">
+      <c r="B205">
+        <f t="shared" si="8"/>
+        <v>20.100000000000016</v>
+      </c>
+      <c r="C205">
+        <f t="shared" si="7"/>
+        <v>7513.5940740630776</v>
+      </c>
+    </row>
+    <row r="206" spans="2:3">
+      <c r="B206">
+        <f t="shared" si="8"/>
+        <v>20.200000000000017</v>
+      </c>
+      <c r="C206">
+        <f t="shared" si="7"/>
+        <v>7514.2859822465089</v>
+      </c>
+    </row>
+    <row r="207" spans="2:3">
+      <c r="B207">
+        <f t="shared" si="8"/>
+        <v>20.300000000000018</v>
+      </c>
+      <c r="C207">
+        <f t="shared" si="7"/>
+        <v>7515.3462076198721</v>
+      </c>
+    </row>
+    <row r="208" spans="2:3">
+      <c r="B208">
+        <f t="shared" si="8"/>
+        <v>20.40000000000002</v>
+      </c>
+      <c r="C208">
+        <f t="shared" si="7"/>
+        <v>7516.7711817495829</v>
+      </c>
+    </row>
+    <row r="209" spans="2:3">
+      <c r="B209">
+        <f t="shared" si="8"/>
+        <v>20.500000000000021</v>
+      </c>
+      <c r="C209">
+        <f t="shared" si="7"/>
+        <v>7518.5574058300263</v>
+      </c>
+    </row>
+    <row r="210" spans="2:3">
+      <c r="B210">
+        <f t="shared" si="8"/>
+        <v>20.600000000000023</v>
+      </c>
+      <c r="C210">
+        <f t="shared" si="7"/>
+        <v>7520.7014489935646</v>
+      </c>
+    </row>
+    <row r="211" spans="2:3">
+      <c r="B211">
+        <f t="shared" si="8"/>
+        <v>20.700000000000024</v>
+      </c>
+      <c r="C211">
+        <f t="shared" si="7"/>
+        <v>7523.1999466695161</v>
+      </c>
+    </row>
+    <row r="212" spans="2:3">
+      <c r="B212">
+        <f t="shared" si="8"/>
+        <v>20.800000000000026</v>
+      </c>
+      <c r="C212">
+        <f t="shared" si="7"/>
+        <v>7526.0495989904848</v>
+      </c>
+    </row>
+    <row r="213" spans="2:3">
+      <c r="B213">
+        <f t="shared" si="8"/>
+        <v>20.900000000000027</v>
+      </c>
+      <c r="C213">
+        <f t="shared" si="7"/>
+        <v>7529.2471692444269</v>
+      </c>
+    </row>
+    <row r="214" spans="2:3">
+      <c r="B214">
+        <f t="shared" si="8"/>
+        <v>21.000000000000028</v>
+      </c>
+      <c r="C214">
+        <f t="shared" si="7"/>
+        <v>7532.7894823709603</v>
+      </c>
+    </row>
+    <row r="215" spans="2:3">
+      <c r="B215">
+        <f t="shared" si="8"/>
+        <v>21.10000000000003</v>
+      </c>
+      <c r="C215">
+        <f t="shared" si="7"/>
+        <v>7536.6734235004205</v>
+      </c>
+    </row>
+    <row r="216" spans="2:3">
+      <c r="B216">
+        <f t="shared" si="8"/>
+        <v>21.200000000000031</v>
+      </c>
+      <c r="C216">
+        <f t="shared" si="7"/>
+        <v>7540.8959365342653</v>
+      </c>
+    </row>
+    <row r="217" spans="2:3">
+      <c r="B217">
+        <f t="shared" si="8"/>
+        <v>21.300000000000033</v>
+      </c>
+      <c r="C217">
+        <f t="shared" si="7"/>
+        <v>7545.4540227654816</v>
+      </c>
+    </row>
+    <row r="218" spans="2:3">
+      <c r="B218">
+        <f t="shared" si="8"/>
+        <v>21.400000000000034</v>
+      </c>
+      <c r="C218">
+        <f t="shared" si="7"/>
+        <v>7550.3447395376479</v>
+      </c>
+    </row>
+    <row r="219" spans="2:3">
+      <c r="B219">
+        <f t="shared" si="8"/>
+        <v>21.500000000000036</v>
+      </c>
+      <c r="C219">
+        <f t="shared" si="7"/>
+        <v>7555.56519894144</v>
+      </c>
+    </row>
+    <row r="220" spans="2:3">
+      <c r="B220">
+        <f t="shared" si="8"/>
+        <v>21.600000000000037</v>
+      </c>
+      <c r="C220">
+        <f t="shared" si="7"/>
+        <v>7561.1125665473392</v>
+      </c>
+    </row>
+    <row r="221" spans="2:3">
+      <c r="B221">
+        <f t="shared" si="8"/>
+        <v>21.700000000000038</v>
+      </c>
+      <c r="C221">
+        <f t="shared" si="7"/>
+        <v>7566.984060173374</v>
+      </c>
+    </row>
+    <row r="222" spans="2:3">
+      <c r="B222">
+        <f t="shared" si="8"/>
+        <v>21.80000000000004</v>
+      </c>
+      <c r="C222">
+        <f t="shared" si="7"/>
+        <v>7573.1769486867815</v>
+      </c>
+    </row>
+    <row r="223" spans="2:3">
+      <c r="B223">
+        <f t="shared" si="8"/>
+        <v>21.900000000000041</v>
+      </c>
+      <c r="C223">
+        <f t="shared" si="7"/>
+        <v>7579.6885508385049</v>
+      </c>
+    </row>
+    <row r="224" spans="2:3">
+      <c r="B224">
+        <f t="shared" si="8"/>
+        <v>22.000000000000043</v>
+      </c>
+      <c r="C224">
+        <f t="shared" si="7"/>
+        <v>7586.516234129469</v>
+      </c>
+    </row>
+    <row r="225" spans="2:3">
+      <c r="B225">
+        <f t="shared" si="8"/>
+        <v>22.100000000000044</v>
+      </c>
+      <c r="C225">
+        <f t="shared" si="7"/>
+        <v>7593.6574137076395</v>
+      </c>
+    </row>
+    <row r="226" spans="2:3">
+      <c r="B226">
+        <f t="shared" si="8"/>
+        <v>22.200000000000045</v>
+      </c>
+      <c r="C226">
+        <f t="shared" si="7"/>
+        <v>7601.1095512948959</v>
+      </c>
+    </row>
+    <row r="227" spans="2:3">
+      <c r="B227">
+        <f t="shared" si="8"/>
+        <v>22.300000000000047</v>
+      </c>
+      <c r="C227">
+        <f t="shared" si="7"/>
+        <v>7608.8701541427654</v>
+      </c>
+    </row>
+    <row r="228" spans="2:3">
+      <c r="B228">
+        <f t="shared" si="8"/>
+        <v>22.400000000000048</v>
+      </c>
+      <c r="C228">
+        <f t="shared" si="7"/>
+        <v>7616.936774016147</v>
+      </c>
+    </row>
+    <row r="229" spans="2:3">
+      <c r="B229">
+        <f t="shared" si="8"/>
+        <v>22.50000000000005</v>
+      </c>
+      <c r="C229">
+        <f t="shared" si="7"/>
+        <v>7625.3070062041133</v>
+      </c>
+    </row>
+    <row r="230" spans="2:3">
+      <c r="B230">
+        <f t="shared" si="8"/>
+        <v>22.600000000000051</v>
+      </c>
+      <c r="C230">
+        <f t="shared" si="7"/>
+        <v>7633.978488556997</v>
+      </c>
+    </row>
+    <row r="231" spans="2:3">
+      <c r="B231">
+        <f t="shared" si="8"/>
+        <v>22.700000000000053</v>
+      </c>
+      <c r="C231">
+        <f t="shared" si="7"/>
+        <v>7642.9489005489086</v>
+      </c>
+    </row>
+    <row r="232" spans="2:3">
+      <c r="B232">
+        <f t="shared" si="8"/>
+        <v>22.800000000000054</v>
+      </c>
+      <c r="C232">
+        <f t="shared" si="7"/>
+        <v>7652.2159623649422</v>
+      </c>
+    </row>
+    <row r="233" spans="2:3">
+      <c r="B233">
+        <f t="shared" si="8"/>
+        <v>22.900000000000055</v>
+      </c>
+      <c r="C233">
+        <f t="shared" si="7"/>
+        <v>7661.7774340122887</v>
+      </c>
+    </row>
+    <row r="234" spans="2:3">
+      <c r="B234">
+        <f t="shared" si="8"/>
+        <v>23.000000000000057</v>
+      </c>
+      <c r="C234">
+        <f t="shared" si="7"/>
+        <v>7671.6311144545289</v>
+      </c>
+    </row>
+    <row r="235" spans="2:3">
+      <c r="B235">
+        <f t="shared" si="8"/>
+        <v>23.100000000000058</v>
+      </c>
+      <c r="C235">
+        <f t="shared" si="7"/>
+        <v>7681.7748407684339</v>
+      </c>
+    </row>
+    <row r="236" spans="2:3">
+      <c r="B236">
+        <f t="shared" si="8"/>
+        <v>23.20000000000006</v>
+      </c>
+      <c r="C236">
+        <f t="shared" si="7"/>
+        <v>7692.2064873225536</v>
+      </c>
+    </row>
+    <row r="237" spans="2:3">
+      <c r="B237">
+        <f t="shared" si="8"/>
+        <v>23.300000000000061</v>
+      </c>
+      <c r="C237">
+        <f t="shared" si="7"/>
+        <v>7702.9239649769643</v>
+      </c>
+    </row>
+    <row r="238" spans="2:3">
+      <c r="B238">
+        <f t="shared" si="8"/>
+        <v>23.400000000000063</v>
+      </c>
+      <c r="C238">
+        <f t="shared" si="7"/>
+        <v>7713.9252203035348</v>
+      </c>
+    </row>
+    <row r="239" spans="2:3">
+      <c r="B239">
+        <f t="shared" si="8"/>
+        <v>23.500000000000064</v>
+      </c>
+      <c r="C239">
+        <f t="shared" si="7"/>
+        <v>7725.2082348261038</v>
+      </c>
+    </row>
+    <row r="240" spans="2:3">
+      <c r="B240">
+        <f t="shared" si="8"/>
+        <v>23.600000000000065</v>
+      </c>
+      <c r="C240">
+        <f t="shared" si="7"/>
+        <v>7736.7710242799703</v>
+      </c>
+    </row>
+    <row r="241" spans="2:3">
+      <c r="B241">
+        <f t="shared" si="8"/>
+        <v>23.700000000000067</v>
+      </c>
+      <c r="C241">
+        <f t="shared" si="7"/>
+        <v>7748.6116378901315</v>
+      </c>
+    </row>
+    <row r="242" spans="2:3">
+      <c r="B242">
+        <f t="shared" si="8"/>
+        <v>23.800000000000068</v>
+      </c>
+      <c r="C242">
+        <f t="shared" si="7"/>
+        <v>7760.7281576677206</v>
+      </c>
+    </row>
+    <row r="243" spans="2:3">
+      <c r="B243">
+        <f t="shared" si="8"/>
+        <v>23.90000000000007</v>
+      </c>
+      <c r="C243">
+        <f t="shared" si="7"/>
+        <v>7773.1186977241014</v>
+      </c>
+    </row>
+    <row r="244" spans="2:3">
+      <c r="B244">
+        <f t="shared" si="8"/>
+        <v>24.000000000000071</v>
+      </c>
+      <c r="C244">
+        <f t="shared" si="7"/>
+        <v>7785.7814036021173</v>
+      </c>
+    </row>
+    <row r="245" spans="2:3">
+      <c r="B245">
+        <f t="shared" si="8"/>
+        <v>24.100000000000072</v>
+      </c>
+      <c r="C245">
+        <f t="shared" si="7"/>
+        <v>7798.7144516239805</v>
+      </c>
+    </row>
+    <row r="246" spans="2:3">
+      <c r="B246">
+        <f t="shared" si="8"/>
+        <v>24.200000000000074</v>
+      </c>
+      <c r="C246">
+        <f t="shared" si="7"/>
+        <v>7811.9160482553407</v>
+      </c>
+    </row>
+    <row r="247" spans="2:3">
+      <c r="B247">
+        <f t="shared" si="8"/>
+        <v>24.300000000000075</v>
+      </c>
+      <c r="C247">
+        <f t="shared" si="7"/>
+        <v>7825.3844294850433</v>
+      </c>
+    </row>
+    <row r="248" spans="2:3">
+      <c r="B248">
+        <f t="shared" si="8"/>
+        <v>24.400000000000077</v>
+      </c>
+      <c r="C248">
+        <f t="shared" si="7"/>
+        <v>7839.1178602201544</v>
+      </c>
+    </row>
+    <row r="249" spans="2:3">
+      <c r="B249">
+        <f t="shared" si="8"/>
+        <v>24.500000000000078</v>
+      </c>
+      <c r="C249">
+        <f t="shared" si="7"/>
+        <v>7853.1146336957827</v>
+      </c>
+    </row>
+    <row r="250" spans="2:3">
+      <c r="B250">
+        <f t="shared" si="8"/>
+        <v>24.60000000000008</v>
+      </c>
+      <c r="C250">
+        <f t="shared" si="7"/>
+        <v>7867.3730708993135</v>
+      </c>
+    </row>
+    <row r="251" spans="2:3">
+      <c r="B251">
+        <f t="shared" si="8"/>
+        <v>24.700000000000081</v>
+      </c>
+      <c r="C251">
+        <f t="shared" si="7"/>
+        <v>7881.891520008623</v>
+      </c>
+    </row>
+    <row r="252" spans="2:3">
+      <c r="B252">
+        <f t="shared" si="8"/>
+        <v>24.800000000000082</v>
+      </c>
+      <c r="C252">
+        <f t="shared" si="7"/>
+        <v>7896.6683558438745</v>
+      </c>
+    </row>
+    <row r="253" spans="2:3">
+      <c r="B253">
+        <f t="shared" si="8"/>
+        <v>24.900000000000084</v>
+      </c>
+      <c r="C253">
+        <f t="shared" si="7"/>
+        <v>7911.7019793325398</v>
+      </c>
+    </row>
+    <row r="254" spans="2:3">
+      <c r="B254">
+        <f t="shared" si="8"/>
+        <v>25.000000000000085</v>
+      </c>
+      <c r="C254">
+        <f t="shared" si="7"/>
+        <v>7926.9908169872542</v>
+      </c>
+    </row>
+    <row r="255" spans="2:3">
+      <c r="B255">
+        <f t="shared" si="8"/>
+        <v>25.100000000000087</v>
+      </c>
+      <c r="C255">
+        <f t="shared" si="7"/>
+        <v>7942.5333203961445</v>
+      </c>
+    </row>
+    <row r="256" spans="2:3">
+      <c r="B256">
+        <f t="shared" si="8"/>
+        <v>25.200000000000088</v>
+      </c>
+      <c r="C256">
+        <f t="shared" si="7"/>
+        <v>7958.3279657253061</v>
+      </c>
+    </row>
+    <row r="257" spans="2:3">
+      <c r="B257">
+        <f t="shared" si="8"/>
+        <v>25.30000000000009</v>
+      </c>
+      <c r="C257">
+        <f t="shared" si="7"/>
+        <v>7974.3732532330705</v>
+      </c>
+    </row>
+    <row r="258" spans="2:3">
+      <c r="B258">
+        <f t="shared" si="8"/>
+        <v>25.400000000000091</v>
+      </c>
+      <c r="C258">
+        <f t="shared" si="7"/>
+        <v>7990.6677067957453</v>
+      </c>
+    </row>
+    <row r="259" spans="2:3">
+      <c r="B259">
+        <f t="shared" si="8"/>
+        <v>25.500000000000092</v>
+      </c>
+      <c r="C259">
+        <f t="shared" si="7"/>
+        <v>8007.2098734445217</v>
+      </c>
+    </row>
+    <row r="260" spans="2:3">
+      <c r="B260">
+        <f t="shared" si="8"/>
+        <v>25.600000000000094</v>
+      </c>
+      <c r="C260">
+        <f t="shared" si="7"/>
+        <v>8023.9983229132304</v>
+      </c>
+    </row>
+    <row r="261" spans="2:3">
+      <c r="B261">
+        <f t="shared" si="8"/>
+        <v>25.700000000000095</v>
+      </c>
+      <c r="C261">
+        <f t="shared" si="7"/>
+        <v>8041.0316471966489</v>
+      </c>
+    </row>
+    <row r="262" spans="2:3">
+      <c r="B262">
+        <f t="shared" si="8"/>
+        <v>25.800000000000097</v>
+      </c>
+      <c r="C262">
+        <f t="shared" ref="C262:C309" si="9">2*PI()*B262^2+100000/B262</f>
+        <v>8058.3084601190985</v>
+      </c>
+    </row>
+    <row r="263" spans="2:3">
+      <c r="B263">
+        <f t="shared" si="8"/>
+        <v>25.900000000000098</v>
+      </c>
+      <c r="C263">
+        <f t="shared" si="9"/>
+        <v>8075.8273969130169</v>
+      </c>
+    </row>
+    <row r="264" spans="2:3">
+      <c r="B264">
+        <f t="shared" ref="B264:B309" si="10">B263+0.1</f>
+        <v>26.000000000000099</v>
+      </c>
+      <c r="C264">
+        <f t="shared" si="9"/>
+        <v>8093.5871138072653</v>
+      </c>
+    </row>
+    <row r="265" spans="2:3">
+      <c r="B265">
+        <f t="shared" si="10"/>
+        <v>26.100000000000101</v>
+      </c>
+      <c r="C265">
+        <f t="shared" si="9"/>
+        <v>8111.5862876248975</v>
+      </c>
+    </row>
+    <row r="266" spans="2:3">
+      <c r="B266">
+        <f t="shared" si="10"/>
+        <v>26.200000000000102</v>
+      </c>
+      <c r="C266">
+        <f t="shared" si="9"/>
+        <v>8129.8236153901453</v>
+      </c>
+    </row>
+    <row r="267" spans="2:3">
+      <c r="B267">
+        <f t="shared" si="10"/>
+        <v>26.300000000000104</v>
+      </c>
+      <c r="C267">
+        <f t="shared" si="9"/>
+        <v>8148.2978139443603</v>
+      </c>
+    </row>
+    <row r="268" spans="2:3">
+      <c r="B268">
+        <f t="shared" si="10"/>
+        <v>26.400000000000105</v>
+      </c>
+      <c r="C268">
+        <f t="shared" si="9"/>
+        <v>8167.0076195706934</v>
+      </c>
+    </row>
+    <row r="269" spans="2:3">
+      <c r="B269">
+        <f t="shared" si="10"/>
+        <v>26.500000000000107</v>
+      </c>
+      <c r="C269">
+        <f t="shared" si="9"/>
+        <v>8185.9517876272621</v>
+      </c>
+    </row>
+    <row r="270" spans="2:3">
+      <c r="B270">
+        <f t="shared" si="10"/>
+        <v>26.600000000000108</v>
+      </c>
+      <c r="C270">
+        <f t="shared" si="9"/>
+        <v>8205.1290921886102</v>
+      </c>
+    </row>
+    <row r="271" spans="2:3">
+      <c r="B271">
+        <f t="shared" si="10"/>
+        <v>26.700000000000109</v>
+      </c>
+      <c r="C271">
+        <f t="shared" si="9"/>
+        <v>8224.5383256952009</v>
+      </c>
+    </row>
+    <row r="272" spans="2:3">
+      <c r="B272">
+        <f t="shared" si="10"/>
+        <v>26.800000000000111</v>
+      </c>
+      <c r="C272">
+        <f t="shared" si="9"/>
+        <v>8244.1782986107773</v>
+      </c>
+    </row>
+    <row r="273" spans="2:3">
+      <c r="B273">
+        <f t="shared" si="10"/>
+        <v>26.900000000000112</v>
+      </c>
+      <c r="C273">
+        <f t="shared" si="9"/>
+        <v>8264.0478390873504</v>
+      </c>
+    </row>
+    <row r="274" spans="2:3">
+      <c r="B274">
+        <f t="shared" si="10"/>
+        <v>27.000000000000114</v>
+      </c>
+      <c r="C274">
+        <f t="shared" si="9"/>
+        <v>8284.1457926376461</v>
+      </c>
+    </row>
+    <row r="275" spans="2:3">
+      <c r="B275">
+        <f t="shared" si="10"/>
+        <v>27.100000000000115</v>
+      </c>
+      <c r="C275">
+        <f t="shared" si="9"/>
+        <v>8304.4710218147866</v>
+      </c>
+    </row>
+    <row r="276" spans="2:3">
+      <c r="B276">
+        <f t="shared" si="10"/>
+        <v>27.200000000000117</v>
+      </c>
+      <c r="C276">
+        <f t="shared" si="9"/>
+        <v>8325.0224058990625</v>
+      </c>
+    </row>
+    <row r="277" spans="2:3">
+      <c r="B277">
+        <f t="shared" si="10"/>
+        <v>27.300000000000118</v>
+      </c>
+      <c r="C277">
+        <f t="shared" si="9"/>
+        <v>8345.7988405915621</v>
+      </c>
+    </row>
+    <row r="278" spans="2:3">
+      <c r="B278">
+        <f t="shared" si="10"/>
+        <v>27.400000000000119</v>
+      </c>
+      <c r="C278">
+        <f t="shared" si="9"/>
+        <v>8366.799237714522</v>
+      </c>
+    </row>
+    <row r="279" spans="2:3">
+      <c r="B279">
+        <f t="shared" si="10"/>
+        <v>27.500000000000121</v>
+      </c>
+      <c r="C279">
+        <f t="shared" si="9"/>
+        <v>8388.022524918224</v>
+      </c>
+    </row>
+    <row r="280" spans="2:3">
+      <c r="B280">
+        <f t="shared" si="10"/>
+        <v>27.600000000000122</v>
+      </c>
+      <c r="C280">
+        <f t="shared" si="9"/>
+        <v>8409.4676453942484</v>
+      </c>
+    </row>
+    <row r="281" spans="2:3">
+      <c r="B281">
+        <f t="shared" si="10"/>
+        <v>27.700000000000124</v>
+      </c>
+      <c r="C281">
+        <f t="shared" si="9"/>
+        <v>8431.1335575949488</v>
+      </c>
+    </row>
+    <row r="282" spans="2:3">
+      <c r="B282">
+        <f t="shared" si="10"/>
+        <v>27.800000000000125</v>
+      </c>
+      <c r="C282">
+        <f t="shared" si="9"/>
+        <v>8453.0192349589724</v>
+      </c>
+    </row>
+    <row r="283" spans="2:3">
+      <c r="B283">
+        <f t="shared" si="10"/>
+        <v>27.900000000000126</v>
+      </c>
+      <c r="C283">
+        <f t="shared" si="9"/>
+        <v>8475.1236656426918</v>
+      </c>
+    </row>
+    <row r="284" spans="2:3">
+      <c r="B284">
+        <f t="shared" si="10"/>
+        <v>28.000000000000128</v>
+      </c>
+      <c r="C284">
+        <f t="shared" si="9"/>
+        <v>8497.445852257395</v>
+      </c>
+    </row>
+    <row r="285" spans="2:3">
+      <c r="B285">
+        <f t="shared" si="10"/>
+        <v>28.100000000000129</v>
+      </c>
+      <c r="C285">
+        <f t="shared" si="9"/>
+        <v>8519.9848116120666</v>
+      </c>
+    </row>
+    <row r="286" spans="2:3">
+      <c r="B286">
+        <f t="shared" si="10"/>
+        <v>28.200000000000131</v>
+      </c>
+      <c r="C286">
+        <f t="shared" si="9"/>
+        <v>8542.7395744616661</v>
+      </c>
+    </row>
+    <row r="287" spans="2:3">
+      <c r="B287">
+        <f t="shared" si="10"/>
+        <v>28.300000000000132</v>
+      </c>
+      <c r="C287">
+        <f t="shared" si="9"/>
+        <v>8565.70918526073</v>
+      </c>
+    </row>
+    <row r="288" spans="2:3">
+      <c r="B288">
+        <f t="shared" si="10"/>
+        <v>28.400000000000134</v>
+      </c>
+      <c r="C288">
+        <f t="shared" si="9"/>
+        <v>8588.8927019221774</v>
+      </c>
+    </row>
+    <row r="289" spans="2:3">
+      <c r="B289">
+        <f t="shared" si="10"/>
+        <v>28.500000000000135</v>
+      </c>
+      <c r="C289">
+        <f t="shared" si="9"/>
+        <v>8612.289195581212</v>
+      </c>
+    </row>
+    <row r="290" spans="2:3">
+      <c r="B290">
+        <f t="shared" si="10"/>
+        <v>28.600000000000136</v>
+      </c>
+      <c r="C290">
+        <f t="shared" si="9"/>
+        <v>8635.8977503641436</v>
+      </c>
+    </row>
+    <row r="291" spans="2:3">
+      <c r="B291">
+        <f t="shared" si="10"/>
+        <v>28.700000000000138</v>
+      </c>
+      <c r="C291">
+        <f t="shared" si="9"/>
+        <v>8659.7174631620765</v>
+      </c>
+    </row>
+    <row r="292" spans="2:3">
+      <c r="B292">
+        <f t="shared" si="10"/>
+        <v>28.800000000000139</v>
+      </c>
+      <c r="C292">
+        <f t="shared" si="9"/>
+        <v>8683.747443409291</v>
+      </c>
+    </row>
+    <row r="293" spans="2:3">
+      <c r="B293">
+        <f t="shared" si="10"/>
+        <v>28.900000000000141</v>
+      </c>
+      <c r="C293">
+        <f t="shared" si="9"/>
+        <v>8707.9868128662438</v>
+      </c>
+    </row>
+    <row r="294" spans="2:3">
+      <c r="B294">
+        <f t="shared" si="10"/>
+        <v>29.000000000000142</v>
+      </c>
+      <c r="C294">
+        <f t="shared" si="9"/>
+        <v>8732.4347054070331</v>
+      </c>
+    </row>
+    <row r="295" spans="2:3">
+      <c r="B295">
+        <f t="shared" si="10"/>
+        <v>29.100000000000144</v>
+      </c>
+      <c r="C295">
+        <f t="shared" si="9"/>
+        <v>8757.0902668112685</v>
+      </c>
+    </row>
+    <row r="296" spans="2:3">
+      <c r="B296">
+        <f t="shared" si="10"/>
+        <v>29.200000000000145</v>
+      </c>
+      <c r="C296">
+        <f t="shared" si="9"/>
+        <v>8781.9526545602148</v>
+      </c>
+    </row>
+    <row r="297" spans="2:3">
+      <c r="B297">
+        <f t="shared" si="10"/>
+        <v>29.300000000000146</v>
+      </c>
+      <c r="C297">
+        <f t="shared" si="9"/>
+        <v>8807.0210376370906</v>
+      </c>
+    </row>
+    <row r="298" spans="2:3">
+      <c r="B298">
+        <f t="shared" si="10"/>
+        <v>29.400000000000148</v>
+      </c>
+      <c r="C298">
+        <f t="shared" si="9"/>
+        <v>8832.2945963314723</v>
+      </c>
+    </row>
+    <row r="299" spans="2:3">
+      <c r="B299">
+        <f t="shared" si="10"/>
+        <v>29.500000000000149</v>
+      </c>
+      <c r="C299">
+        <f t="shared" si="9"/>
+        <v>8857.7725220476495</v>
+      </c>
+    </row>
+    <row r="300" spans="2:3">
+      <c r="B300">
+        <f t="shared" si="10"/>
+        <v>29.600000000000151</v>
+      </c>
+      <c r="C300">
+        <f t="shared" si="9"/>
+        <v>8883.4540171168846</v>
+      </c>
+    </row>
+    <row r="301" spans="2:3">
+      <c r="B301">
+        <f t="shared" si="10"/>
+        <v>29.700000000000152</v>
+      </c>
+      <c r="C301">
+        <f t="shared" si="9"/>
+        <v>8909.3382946134479</v>
+      </c>
+    </row>
+    <row r="302" spans="2:3">
+      <c r="B302">
+        <f t="shared" si="10"/>
+        <v>29.800000000000153</v>
+      </c>
+      <c r="C302">
+        <f t="shared" si="9"/>
+        <v>8935.4245781743775</v>
+      </c>
+    </row>
+    <row r="303" spans="2:3">
+      <c r="B303">
+        <f t="shared" si="10"/>
+        <v>29.900000000000155</v>
+      </c>
+      <c r="C303">
+        <f t="shared" si="9"/>
+        <v>8961.7121018228336</v>
+      </c>
+    </row>
+    <row r="304" spans="2:3">
+      <c r="B304">
+        <f t="shared" si="10"/>
+        <v>30.000000000000156</v>
+      </c>
+      <c r="C304">
+        <f t="shared" si="9"/>
+        <v>8988.2001097950015</v>
+      </c>
+    </row>
+    <row r="305" spans="2:3">
+      <c r="B305">
+        <f t="shared" si="10"/>
+        <v>30.100000000000158</v>
+      </c>
+      <c r="C305">
+        <f t="shared" si="9"/>
+        <v>9014.8878563704438</v>
+      </c>
+    </row>
+    <row r="306" spans="2:3">
+      <c r="B306">
+        <f t="shared" si="10"/>
+        <v>30.200000000000159</v>
+      </c>
+      <c r="C306">
+        <f t="shared" si="9"/>
+        <v>9041.7746057058084</v>
+      </c>
+    </row>
+    <row r="307" spans="2:3">
+      <c r="B307">
+        <f t="shared" si="10"/>
+        <v>30.300000000000161</v>
+      </c>
+      <c r="C307">
+        <f t="shared" si="9"/>
+        <v>9068.8596316718504</v>
+      </c>
+    </row>
+    <row r="308" spans="2:3">
+      <c r="B308">
+        <f t="shared" si="10"/>
+        <v>30.400000000000162</v>
+      </c>
+      <c r="C308">
+        <f t="shared" si="9"/>
+        <v>9096.1422176936576</v>
+      </c>
+    </row>
+    <row r="309" spans="2:3">
+      <c r="B309">
+        <f t="shared" si="10"/>
+        <v>30.500000000000163</v>
+      </c>
+      <c r="C309">
+        <f t="shared" si="9"/>
+        <v>9123.6216565940194</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>
--- a/l_r/1st.xlsx
+++ b/l_r/1st.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\l_r\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B358EF73-1CF8-4621-8A9B-0BE3B3A63384}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BA5B787-1278-40DE-BA55-000886D44E39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-450" yWindow="0" windowWidth="17715" windowHeight="15585" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="3" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="59">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -280,6 +280,10 @@
   </si>
   <si>
     <t>x</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>enroll in</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -5345,7 +5349,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C7A3EDD-6597-4754-A609-A225833ECC81}">
-  <dimension ref="A2:H122"/>
+  <dimension ref="A2:H132"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="2" spans="1:4">
@@ -6646,7 +6650,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="113" spans="1:3">
+    <row r="113" spans="1:5">
       <c r="A113">
         <f t="shared" si="4"/>
         <v>119</v>
@@ -6658,7 +6662,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="114" spans="1:3">
+    <row r="114" spans="1:5">
       <c r="A114">
         <f t="shared" si="4"/>
         <v>120</v>
@@ -6670,7 +6674,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="115" spans="1:3">
+    <row r="115" spans="1:5">
       <c r="A115">
         <v>102</v>
       </c>
@@ -6681,7 +6685,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:3">
+    <row r="116" spans="1:5">
       <c r="A116">
         <v>103</v>
       </c>
@@ -6692,7 +6696,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="117" spans="1:3">
+    <row r="117" spans="1:5">
       <c r="A117">
         <v>104</v>
       </c>
@@ -6703,7 +6707,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="118" spans="1:3">
+    <row r="118" spans="1:5">
       <c r="A118">
         <v>109</v>
       </c>
@@ -6714,7 +6718,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="119" spans="1:3">
+    <row r="119" spans="1:5">
       <c r="A119">
         <v>111</v>
       </c>
@@ -6725,7 +6729,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="120" spans="1:3">
+    <row r="120" spans="1:5">
       <c r="A120">
         <v>115</v>
       </c>
@@ -6736,7 +6740,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="121" spans="1:3">
+    <row r="121" spans="1:5">
       <c r="A121">
         <v>116</v>
       </c>
@@ -6747,7 +6751,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="122" spans="1:3">
+    <row r="122" spans="1:5">
       <c r="A122">
         <v>117</v>
       </c>
@@ -6755,6 +6759,128 @@
         <v>11</v>
       </c>
       <c r="C122">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="123" spans="1:5">
+      <c r="A123">
+        <v>121</v>
+      </c>
+      <c r="B123" t="s">
+        <v>11</v>
+      </c>
+      <c r="C123">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="124" spans="1:5">
+      <c r="A124">
+        <f>A123+1</f>
+        <v>122</v>
+      </c>
+      <c r="B124" t="s">
+        <v>9</v>
+      </c>
+      <c r="C124">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="125" spans="1:5">
+      <c r="A125">
+        <f t="shared" ref="A125:A132" si="5">A124+1</f>
+        <v>123</v>
+      </c>
+      <c r="B125" t="s">
+        <v>10</v>
+      </c>
+      <c r="C125">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="126" spans="1:5">
+      <c r="A126">
+        <f t="shared" si="5"/>
+        <v>124</v>
+      </c>
+      <c r="B126" t="s">
+        <v>10</v>
+      </c>
+      <c r="C126">
+        <v>0</v>
+      </c>
+      <c r="E126" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="127" spans="1:5">
+      <c r="A127">
+        <f t="shared" si="5"/>
+        <v>125</v>
+      </c>
+      <c r="B127" t="s">
+        <v>11</v>
+      </c>
+      <c r="C127">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="128" spans="1:5">
+      <c r="A128">
+        <f t="shared" si="5"/>
+        <v>126</v>
+      </c>
+      <c r="B128" t="s">
+        <v>8</v>
+      </c>
+      <c r="C128">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3">
+      <c r="A129">
+        <f t="shared" si="5"/>
+        <v>127</v>
+      </c>
+      <c r="B129" t="s">
+        <v>9</v>
+      </c>
+      <c r="C129">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3">
+      <c r="A130">
+        <f t="shared" si="5"/>
+        <v>128</v>
+      </c>
+      <c r="B130" t="s">
+        <v>9</v>
+      </c>
+      <c r="C130">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3">
+      <c r="A131">
+        <f t="shared" si="5"/>
+        <v>129</v>
+      </c>
+      <c r="B131" t="s">
+        <v>11</v>
+      </c>
+      <c r="C131">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3">
+      <c r="A132">
+        <f t="shared" si="5"/>
+        <v>130</v>
+      </c>
+      <c r="B132" t="s">
+        <v>9</v>
+      </c>
+      <c r="C132">
         <v>1</v>
       </c>
     </row>

--- a/l_r/1st.xlsx
+++ b/l_r/1st.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\l_r\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BA5B787-1278-40DE-BA55-000886D44E39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE2C538F-2069-4269-AAEC-F64B6D33603C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-450" yWindow="0" windowWidth="17715" windowHeight="15585" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="330" yWindow="0" windowWidth="12315" windowHeight="15585" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="3" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="59">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -5349,7 +5349,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C7A3EDD-6597-4754-A609-A225833ECC81}">
-  <dimension ref="A2:H132"/>
+  <dimension ref="A2:H142"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="2" spans="1:4">
@@ -6882,6 +6882,80 @@
       </c>
       <c r="C132">
         <v>1</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3">
+      <c r="A133">
+        <v>131</v>
+      </c>
+      <c r="B133" t="s">
+        <v>9</v>
+      </c>
+      <c r="C133">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="134" spans="1:3">
+      <c r="A134">
+        <v>132</v>
+      </c>
+      <c r="B134" t="s">
+        <v>8</v>
+      </c>
+      <c r="C134">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="135" spans="1:3">
+      <c r="A135">
+        <v>133</v>
+      </c>
+      <c r="B135" t="s">
+        <v>8</v>
+      </c>
+      <c r="C135">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="136" spans="1:3">
+      <c r="A136">
+        <v>134</v>
+      </c>
+      <c r="B136" t="s">
+        <v>10</v>
+      </c>
+      <c r="C136">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="137" spans="1:3">
+      <c r="A137">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="138" spans="1:3">
+      <c r="A138">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="139" spans="1:3">
+      <c r="A139">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="140" spans="1:3">
+      <c r="A140">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="141" spans="1:3">
+      <c r="A141">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="142" spans="1:3">
+      <c r="A142">
+        <v>140</v>
       </c>
     </row>
   </sheetData>

--- a/l_r/1st.xlsx
+++ b/l_r/1st.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\l_r\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE2C538F-2069-4269-AAEC-F64B6D33603C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AE6F68B-257C-4941-A314-B1514F9E6C8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="330" yWindow="0" windowWidth="12315" windowHeight="15585" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="855" yWindow="4530" windowWidth="21600" windowHeight="11295" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="3" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="61">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -284,6 +284,14 @@
   </si>
   <si>
     <t>enroll in</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>commend</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ほめる</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -6836,7 +6844,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="129" spans="1:3">
+    <row r="129" spans="1:7">
       <c r="A129">
         <f t="shared" si="5"/>
         <v>127</v>
@@ -6848,7 +6856,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="130" spans="1:3">
+    <row r="130" spans="1:7">
       <c r="A130">
         <f t="shared" si="5"/>
         <v>128</v>
@@ -6860,7 +6868,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="131" spans="1:3">
+    <row r="131" spans="1:7">
       <c r="A131">
         <f t="shared" si="5"/>
         <v>129</v>
@@ -6872,7 +6880,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="132" spans="1:3">
+    <row r="132" spans="1:7">
       <c r="A132">
         <f t="shared" si="5"/>
         <v>130</v>
@@ -6884,7 +6892,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="133" spans="1:3">
+    <row r="133" spans="1:7">
       <c r="A133">
         <v>131</v>
       </c>
@@ -6894,8 +6902,14 @@
       <c r="C133">
         <v>1</v>
       </c>
-    </row>
-    <row r="134" spans="1:3">
+      <c r="F133" t="s">
+        <v>59</v>
+      </c>
+      <c r="G133" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="134" spans="1:7">
       <c r="A134">
         <v>132</v>
       </c>
@@ -6906,7 +6920,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="135" spans="1:3">
+    <row r="135" spans="1:7">
       <c r="A135">
         <v>133</v>
       </c>
@@ -6917,7 +6931,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="136" spans="1:3">
+    <row r="136" spans="1:7">
       <c r="A136">
         <v>134</v>
       </c>
@@ -6928,32 +6942,56 @@
         <v>1</v>
       </c>
     </row>
-    <row r="137" spans="1:3">
+    <row r="137" spans="1:7">
       <c r="A137">
         <v>135</v>
       </c>
-    </row>
-    <row r="138" spans="1:3">
+      <c r="B137" t="s">
+        <v>9</v>
+      </c>
+      <c r="C137">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="138" spans="1:7">
       <c r="A138">
         <v>136</v>
       </c>
-    </row>
-    <row r="139" spans="1:3">
+      <c r="B138" t="s">
+        <v>10</v>
+      </c>
+      <c r="C138">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="139" spans="1:7">
       <c r="A139">
         <v>137</v>
       </c>
-    </row>
-    <row r="140" spans="1:3">
+      <c r="B139" t="s">
+        <v>11</v>
+      </c>
+      <c r="C139">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="140" spans="1:7">
       <c r="A140">
         <v>138</v>
       </c>
-    </row>
-    <row r="141" spans="1:3">
+      <c r="B140" t="s">
+        <v>11</v>
+      </c>
+      <c r="C140">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="141" spans="1:7">
       <c r="A141">
         <v>139</v>
       </c>
     </row>
-    <row r="142" spans="1:3">
+    <row r="142" spans="1:7">
       <c r="A142">
         <v>140</v>
       </c>

--- a/l_r/1st.xlsx
+++ b/l_r/1st.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\l_r\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AE6F68B-257C-4941-A314-B1514F9E6C8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9C7DFFE-E7CC-425D-B7BE-5CDAB7F0B098}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="855" yWindow="4530" windowWidth="21600" windowHeight="11295" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="615" yWindow="0" windowWidth="14460" windowHeight="15585" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="3" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="61">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -5357,7 +5357,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C7A3EDD-6597-4754-A609-A225833ECC81}">
-  <dimension ref="A2:H142"/>
+  <dimension ref="A2:H144"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="2" spans="1:4">
@@ -6990,10 +6990,44 @@
       <c r="A141">
         <v>139</v>
       </c>
+      <c r="B141" t="s">
+        <v>8</v>
+      </c>
+      <c r="C141">
+        <v>1</v>
+      </c>
     </row>
     <row r="142" spans="1:7">
       <c r="A142">
         <v>140</v>
+      </c>
+      <c r="B142" t="s">
+        <v>11</v>
+      </c>
+      <c r="C142">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="143" spans="1:7">
+      <c r="A143">
+        <v>141</v>
+      </c>
+      <c r="B143" t="s">
+        <v>9</v>
+      </c>
+      <c r="C143">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="144" spans="1:7">
+      <c r="A144">
+        <v>142</v>
+      </c>
+      <c r="B144" t="s">
+        <v>8</v>
+      </c>
+      <c r="C144">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/l_r/1st.xlsx
+++ b/l_r/1st.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\l_r\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9C7DFFE-E7CC-425D-B7BE-5CDAB7F0B098}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BEFB8E8F-23FD-4FF2-A34B-2540AAC6A17C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="615" yWindow="0" windowWidth="14460" windowHeight="15585" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="195" windowWidth="16815" windowHeight="15345" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="3" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="62">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -292,6 +292,13 @@
   </si>
   <si>
     <t>ほめる</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>賞賛する</t>
+    <rPh sb="0" eb="2">
+      <t>ショウサン</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -5357,7 +5364,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C7A3EDD-6597-4754-A609-A225833ECC81}">
-  <dimension ref="A2:H144"/>
+  <dimension ref="A2:H148"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="2" spans="1:4">
@@ -6844,7 +6851,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="129" spans="1:7">
+    <row r="129" spans="1:8">
       <c r="A129">
         <f t="shared" si="5"/>
         <v>127</v>
@@ -6856,7 +6863,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="130" spans="1:7">
+    <row r="130" spans="1:8">
       <c r="A130">
         <f t="shared" si="5"/>
         <v>128</v>
@@ -6868,7 +6875,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="131" spans="1:7">
+    <row r="131" spans="1:8">
       <c r="A131">
         <f t="shared" si="5"/>
         <v>129</v>
@@ -6880,7 +6887,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="132" spans="1:7">
+    <row r="132" spans="1:8">
       <c r="A132">
         <f t="shared" si="5"/>
         <v>130</v>
@@ -6892,7 +6899,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="133" spans="1:7">
+    <row r="133" spans="1:8">
       <c r="A133">
         <v>131</v>
       </c>
@@ -6909,7 +6916,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="134" spans="1:7">
+    <row r="134" spans="1:8">
       <c r="A134">
         <v>132</v>
       </c>
@@ -6920,7 +6927,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="135" spans="1:7">
+    <row r="135" spans="1:8">
       <c r="A135">
         <v>133</v>
       </c>
@@ -6931,7 +6938,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="136" spans="1:7">
+    <row r="136" spans="1:8">
       <c r="A136">
         <v>134</v>
       </c>
@@ -6942,7 +6949,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="137" spans="1:7">
+    <row r="137" spans="1:8">
       <c r="A137">
         <v>135</v>
       </c>
@@ -6953,7 +6960,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="138" spans="1:7">
+    <row r="138" spans="1:8">
       <c r="A138">
         <v>136</v>
       </c>
@@ -6964,7 +6971,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="139" spans="1:7">
+    <row r="139" spans="1:8">
       <c r="A139">
         <v>137</v>
       </c>
@@ -6975,7 +6982,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="140" spans="1:7">
+    <row r="140" spans="1:8">
       <c r="A140">
         <v>138</v>
       </c>
@@ -6986,7 +6993,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="141" spans="1:7">
+    <row r="141" spans="1:8">
       <c r="A141">
         <v>139</v>
       </c>
@@ -6996,8 +7003,14 @@
       <c r="C141">
         <v>1</v>
       </c>
-    </row>
-    <row r="142" spans="1:7">
+      <c r="G141" t="s">
+        <v>59</v>
+      </c>
+      <c r="H141" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="142" spans="1:8">
       <c r="A142">
         <v>140</v>
       </c>
@@ -7008,7 +7021,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="143" spans="1:7">
+    <row r="143" spans="1:8">
       <c r="A143">
         <v>141</v>
       </c>
@@ -7019,7 +7032,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="144" spans="1:7">
+    <row r="144" spans="1:8">
       <c r="A144">
         <v>142</v>
       </c>
@@ -7027,6 +7040,50 @@
         <v>8</v>
       </c>
       <c r="C144">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="145" spans="1:3">
+      <c r="A145">
+        <v>135</v>
+      </c>
+      <c r="B145" t="s">
+        <v>9</v>
+      </c>
+      <c r="C145">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="146" spans="1:3">
+      <c r="A146">
+        <v>136</v>
+      </c>
+      <c r="B146" t="s">
+        <v>10</v>
+      </c>
+      <c r="C146">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="147" spans="1:3">
+      <c r="A147">
+        <v>137</v>
+      </c>
+      <c r="B147" t="s">
+        <v>9</v>
+      </c>
+      <c r="C147">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="148" spans="1:3">
+      <c r="A148">
+        <v>138</v>
+      </c>
+      <c r="B148" t="s">
+        <v>11</v>
+      </c>
+      <c r="C148">
         <v>1</v>
       </c>
     </row>

--- a/l_r/1st.xlsx
+++ b/l_r/1st.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\l_r\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BEFB8E8F-23FD-4FF2-A34B-2540AAC6A17C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B6C42C7-2F01-4F10-811D-7E1FFB3C550D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="195" windowWidth="16815" windowHeight="15345" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="705" yWindow="225" windowWidth="16815" windowHeight="15345" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="3" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="62">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -5364,7 +5364,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C7A3EDD-6597-4754-A609-A225833ECC81}">
-  <dimension ref="A2:H148"/>
+  <dimension ref="A2:H152"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="2" spans="1:4">
@@ -7084,6 +7084,50 @@
         <v>11</v>
       </c>
       <c r="C148">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="149" spans="1:3">
+      <c r="A149">
+        <v>139</v>
+      </c>
+      <c r="B149" t="s">
+        <v>8</v>
+      </c>
+      <c r="C149">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="150" spans="1:3">
+      <c r="A150">
+        <v>140</v>
+      </c>
+      <c r="B150" t="s">
+        <v>11</v>
+      </c>
+      <c r="C150">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="151" spans="1:3">
+      <c r="A151">
+        <v>141</v>
+      </c>
+      <c r="B151" t="s">
+        <v>9</v>
+      </c>
+      <c r="C151">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="152" spans="1:3">
+      <c r="A152">
+        <v>142</v>
+      </c>
+      <c r="B152" t="s">
+        <v>8</v>
+      </c>
+      <c r="C152">
         <v>1</v>
       </c>
     </row>

--- a/l_r/1st.xlsx
+++ b/l_r/1st.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\l_r\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B6C42C7-2F01-4F10-811D-7E1FFB3C550D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76AA5393-E316-4A3D-99AB-C467DCF771FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="705" yWindow="225" windowWidth="16815" windowHeight="15345" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="705" yWindow="135" windowWidth="16815" windowHeight="15345" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="3" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="62">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -5364,7 +5364,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C7A3EDD-6597-4754-A609-A225833ECC81}">
-  <dimension ref="A2:H152"/>
+  <dimension ref="A2:H156"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="2" spans="1:4">
@@ -7129,6 +7129,54 @@
       </c>
       <c r="C152">
         <v>1</v>
+      </c>
+    </row>
+    <row r="153" spans="1:3">
+      <c r="A153">
+        <f>A152+1</f>
+        <v>143</v>
+      </c>
+      <c r="B153" t="s">
+        <v>10</v>
+      </c>
+      <c r="C153">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="154" spans="1:3">
+      <c r="A154">
+        <f t="shared" ref="A154:A156" si="6">A153+1</f>
+        <v>144</v>
+      </c>
+      <c r="B154" t="s">
+        <v>10</v>
+      </c>
+      <c r="C154">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="155" spans="1:3">
+      <c r="A155">
+        <f t="shared" si="6"/>
+        <v>145</v>
+      </c>
+      <c r="B155" t="s">
+        <v>10</v>
+      </c>
+      <c r="C155">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="156" spans="1:3">
+      <c r="A156">
+        <f t="shared" si="6"/>
+        <v>146</v>
+      </c>
+      <c r="B156" t="s">
+        <v>8</v>
+      </c>
+      <c r="C156">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/l_r/1st.xlsx
+++ b/l_r/1st.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\l_r\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76AA5393-E316-4A3D-99AB-C467DCF771FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA5D4540-D29F-4CBF-B4E7-126E78E197F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="705" yWindow="135" windowWidth="16815" windowHeight="15345" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="62">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -5364,7 +5364,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C7A3EDD-6597-4754-A609-A225833ECC81}">
-  <dimension ref="A2:H156"/>
+  <dimension ref="A2:H160"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="2" spans="1:4">
@@ -7177,6 +7177,53 @@
       </c>
       <c r="C156">
         <v>0</v>
+      </c>
+    </row>
+    <row r="157" spans="1:3">
+      <c r="A157">
+        <v>131</v>
+      </c>
+      <c r="B157" t="s">
+        <v>9</v>
+      </c>
+      <c r="C157">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="158" spans="1:3">
+      <c r="A158">
+        <f>A157+1</f>
+        <v>132</v>
+      </c>
+      <c r="B158" t="s">
+        <v>8</v>
+      </c>
+      <c r="C158">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="159" spans="1:3">
+      <c r="A159">
+        <f t="shared" ref="A159:A160" si="7">A158+1</f>
+        <v>133</v>
+      </c>
+      <c r="B159" t="s">
+        <v>8</v>
+      </c>
+      <c r="C159">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="160" spans="1:3">
+      <c r="A160">
+        <f t="shared" si="7"/>
+        <v>134</v>
+      </c>
+      <c r="B160" t="s">
+        <v>10</v>
+      </c>
+      <c r="C160">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/l_r/1st.xlsx
+++ b/l_r/1st.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\l_r\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA5D4540-D29F-4CBF-B4E7-126E78E197F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30B3FE73-8D92-4C9F-BA3D-050BF96391C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="705" yWindow="135" windowWidth="16815" windowHeight="15345" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="62">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -5364,7 +5364,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C7A3EDD-6597-4754-A609-A225833ECC81}">
-  <dimension ref="A2:H160"/>
+  <dimension ref="A2:H164"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="2" spans="1:4">
@@ -7204,7 +7204,7 @@
     </row>
     <row r="159" spans="1:3">
       <c r="A159">
-        <f t="shared" ref="A159:A160" si="7">A158+1</f>
+        <f t="shared" ref="A159:A164" si="7">A158+1</f>
         <v>133</v>
       </c>
       <c r="B159" t="s">
@@ -7223,6 +7223,54 @@
         <v>10</v>
       </c>
       <c r="C160">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="161" spans="1:3">
+      <c r="A161">
+        <f t="shared" si="7"/>
+        <v>135</v>
+      </c>
+      <c r="B161" t="s">
+        <v>8</v>
+      </c>
+      <c r="C161">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="162" spans="1:3">
+      <c r="A162">
+        <f t="shared" si="7"/>
+        <v>136</v>
+      </c>
+      <c r="B162" t="s">
+        <v>10</v>
+      </c>
+      <c r="C162">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="163" spans="1:3">
+      <c r="A163">
+        <f t="shared" si="7"/>
+        <v>137</v>
+      </c>
+      <c r="B163" t="s">
+        <v>11</v>
+      </c>
+      <c r="C163">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="164" spans="1:3">
+      <c r="A164">
+        <f t="shared" si="7"/>
+        <v>138</v>
+      </c>
+      <c r="B164" t="s">
+        <v>11</v>
+      </c>
+      <c r="C164">
         <v>1</v>
       </c>
     </row>

--- a/l_r/1st.xlsx
+++ b/l_r/1st.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\l_r\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30B3FE73-8D92-4C9F-BA3D-050BF96391C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF474A25-6253-46E8-8191-455CE2D38F71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="705" yWindow="135" windowWidth="16815" windowHeight="15345" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="295" uniqueCount="62">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -5364,7 +5364,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C7A3EDD-6597-4754-A609-A225833ECC81}">
-  <dimension ref="A2:H164"/>
+  <dimension ref="A2:H168"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="2" spans="1:4">
@@ -7204,7 +7204,7 @@
     </row>
     <row r="159" spans="1:3">
       <c r="A159">
-        <f t="shared" ref="A159:A164" si="7">A158+1</f>
+        <f t="shared" ref="A159:A168" si="7">A158+1</f>
         <v>133</v>
       </c>
       <c r="B159" t="s">
@@ -7274,9 +7274,57 @@
         <v>1</v>
       </c>
     </row>
+    <row r="165" spans="1:3">
+      <c r="A165">
+        <f>A164+1</f>
+        <v>139</v>
+      </c>
+      <c r="B165" t="s">
+        <v>8</v>
+      </c>
+      <c r="C165">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="166" spans="1:3">
+      <c r="A166">
+        <f t="shared" ref="A166:A168" si="8">A165+1</f>
+        <v>140</v>
+      </c>
+      <c r="B166" t="s">
+        <v>11</v>
+      </c>
+      <c r="C166">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="167" spans="1:3">
+      <c r="A167">
+        <f t="shared" si="8"/>
+        <v>141</v>
+      </c>
+      <c r="B167" t="s">
+        <v>11</v>
+      </c>
+      <c r="C167">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="168" spans="1:3">
+      <c r="A168">
+        <f t="shared" si="8"/>
+        <v>142</v>
+      </c>
+      <c r="B168" t="s">
+        <v>8</v>
+      </c>
+      <c r="C168">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1"/>
-  <dataValidations count="1">
+  <dataValidations disablePrompts="1" count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B56:B59 B41:B50 B20:B32 B3:B17" xr:uid="{D8C212E3-0513-4E96-9660-7E8BB94F20D2}">
       <formula1>"A,B,C,D"</formula1>
     </dataValidation>

--- a/l_r/1st.xlsx
+++ b/l_r/1st.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\l_r\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF474A25-6253-46E8-8191-455CE2D38F71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F89B841-C3F9-4021-BA86-5851CE074774}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="705" yWindow="135" windowWidth="16815" windowHeight="15345" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="295" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="62">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -5364,7 +5364,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C7A3EDD-6597-4754-A609-A225833ECC81}">
-  <dimension ref="A2:H168"/>
+  <dimension ref="A2:H172"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="2" spans="1:4">
@@ -7204,7 +7204,7 @@
     </row>
     <row r="159" spans="1:3">
       <c r="A159">
-        <f t="shared" ref="A159:A168" si="7">A158+1</f>
+        <f t="shared" ref="A159:A164" si="7">A158+1</f>
         <v>133</v>
       </c>
       <c r="B159" t="s">
@@ -7288,7 +7288,7 @@
     </row>
     <row r="166" spans="1:3">
       <c r="A166">
-        <f t="shared" ref="A166:A168" si="8">A165+1</f>
+        <f t="shared" ref="A166:A172" si="8">A165+1</f>
         <v>140</v>
       </c>
       <c r="B166" t="s">
@@ -7312,13 +7312,61 @@
     </row>
     <row r="168" spans="1:3">
       <c r="A168">
-        <f t="shared" si="8"/>
+        <f>A167+1</f>
         <v>142</v>
       </c>
       <c r="B168" t="s">
         <v>8</v>
       </c>
       <c r="C168">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="169" spans="1:3">
+      <c r="A169">
+        <f t="shared" si="8"/>
+        <v>143</v>
+      </c>
+      <c r="B169" t="s">
+        <v>10</v>
+      </c>
+      <c r="C169">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="170" spans="1:3">
+      <c r="A170">
+        <f t="shared" si="8"/>
+        <v>144</v>
+      </c>
+      <c r="B170" t="s">
+        <v>10</v>
+      </c>
+      <c r="C170">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="171" spans="1:3">
+      <c r="A171">
+        <f t="shared" si="8"/>
+        <v>145</v>
+      </c>
+      <c r="B171" t="s">
+        <v>8</v>
+      </c>
+      <c r="C171">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="172" spans="1:3">
+      <c r="A172">
+        <f t="shared" si="8"/>
+        <v>146</v>
+      </c>
+      <c r="B172" t="s">
+        <v>11</v>
+      </c>
+      <c r="C172">
         <v>1</v>
       </c>
     </row>

--- a/l_r/1st.xlsx
+++ b/l_r/1st.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\l_r\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F89B841-C3F9-4021-BA86-5851CE074774}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CD1E040-F4DC-4CC6-AE40-996D30F4937A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="705" yWindow="135" windowWidth="16815" windowHeight="15345" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="210" yWindow="0" windowWidth="15930" windowHeight="15585" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="3" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="313" uniqueCount="64">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -298,6 +298,20 @@
     <t>賞賛する</t>
     <rPh sb="0" eb="2">
       <t>ショウサン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>narrow down</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>絞り込む</t>
+    <rPh sb="0" eb="1">
+      <t>シボ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>コ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -5364,7 +5378,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C7A3EDD-6597-4754-A609-A225833ECC81}">
-  <dimension ref="A2:H172"/>
+  <dimension ref="A2:H184"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="2" spans="1:4">
@@ -7226,7 +7240,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="161" spans="1:3">
+    <row r="161" spans="1:7">
       <c r="A161">
         <f t="shared" si="7"/>
         <v>135</v>
@@ -7238,7 +7252,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="162" spans="1:3">
+    <row r="162" spans="1:7">
       <c r="A162">
         <f t="shared" si="7"/>
         <v>136</v>
@@ -7250,7 +7264,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="163" spans="1:3">
+    <row r="163" spans="1:7">
       <c r="A163">
         <f t="shared" si="7"/>
         <v>137</v>
@@ -7262,7 +7276,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="164" spans="1:3">
+    <row r="164" spans="1:7">
       <c r="A164">
         <f t="shared" si="7"/>
         <v>138</v>
@@ -7274,7 +7288,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="165" spans="1:3">
+    <row r="165" spans="1:7">
       <c r="A165">
         <f>A164+1</f>
         <v>139</v>
@@ -7286,9 +7300,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="166" spans="1:3">
+    <row r="166" spans="1:7">
       <c r="A166">
-        <f t="shared" ref="A166:A172" si="8">A165+1</f>
+        <f t="shared" ref="A166:A185" si="8">A165+1</f>
         <v>140</v>
       </c>
       <c r="B166" t="s">
@@ -7298,7 +7312,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="167" spans="1:3">
+    <row r="167" spans="1:7">
       <c r="A167">
         <f t="shared" si="8"/>
         <v>141</v>
@@ -7310,7 +7324,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="168" spans="1:3">
+    <row r="168" spans="1:7">
       <c r="A168">
         <f>A167+1</f>
         <v>142</v>
@@ -7322,7 +7336,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="169" spans="1:3">
+    <row r="169" spans="1:7">
       <c r="A169">
         <f t="shared" si="8"/>
         <v>143</v>
@@ -7334,7 +7348,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="170" spans="1:3">
+    <row r="170" spans="1:7">
       <c r="A170">
         <f t="shared" si="8"/>
         <v>144</v>
@@ -7346,7 +7360,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="171" spans="1:3">
+    <row r="171" spans="1:7">
       <c r="A171">
         <f t="shared" si="8"/>
         <v>145</v>
@@ -7358,7 +7372,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="172" spans="1:3">
+    <row r="172" spans="1:7">
       <c r="A172">
         <f t="shared" si="8"/>
         <v>146</v>
@@ -7367,6 +7381,155 @@
         <v>11</v>
       </c>
       <c r="C172">
+        <v>1</v>
+      </c>
+      <c r="F172" t="s">
+        <v>62</v>
+      </c>
+      <c r="G172" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="173" spans="1:7">
+      <c r="A173">
+        <v>164</v>
+      </c>
+      <c r="B173" t="s">
+        <v>11</v>
+      </c>
+      <c r="C173">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="174" spans="1:7">
+      <c r="A174">
+        <f t="shared" si="8"/>
+        <v>165</v>
+      </c>
+      <c r="B174" t="s">
+        <v>8</v>
+      </c>
+      <c r="C174">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="175" spans="1:7">
+      <c r="A175">
+        <f t="shared" si="8"/>
+        <v>166</v>
+      </c>
+      <c r="B175" t="s">
+        <v>11</v>
+      </c>
+      <c r="C175">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="176" spans="1:7">
+      <c r="A176">
+        <f t="shared" si="8"/>
+        <v>167</v>
+      </c>
+      <c r="B176" t="s">
+        <v>8</v>
+      </c>
+      <c r="C176">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="177" spans="1:3">
+      <c r="A177">
+        <f t="shared" si="8"/>
+        <v>168</v>
+      </c>
+      <c r="B177" t="s">
+        <v>10</v>
+      </c>
+      <c r="C177">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="178" spans="1:3">
+      <c r="A178">
+        <f t="shared" si="8"/>
+        <v>169</v>
+      </c>
+      <c r="B178" t="s">
+        <v>11</v>
+      </c>
+      <c r="C178">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="179" spans="1:3">
+      <c r="A179">
+        <f t="shared" si="8"/>
+        <v>170</v>
+      </c>
+      <c r="B179" t="s">
+        <v>9</v>
+      </c>
+      <c r="C179">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="180" spans="1:3">
+      <c r="A180">
+        <f t="shared" si="8"/>
+        <v>171</v>
+      </c>
+      <c r="B180" t="s">
+        <v>10</v>
+      </c>
+      <c r="C180">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="181" spans="1:3">
+      <c r="A181">
+        <f t="shared" si="8"/>
+        <v>172</v>
+      </c>
+      <c r="B181" t="s">
+        <v>8</v>
+      </c>
+      <c r="C181">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="182" spans="1:3">
+      <c r="A182">
+        <f t="shared" si="8"/>
+        <v>173</v>
+      </c>
+      <c r="B182" t="s">
+        <v>8</v>
+      </c>
+      <c r="C182">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="183" spans="1:3">
+      <c r="A183">
+        <f t="shared" si="8"/>
+        <v>174</v>
+      </c>
+      <c r="B183" t="s">
+        <v>8</v>
+      </c>
+      <c r="C183">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="184" spans="1:3">
+      <c r="A184">
+        <f t="shared" si="8"/>
+        <v>175</v>
+      </c>
+      <c r="B184" t="s">
+        <v>11</v>
+      </c>
+      <c r="C184">
         <v>1</v>
       </c>
     </row>

--- a/l_r/1st.xlsx
+++ b/l_r/1st.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\l_r\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CD1E040-F4DC-4CC6-AE40-996D30F4937A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{948B8CE5-497A-43D8-A1A2-81A208739C14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="210" yWindow="0" windowWidth="15930" windowHeight="15585" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="210" yWindow="450" windowWidth="21600" windowHeight="11295" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="3" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="313" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="325" uniqueCount="66">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -312,6 +312,17 @@
     </rPh>
     <rPh sb="2" eb="3">
       <t>コ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>on his own</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>一人で</t>
+    <rPh sb="0" eb="2">
+      <t>ヒトリ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -5378,7 +5389,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C7A3EDD-6597-4754-A609-A225833ECC81}">
-  <dimension ref="A2:H184"/>
+  <dimension ref="A2:H194"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="2" spans="1:4">
@@ -7302,7 +7313,7 @@
     </row>
     <row r="166" spans="1:7">
       <c r="A166">
-        <f t="shared" ref="A166:A185" si="8">A165+1</f>
+        <f t="shared" ref="A166:A194" si="8">A165+1</f>
         <v>140</v>
       </c>
       <c r="B166" t="s">
@@ -7437,7 +7448,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="177" spans="1:3">
+    <row r="177" spans="1:7">
       <c r="A177">
         <f t="shared" si="8"/>
         <v>168</v>
@@ -7449,7 +7460,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="178" spans="1:3">
+    <row r="178" spans="1:7">
       <c r="A178">
         <f t="shared" si="8"/>
         <v>169</v>
@@ -7461,7 +7472,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="179" spans="1:3">
+    <row r="179" spans="1:7">
       <c r="A179">
         <f t="shared" si="8"/>
         <v>170</v>
@@ -7473,7 +7484,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="180" spans="1:3">
+    <row r="180" spans="1:7">
       <c r="A180">
         <f t="shared" si="8"/>
         <v>171</v>
@@ -7485,7 +7496,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="181" spans="1:3">
+    <row r="181" spans="1:7">
       <c r="A181">
         <f t="shared" si="8"/>
         <v>172</v>
@@ -7497,7 +7508,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="182" spans="1:3">
+    <row r="182" spans="1:7">
       <c r="A182">
         <f t="shared" si="8"/>
         <v>173</v>
@@ -7509,7 +7520,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="183" spans="1:3">
+    <row r="183" spans="1:7">
       <c r="A183">
         <f t="shared" si="8"/>
         <v>174</v>
@@ -7521,7 +7532,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="184" spans="1:3">
+    <row r="184" spans="1:7">
       <c r="A184">
         <f t="shared" si="8"/>
         <v>175</v>
@@ -7530,6 +7541,131 @@
         <v>11</v>
       </c>
       <c r="C184">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="185" spans="1:7">
+      <c r="A185">
+        <v>101</v>
+      </c>
+      <c r="B185" t="s">
+        <v>8</v>
+      </c>
+      <c r="C185">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="186" spans="1:7">
+      <c r="A186">
+        <f t="shared" si="8"/>
+        <v>102</v>
+      </c>
+      <c r="B186" t="s">
+        <v>9</v>
+      </c>
+      <c r="C186">
+        <v>0</v>
+      </c>
+      <c r="F186" t="s">
+        <v>64</v>
+      </c>
+      <c r="G186" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="187" spans="1:7">
+      <c r="A187">
+        <f t="shared" si="8"/>
+        <v>103</v>
+      </c>
+      <c r="B187" t="s">
+        <v>10</v>
+      </c>
+      <c r="C187">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="188" spans="1:7">
+      <c r="A188">
+        <f t="shared" si="8"/>
+        <v>104</v>
+      </c>
+      <c r="B188" t="s">
+        <v>9</v>
+      </c>
+      <c r="C188">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="189" spans="1:7">
+      <c r="A189">
+        <f t="shared" si="8"/>
+        <v>105</v>
+      </c>
+      <c r="B189" t="s">
+        <v>10</v>
+      </c>
+      <c r="C189">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="190" spans="1:7">
+      <c r="A190">
+        <f t="shared" si="8"/>
+        <v>106</v>
+      </c>
+      <c r="B190" t="s">
+        <v>10</v>
+      </c>
+      <c r="C190">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="191" spans="1:7">
+      <c r="A191">
+        <f t="shared" si="8"/>
+        <v>107</v>
+      </c>
+      <c r="B191" t="s">
+        <v>11</v>
+      </c>
+      <c r="C191">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="192" spans="1:7">
+      <c r="A192">
+        <f t="shared" si="8"/>
+        <v>108</v>
+      </c>
+      <c r="B192" t="s">
+        <v>8</v>
+      </c>
+      <c r="C192">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="193" spans="1:3">
+      <c r="A193">
+        <f t="shared" si="8"/>
+        <v>109</v>
+      </c>
+      <c r="B193" t="s">
+        <v>9</v>
+      </c>
+      <c r="C193">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="194" spans="1:3">
+      <c r="A194">
+        <f t="shared" si="8"/>
+        <v>110</v>
+      </c>
+      <c r="B194" t="s">
+        <v>11</v>
+      </c>
+      <c r="C194">
         <v>1</v>
       </c>
     </row>

--- a/l_r/1st.xlsx
+++ b/l_r/1st.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\l_r\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{948B8CE5-497A-43D8-A1A2-81A208739C14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82ABF5F5-677E-4A39-811B-206870C6D966}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="210" yWindow="450" windowWidth="21600" windowHeight="11295" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1170" yWindow="0" windowWidth="18615" windowHeight="15585" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="3" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="325" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="335" uniqueCount="66">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -5389,7 +5389,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C7A3EDD-6597-4754-A609-A225833ECC81}">
-  <dimension ref="A2:H194"/>
+  <dimension ref="A2:H204"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="2" spans="1:4">
@@ -7313,7 +7313,7 @@
     </row>
     <row r="166" spans="1:7">
       <c r="A166">
-        <f t="shared" ref="A166:A194" si="8">A165+1</f>
+        <f t="shared" ref="A166:A204" si="8">A165+1</f>
         <v>140</v>
       </c>
       <c r="B166" t="s">
@@ -7667,6 +7667,126 @@
       </c>
       <c r="C194">
         <v>1</v>
+      </c>
+    </row>
+    <row r="195" spans="1:3">
+      <c r="A195">
+        <f t="shared" si="8"/>
+        <v>111</v>
+      </c>
+      <c r="B195" t="s">
+        <v>8</v>
+      </c>
+      <c r="C195">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="196" spans="1:3">
+      <c r="A196">
+        <f t="shared" si="8"/>
+        <v>112</v>
+      </c>
+      <c r="B196" t="s">
+        <v>10</v>
+      </c>
+      <c r="C196">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="197" spans="1:3">
+      <c r="A197">
+        <f t="shared" si="8"/>
+        <v>113</v>
+      </c>
+      <c r="B197" t="s">
+        <v>9</v>
+      </c>
+      <c r="C197">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="198" spans="1:3">
+      <c r="A198">
+        <f t="shared" si="8"/>
+        <v>114</v>
+      </c>
+      <c r="B198" t="s">
+        <v>9</v>
+      </c>
+      <c r="C198">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="199" spans="1:3">
+      <c r="A199">
+        <f t="shared" si="8"/>
+        <v>115</v>
+      </c>
+      <c r="B199" t="s">
+        <v>9</v>
+      </c>
+      <c r="C199">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="200" spans="1:3">
+      <c r="A200">
+        <f t="shared" si="8"/>
+        <v>116</v>
+      </c>
+      <c r="B200" t="s">
+        <v>10</v>
+      </c>
+      <c r="C200">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="201" spans="1:3">
+      <c r="A201">
+        <f t="shared" si="8"/>
+        <v>117</v>
+      </c>
+      <c r="B201" t="s">
+        <v>11</v>
+      </c>
+      <c r="C201">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="202" spans="1:3">
+      <c r="A202">
+        <f t="shared" si="8"/>
+        <v>118</v>
+      </c>
+      <c r="B202" t="s">
+        <v>8</v>
+      </c>
+      <c r="C202">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="203" spans="1:3">
+      <c r="A203">
+        <f t="shared" si="8"/>
+        <v>119</v>
+      </c>
+      <c r="B203" t="s">
+        <v>10</v>
+      </c>
+      <c r="C203">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="204" spans="1:3">
+      <c r="A204">
+        <f t="shared" si="8"/>
+        <v>120</v>
+      </c>
+      <c r="B204" t="s">
+        <v>8</v>
+      </c>
+      <c r="C204">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/l_r/1st.xlsx
+++ b/l_r/1st.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\l_r\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82ABF5F5-677E-4A39-811B-206870C6D966}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E1B609C-6D9E-44A0-A02F-03B45D7078C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1170" yWindow="0" windowWidth="18615" windowHeight="15585" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="0" windowWidth="16110" windowHeight="15585" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="3" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="335" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="345" uniqueCount="66">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -5389,7 +5389,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C7A3EDD-6597-4754-A609-A225833ECC81}">
-  <dimension ref="A2:H204"/>
+  <dimension ref="A2:H214"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="2" spans="1:4">
@@ -7313,7 +7313,7 @@
     </row>
     <row r="166" spans="1:7">
       <c r="A166">
-        <f t="shared" ref="A166:A204" si="8">A165+1</f>
+        <f t="shared" ref="A166:A214" si="8">A165+1</f>
         <v>140</v>
       </c>
       <c r="B166" t="s">
@@ -7787,6 +7787,126 @@
       </c>
       <c r="C204">
         <v>0</v>
+      </c>
+    </row>
+    <row r="205" spans="1:3">
+      <c r="A205">
+        <f t="shared" si="8"/>
+        <v>121</v>
+      </c>
+      <c r="B205" t="s">
+        <v>11</v>
+      </c>
+      <c r="C205">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="206" spans="1:3">
+      <c r="A206">
+        <f t="shared" si="8"/>
+        <v>122</v>
+      </c>
+      <c r="B206" t="s">
+        <v>9</v>
+      </c>
+      <c r="C206">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="207" spans="1:3">
+      <c r="A207">
+        <f t="shared" si="8"/>
+        <v>123</v>
+      </c>
+      <c r="B207" t="s">
+        <v>10</v>
+      </c>
+      <c r="C207">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="208" spans="1:3">
+      <c r="A208">
+        <f t="shared" si="8"/>
+        <v>124</v>
+      </c>
+      <c r="B208" t="s">
+        <v>8</v>
+      </c>
+      <c r="C208">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="209" spans="1:3">
+      <c r="A209">
+        <f t="shared" si="8"/>
+        <v>125</v>
+      </c>
+      <c r="B209" t="s">
+        <v>8</v>
+      </c>
+      <c r="C209">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="210" spans="1:3">
+      <c r="A210">
+        <f t="shared" si="8"/>
+        <v>126</v>
+      </c>
+      <c r="B210" t="s">
+        <v>8</v>
+      </c>
+      <c r="C210">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="211" spans="1:3">
+      <c r="A211">
+        <f t="shared" si="8"/>
+        <v>127</v>
+      </c>
+      <c r="B211" t="s">
+        <v>9</v>
+      </c>
+      <c r="C211">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="212" spans="1:3">
+      <c r="A212">
+        <f t="shared" si="8"/>
+        <v>128</v>
+      </c>
+      <c r="B212" t="s">
+        <v>9</v>
+      </c>
+      <c r="C212">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="213" spans="1:3">
+      <c r="A213">
+        <f t="shared" si="8"/>
+        <v>129</v>
+      </c>
+      <c r="B213" t="s">
+        <v>11</v>
+      </c>
+      <c r="C213">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="214" spans="1:3">
+      <c r="A214">
+        <f t="shared" si="8"/>
+        <v>130</v>
+      </c>
+      <c r="B214" t="s">
+        <v>9</v>
+      </c>
+      <c r="C214">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/l_r/1st.xlsx
+++ b/l_r/1st.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\l_r\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E1B609C-6D9E-44A0-A02F-03B45D7078C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{309CFEED-05EB-4267-85CF-D7C86DAF094B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="0" windowWidth="16110" windowHeight="15585" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="12585" windowHeight="15585" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="3" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="345" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="353" uniqueCount="66">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -5389,7 +5389,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C7A3EDD-6597-4754-A609-A225833ECC81}">
-  <dimension ref="A2:H214"/>
+  <dimension ref="A2:H222"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="2" spans="1:4">
@@ -7313,7 +7313,7 @@
     </row>
     <row r="166" spans="1:7">
       <c r="A166">
-        <f t="shared" ref="A166:A214" si="8">A165+1</f>
+        <f t="shared" ref="A166:A222" si="8">A165+1</f>
         <v>140</v>
       </c>
       <c r="B166" t="s">
@@ -7906,6 +7906,102 @@
         <v>9</v>
       </c>
       <c r="C214">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="215" spans="1:3">
+      <c r="A215">
+        <f t="shared" si="8"/>
+        <v>131</v>
+      </c>
+      <c r="B215" t="s">
+        <v>9</v>
+      </c>
+      <c r="C215">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="216" spans="1:3">
+      <c r="A216">
+        <f t="shared" si="8"/>
+        <v>132</v>
+      </c>
+      <c r="B216" t="s">
+        <v>8</v>
+      </c>
+      <c r="C216">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="217" spans="1:3">
+      <c r="A217">
+        <f t="shared" si="8"/>
+        <v>133</v>
+      </c>
+      <c r="B217" t="s">
+        <v>8</v>
+      </c>
+      <c r="C217">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="218" spans="1:3">
+      <c r="A218">
+        <f t="shared" si="8"/>
+        <v>134</v>
+      </c>
+      <c r="B218" t="s">
+        <v>10</v>
+      </c>
+      <c r="C218">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="219" spans="1:3">
+      <c r="A219">
+        <f t="shared" si="8"/>
+        <v>135</v>
+      </c>
+      <c r="B219" t="s">
+        <v>9</v>
+      </c>
+      <c r="C219">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="220" spans="1:3">
+      <c r="A220">
+        <f t="shared" si="8"/>
+        <v>136</v>
+      </c>
+      <c r="B220" t="s">
+        <v>10</v>
+      </c>
+      <c r="C220">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="221" spans="1:3">
+      <c r="A221">
+        <f t="shared" si="8"/>
+        <v>137</v>
+      </c>
+      <c r="B221" t="s">
+        <v>11</v>
+      </c>
+      <c r="C221">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="222" spans="1:3">
+      <c r="A222">
+        <f t="shared" si="8"/>
+        <v>138</v>
+      </c>
+      <c r="B222" t="s">
+        <v>11</v>
+      </c>
+      <c r="C222">
         <v>1</v>
       </c>
     </row>

--- a/l_r/1st.xlsx
+++ b/l_r/1st.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\l_r\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{309CFEED-05EB-4267-85CF-D7C86DAF094B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{881BF884-46BA-4DB6-80A5-3B212EE83ED6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="12585" windowHeight="15585" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="13950" yWindow="0" windowWidth="14685" windowHeight="15585" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="3" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="353" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="373" uniqueCount="66">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -5389,7 +5389,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C7A3EDD-6597-4754-A609-A225833ECC81}">
-  <dimension ref="A2:H222"/>
+  <dimension ref="A2:H242"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="2" spans="1:4">
@@ -7313,7 +7313,7 @@
     </row>
     <row r="166" spans="1:7">
       <c r="A166">
-        <f t="shared" ref="A166:A222" si="8">A165+1</f>
+        <f t="shared" ref="A166:A229" si="8">A165+1</f>
         <v>140</v>
       </c>
       <c r="B166" t="s">
@@ -8002,6 +8002,240 @@
         <v>11</v>
       </c>
       <c r="C222">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="223" spans="1:3">
+      <c r="A223">
+        <f t="shared" si="8"/>
+        <v>139</v>
+      </c>
+      <c r="B223" t="s">
+        <v>8</v>
+      </c>
+      <c r="C223">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="224" spans="1:3">
+      <c r="A224">
+        <f t="shared" si="8"/>
+        <v>140</v>
+      </c>
+      <c r="B224" t="s">
+        <v>11</v>
+      </c>
+      <c r="C224">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="225" spans="1:3">
+      <c r="A225">
+        <f t="shared" si="8"/>
+        <v>141</v>
+      </c>
+      <c r="B225" t="s">
+        <v>9</v>
+      </c>
+      <c r="C225">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="226" spans="1:3">
+      <c r="A226">
+        <f t="shared" si="8"/>
+        <v>142</v>
+      </c>
+      <c r="B226" t="s">
+        <v>8</v>
+      </c>
+      <c r="C226">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="227" spans="1:3">
+      <c r="A227">
+        <f t="shared" si="8"/>
+        <v>143</v>
+      </c>
+      <c r="B227" t="s">
+        <v>10</v>
+      </c>
+      <c r="C227">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="228" spans="1:3">
+      <c r="A228">
+        <f t="shared" si="8"/>
+        <v>144</v>
+      </c>
+      <c r="B228" t="s">
+        <v>10</v>
+      </c>
+      <c r="C228">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="229" spans="1:3">
+      <c r="A229">
+        <f t="shared" si="8"/>
+        <v>145</v>
+      </c>
+      <c r="B229" t="s">
+        <v>8</v>
+      </c>
+      <c r="C229">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="230" spans="1:3">
+      <c r="A230">
+        <f t="shared" ref="A230:A238" si="9">A229+1</f>
+        <v>146</v>
+      </c>
+      <c r="B230" t="s">
+        <v>11</v>
+      </c>
+      <c r="C230">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="231" spans="1:3">
+      <c r="A231">
+        <v>143</v>
+      </c>
+      <c r="B231" t="s">
+        <v>10</v>
+      </c>
+      <c r="C231">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="232" spans="1:3">
+      <c r="A232">
+        <f t="shared" si="9"/>
+        <v>144</v>
+      </c>
+      <c r="B232" t="s">
+        <v>10</v>
+      </c>
+      <c r="C232">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="233" spans="1:3">
+      <c r="A233">
+        <f t="shared" si="9"/>
+        <v>145</v>
+      </c>
+      <c r="B233" t="s">
+        <v>8</v>
+      </c>
+      <c r="C233">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="234" spans="1:3">
+      <c r="A234">
+        <f t="shared" si="9"/>
+        <v>146</v>
+      </c>
+      <c r="B234" t="s">
+        <v>11</v>
+      </c>
+      <c r="C234">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="235" spans="1:3">
+      <c r="A235">
+        <v>135</v>
+      </c>
+      <c r="B235" t="s">
+        <v>10</v>
+      </c>
+      <c r="C235">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="236" spans="1:3">
+      <c r="A236">
+        <f t="shared" si="9"/>
+        <v>136</v>
+      </c>
+      <c r="B236" t="s">
+        <v>10</v>
+      </c>
+      <c r="C236">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="237" spans="1:3">
+      <c r="A237">
+        <f t="shared" si="9"/>
+        <v>137</v>
+      </c>
+      <c r="B237" t="s">
+        <v>11</v>
+      </c>
+      <c r="C237">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="238" spans="1:3">
+      <c r="A238">
+        <f t="shared" si="9"/>
+        <v>138</v>
+      </c>
+      <c r="B238" t="s">
+        <v>11</v>
+      </c>
+      <c r="C238">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="239" spans="1:3">
+      <c r="A239">
+        <v>147</v>
+      </c>
+      <c r="B239" t="s">
+        <v>9</v>
+      </c>
+      <c r="C239">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="240" spans="1:3">
+      <c r="A240">
+        <v>148</v>
+      </c>
+      <c r="B240" t="s">
+        <v>10</v>
+      </c>
+      <c r="C240">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="241" spans="1:3">
+      <c r="A241">
+        <v>149</v>
+      </c>
+      <c r="B241" t="s">
+        <v>10</v>
+      </c>
+      <c r="C241">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="242" spans="1:3">
+      <c r="A242">
+        <v>150</v>
+      </c>
+      <c r="B242" t="s">
+        <v>8</v>
+      </c>
+      <c r="C242">
         <v>1</v>
       </c>
     </row>

--- a/l_r/1st.xlsx
+++ b/l_r/1st.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\l_r\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{881BF884-46BA-4DB6-80A5-3B212EE83ED6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99EFD1F7-184F-4665-856D-41D165A58B4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13950" yWindow="0" windowWidth="14685" windowHeight="15585" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="525" yWindow="0" windowWidth="12135" windowHeight="15585" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="3" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="373" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="380" uniqueCount="66">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -5389,7 +5389,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C7A3EDD-6597-4754-A609-A225833ECC81}">
-  <dimension ref="A2:H242"/>
+  <dimension ref="A2:H249"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="2" spans="1:4">
@@ -8236,6 +8236,90 @@
         <v>8</v>
       </c>
       <c r="C242">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="243" spans="1:3">
+      <c r="A243">
+        <f>A242+1</f>
+        <v>151</v>
+      </c>
+      <c r="B243" t="s">
+        <v>11</v>
+      </c>
+      <c r="C243">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="244" spans="1:3">
+      <c r="A244">
+        <f>A243+1</f>
+        <v>152</v>
+      </c>
+      <c r="B244" t="s">
+        <v>8</v>
+      </c>
+      <c r="C244">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="245" spans="1:3">
+      <c r="A245">
+        <f t="shared" ref="A245:A249" si="10">A244+1</f>
+        <v>153</v>
+      </c>
+      <c r="B245" t="s">
+        <v>10</v>
+      </c>
+      <c r="C245">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="246" spans="1:3">
+      <c r="A246">
+        <f t="shared" si="10"/>
+        <v>154</v>
+      </c>
+      <c r="B246" t="s">
+        <v>9</v>
+      </c>
+      <c r="C246">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="247" spans="1:3">
+      <c r="A247">
+        <f t="shared" si="10"/>
+        <v>155</v>
+      </c>
+      <c r="B247" t="s">
+        <v>9</v>
+      </c>
+      <c r="C247">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="248" spans="1:3">
+      <c r="A248">
+        <f t="shared" si="10"/>
+        <v>156</v>
+      </c>
+      <c r="B248" t="s">
+        <v>8</v>
+      </c>
+      <c r="C248">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="249" spans="1:3">
+      <c r="A249">
+        <f t="shared" si="10"/>
+        <v>157</v>
+      </c>
+      <c r="B249" t="s">
+        <v>10</v>
+      </c>
+      <c r="C249">
         <v>1</v>
       </c>
     </row>

--- a/l_r/1st.xlsx
+++ b/l_r/1st.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\l_r\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99EFD1F7-184F-4665-856D-41D165A58B4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B8B975D-3E17-4ED4-8250-5027B1B42E0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="525" yWindow="0" windowWidth="12135" windowHeight="15585" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="525" yWindow="690" windowWidth="21600" windowHeight="11295" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="3" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="380" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="386" uniqueCount="66">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -5389,7 +5389,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C7A3EDD-6597-4754-A609-A225833ECC81}">
-  <dimension ref="A2:H249"/>
+  <dimension ref="A2:H255"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="2" spans="1:4">
@@ -8265,7 +8265,7 @@
     </row>
     <row r="245" spans="1:3">
       <c r="A245">
-        <f t="shared" ref="A245:A249" si="10">A244+1</f>
+        <f t="shared" ref="A245:A255" si="10">A244+1</f>
         <v>153</v>
       </c>
       <c r="B245" t="s">
@@ -8320,6 +8320,78 @@
         <v>10</v>
       </c>
       <c r="C249">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="250" spans="1:3">
+      <c r="A250">
+        <f t="shared" si="10"/>
+        <v>158</v>
+      </c>
+      <c r="B250" t="s">
+        <v>11</v>
+      </c>
+      <c r="C250">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="251" spans="1:3">
+      <c r="A251">
+        <f t="shared" si="10"/>
+        <v>159</v>
+      </c>
+      <c r="B251" t="s">
+        <v>9</v>
+      </c>
+      <c r="C251">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="252" spans="1:3">
+      <c r="A252">
+        <f t="shared" si="10"/>
+        <v>160</v>
+      </c>
+      <c r="B252" t="s">
+        <v>11</v>
+      </c>
+      <c r="C252">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="253" spans="1:3">
+      <c r="A253">
+        <f t="shared" si="10"/>
+        <v>161</v>
+      </c>
+      <c r="B253" t="s">
+        <v>11</v>
+      </c>
+      <c r="C253">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="254" spans="1:3">
+      <c r="A254">
+        <f t="shared" si="10"/>
+        <v>162</v>
+      </c>
+      <c r="B254" t="s">
+        <v>9</v>
+      </c>
+      <c r="C254">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="255" spans="1:3">
+      <c r="A255">
+        <f t="shared" si="10"/>
+        <v>163</v>
+      </c>
+      <c r="B255" t="s">
+        <v>8</v>
+      </c>
+      <c r="C255">
         <v>1</v>
       </c>
     </row>

--- a/l_r/1st.xlsx
+++ b/l_r/1st.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\l_r\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B8B975D-3E17-4ED4-8250-5027B1B42E0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B28E32EA-FDBF-41D2-8E64-D26374A93D74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="525" yWindow="690" windowWidth="21600" windowHeight="11295" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8160" yWindow="75" windowWidth="21600" windowHeight="11295" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="3" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="386" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="394" uniqueCount="66">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -5389,7 +5389,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C7A3EDD-6597-4754-A609-A225833ECC81}">
-  <dimension ref="A2:H255"/>
+  <dimension ref="A2:H263"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="2" spans="1:4">
@@ -8265,7 +8265,7 @@
     </row>
     <row r="245" spans="1:3">
       <c r="A245">
-        <f t="shared" ref="A245:A255" si="10">A244+1</f>
+        <f t="shared" ref="A245:A263" si="10">A244+1</f>
         <v>153</v>
       </c>
       <c r="B245" t="s">
@@ -8392,6 +8392,102 @@
         <v>8</v>
       </c>
       <c r="C255">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="256" spans="1:3">
+      <c r="A256">
+        <f t="shared" si="10"/>
+        <v>164</v>
+      </c>
+      <c r="B256" t="s">
+        <v>11</v>
+      </c>
+      <c r="C256">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="257" spans="1:3">
+      <c r="A257">
+        <f t="shared" si="10"/>
+        <v>165</v>
+      </c>
+      <c r="B257" t="s">
+        <v>8</v>
+      </c>
+      <c r="C257">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="258" spans="1:3">
+      <c r="A258">
+        <f t="shared" si="10"/>
+        <v>166</v>
+      </c>
+      <c r="B258" t="s">
+        <v>10</v>
+      </c>
+      <c r="C258">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="259" spans="1:3">
+      <c r="A259">
+        <f t="shared" si="10"/>
+        <v>167</v>
+      </c>
+      <c r="B259" t="s">
+        <v>9</v>
+      </c>
+      <c r="C259">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="260" spans="1:3">
+      <c r="A260">
+        <f t="shared" si="10"/>
+        <v>168</v>
+      </c>
+      <c r="B260" t="s">
+        <v>10</v>
+      </c>
+      <c r="C260">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="261" spans="1:3">
+      <c r="A261">
+        <f t="shared" si="10"/>
+        <v>169</v>
+      </c>
+      <c r="B261" t="s">
+        <v>11</v>
+      </c>
+      <c r="C261">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="262" spans="1:3">
+      <c r="A262">
+        <f t="shared" si="10"/>
+        <v>170</v>
+      </c>
+      <c r="B262" t="s">
+        <v>9</v>
+      </c>
+      <c r="C262">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="263" spans="1:3">
+      <c r="A263">
+        <f t="shared" si="10"/>
+        <v>171</v>
+      </c>
+      <c r="B263" t="s">
+        <v>9</v>
+      </c>
+      <c r="C263">
         <v>1</v>
       </c>
     </row>

--- a/l_r/1st.xlsx
+++ b/l_r/1st.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\l_r\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B28E32EA-FDBF-41D2-8E64-D26374A93D74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0163887-B911-44C1-B09C-59642C56BF19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8160" yWindow="75" windowWidth="21600" windowHeight="11295" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="1260" windowWidth="21600" windowHeight="11295" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="3" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="394" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="403" uniqueCount="66">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -5389,7 +5389,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C7A3EDD-6597-4754-A609-A225833ECC81}">
-  <dimension ref="A2:H263"/>
+  <dimension ref="A2:H272"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="2" spans="1:4">
@@ -8265,7 +8265,7 @@
     </row>
     <row r="245" spans="1:3">
       <c r="A245">
-        <f t="shared" ref="A245:A263" si="10">A244+1</f>
+        <f t="shared" ref="A245:A272" si="10">A244+1</f>
         <v>153</v>
       </c>
       <c r="B245" t="s">
@@ -8488,6 +8488,114 @@
         <v>9</v>
       </c>
       <c r="C263">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="264" spans="1:3">
+      <c r="A264">
+        <f t="shared" si="10"/>
+        <v>172</v>
+      </c>
+      <c r="B264" t="s">
+        <v>8</v>
+      </c>
+      <c r="C264">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="265" spans="1:3">
+      <c r="A265">
+        <f t="shared" si="10"/>
+        <v>173</v>
+      </c>
+      <c r="B265" t="s">
+        <v>10</v>
+      </c>
+      <c r="C265">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="266" spans="1:3">
+      <c r="A266">
+        <f t="shared" si="10"/>
+        <v>174</v>
+      </c>
+      <c r="B266" t="s">
+        <v>8</v>
+      </c>
+      <c r="C266">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="267" spans="1:3">
+      <c r="A267">
+        <f t="shared" si="10"/>
+        <v>175</v>
+      </c>
+      <c r="B267" t="s">
+        <v>9</v>
+      </c>
+      <c r="C267">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="268" spans="1:3">
+      <c r="A268">
+        <f t="shared" si="10"/>
+        <v>176</v>
+      </c>
+      <c r="B268" t="s">
+        <v>10</v>
+      </c>
+      <c r="C268">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="269" spans="1:3">
+      <c r="A269">
+        <f t="shared" si="10"/>
+        <v>177</v>
+      </c>
+      <c r="B269" t="s">
+        <v>8</v>
+      </c>
+      <c r="C269">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="270" spans="1:3">
+      <c r="A270">
+        <f t="shared" si="10"/>
+        <v>178</v>
+      </c>
+      <c r="B270" t="s">
+        <v>9</v>
+      </c>
+      <c r="C270">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="271" spans="1:3">
+      <c r="A271">
+        <f t="shared" si="10"/>
+        <v>179</v>
+      </c>
+      <c r="B271" t="s">
+        <v>10</v>
+      </c>
+      <c r="C271">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="272" spans="1:3">
+      <c r="A272">
+        <f t="shared" si="10"/>
+        <v>180</v>
+      </c>
+      <c r="B272" t="s">
+        <v>9</v>
+      </c>
+      <c r="C272">
         <v>1</v>
       </c>
     </row>

--- a/l_r/1st.xlsx
+++ b/l_r/1st.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\l_r\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0163887-B911-44C1-B09C-59642C56BF19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D9DBE66-41FA-478B-ABA7-F1F05398C8C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="1260" windowWidth="21600" windowHeight="11295" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1260" yWindow="1050" windowWidth="12840" windowHeight="14280" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="3" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="403" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="408" uniqueCount="66">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -5389,7 +5389,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C7A3EDD-6597-4754-A609-A225833ECC81}">
-  <dimension ref="A2:H272"/>
+  <dimension ref="A2:H277"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="2" spans="1:4">
@@ -8265,7 +8265,7 @@
     </row>
     <row r="245" spans="1:3">
       <c r="A245">
-        <f t="shared" ref="A245:A272" si="10">A244+1</f>
+        <f t="shared" ref="A245:A277" si="10">A244+1</f>
         <v>153</v>
       </c>
       <c r="B245" t="s">
@@ -8596,6 +8596,66 @@
         <v>9</v>
       </c>
       <c r="C272">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="273" spans="1:3">
+      <c r="A273">
+        <f t="shared" si="10"/>
+        <v>181</v>
+      </c>
+      <c r="B273" t="s">
+        <v>11</v>
+      </c>
+      <c r="C273">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="274" spans="1:3">
+      <c r="A274">
+        <f t="shared" si="10"/>
+        <v>182</v>
+      </c>
+      <c r="B274" t="s">
+        <v>11</v>
+      </c>
+      <c r="C274">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="275" spans="1:3">
+      <c r="A275">
+        <f t="shared" si="10"/>
+        <v>183</v>
+      </c>
+      <c r="B275" t="s">
+        <v>11</v>
+      </c>
+      <c r="C275">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="276" spans="1:3">
+      <c r="A276">
+        <f t="shared" si="10"/>
+        <v>184</v>
+      </c>
+      <c r="B276" t="s">
+        <v>11</v>
+      </c>
+      <c r="C276">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="277" spans="1:3">
+      <c r="A277">
+        <f t="shared" si="10"/>
+        <v>185</v>
+      </c>
+      <c r="B277" t="s">
+        <v>10</v>
+      </c>
+      <c r="C277">
         <v>1</v>
       </c>
     </row>

--- a/l_r/1st.xlsx
+++ b/l_r/1st.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\l_r\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D9DBE66-41FA-478B-ABA7-F1F05398C8C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{927D79B1-ECC3-4859-A250-B202CEB97E5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1260" yWindow="1050" windowWidth="12840" windowHeight="14280" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="3" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="408" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="413" uniqueCount="66">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -5389,7 +5389,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C7A3EDD-6597-4754-A609-A225833ECC81}">
-  <dimension ref="A2:H277"/>
+  <dimension ref="A2:H282"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="2" spans="1:4">
@@ -8265,7 +8265,7 @@
     </row>
     <row r="245" spans="1:3">
       <c r="A245">
-        <f t="shared" ref="A245:A277" si="10">A244+1</f>
+        <f t="shared" ref="A245:A282" si="10">A244+1</f>
         <v>153</v>
       </c>
       <c r="B245" t="s">
@@ -8657,6 +8657,66 @@
       </c>
       <c r="C277">
         <v>1</v>
+      </c>
+    </row>
+    <row r="278" spans="1:3">
+      <c r="A278">
+        <f t="shared" si="10"/>
+        <v>186</v>
+      </c>
+      <c r="B278" t="s">
+        <v>10</v>
+      </c>
+      <c r="C278">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="279" spans="1:3">
+      <c r="A279">
+        <f t="shared" si="10"/>
+        <v>187</v>
+      </c>
+      <c r="B279" t="s">
+        <v>11</v>
+      </c>
+      <c r="C279">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="280" spans="1:3">
+      <c r="A280">
+        <f t="shared" si="10"/>
+        <v>188</v>
+      </c>
+      <c r="B280" t="s">
+        <v>9</v>
+      </c>
+      <c r="C280">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="281" spans="1:3">
+      <c r="A281">
+        <f t="shared" si="10"/>
+        <v>189</v>
+      </c>
+      <c r="B281" t="s">
+        <v>8</v>
+      </c>
+      <c r="C281">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="282" spans="1:3">
+      <c r="A282">
+        <f t="shared" si="10"/>
+        <v>190</v>
+      </c>
+      <c r="B282" t="s">
+        <v>11</v>
+      </c>
+      <c r="C282">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/l_r/1st.xlsx
+++ b/l_r/1st.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\l_r\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{927D79B1-ECC3-4859-A250-B202CEB97E5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42044340-87DE-4655-8676-68BE99DD1F65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="413" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="418" uniqueCount="66">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -5389,7 +5389,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C7A3EDD-6597-4754-A609-A225833ECC81}">
-  <dimension ref="A2:H282"/>
+  <dimension ref="A2:H287"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="2" spans="1:4">
@@ -8265,7 +8265,7 @@
     </row>
     <row r="245" spans="1:3">
       <c r="A245">
-        <f t="shared" ref="A245:A282" si="10">A244+1</f>
+        <f t="shared" ref="A245:A287" si="10">A244+1</f>
         <v>153</v>
       </c>
       <c r="B245" t="s">
@@ -8717,6 +8717,66 @@
       </c>
       <c r="C282">
         <v>0</v>
+      </c>
+    </row>
+    <row r="283" spans="1:3">
+      <c r="A283">
+        <f t="shared" si="10"/>
+        <v>191</v>
+      </c>
+      <c r="B283" t="s">
+        <v>10</v>
+      </c>
+      <c r="C283">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="284" spans="1:3">
+      <c r="A284">
+        <f t="shared" si="10"/>
+        <v>192</v>
+      </c>
+      <c r="B284" t="s">
+        <v>11</v>
+      </c>
+      <c r="C284">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="285" spans="1:3">
+      <c r="A285">
+        <f t="shared" si="10"/>
+        <v>193</v>
+      </c>
+      <c r="B285" t="s">
+        <v>9</v>
+      </c>
+      <c r="C285">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="286" spans="1:3">
+      <c r="A286">
+        <f t="shared" si="10"/>
+        <v>194</v>
+      </c>
+      <c r="B286" t="s">
+        <v>11</v>
+      </c>
+      <c r="C286">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="287" spans="1:3">
+      <c r="A287">
+        <f t="shared" si="10"/>
+        <v>195</v>
+      </c>
+      <c r="B287" t="s">
+        <v>8</v>
+      </c>
+      <c r="C287">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/l_r/1st.xlsx
+++ b/l_r/1st.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\l_r\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42044340-87DE-4655-8676-68BE99DD1F65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1174843-976B-4718-A287-039392C1C318}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="418" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="423" uniqueCount="66">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -5389,7 +5389,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C7A3EDD-6597-4754-A609-A225833ECC81}">
-  <dimension ref="A2:H287"/>
+  <dimension ref="A2:H292"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="2" spans="1:4">
@@ -8265,7 +8265,7 @@
     </row>
     <row r="245" spans="1:3">
       <c r="A245">
-        <f t="shared" ref="A245:A287" si="10">A244+1</f>
+        <f t="shared" ref="A245:A292" si="10">A244+1</f>
         <v>153</v>
       </c>
       <c r="B245" t="s">
@@ -8776,6 +8776,66 @@
         <v>8</v>
       </c>
       <c r="C287">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="288" spans="1:3">
+      <c r="A288">
+        <f t="shared" si="10"/>
+        <v>196</v>
+      </c>
+      <c r="B288" t="s">
+        <v>10</v>
+      </c>
+      <c r="C288">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="289" spans="1:3">
+      <c r="A289">
+        <f t="shared" si="10"/>
+        <v>197</v>
+      </c>
+      <c r="B289" t="s">
+        <v>10</v>
+      </c>
+      <c r="C289">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="290" spans="1:3">
+      <c r="A290">
+        <f t="shared" si="10"/>
+        <v>198</v>
+      </c>
+      <c r="B290" t="s">
+        <v>10</v>
+      </c>
+      <c r="C290">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="291" spans="1:3">
+      <c r="A291">
+        <f t="shared" si="10"/>
+        <v>199</v>
+      </c>
+      <c r="B291" t="s">
+        <v>9</v>
+      </c>
+      <c r="C291">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="292" spans="1:3">
+      <c r="A292">
+        <f t="shared" si="10"/>
+        <v>200</v>
+      </c>
+      <c r="B292" t="s">
+        <v>11</v>
+      </c>
+      <c r="C292">
         <v>1</v>
       </c>
     </row>

--- a/l_r/1st.xlsx
+++ b/l_r/1st.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\l_r\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1174843-976B-4718-A287-039392C1C318}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF14C653-AE89-4D32-A833-863D2E660631}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="423" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="433" uniqueCount="66">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -5389,7 +5389,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C7A3EDD-6597-4754-A609-A225833ECC81}">
-  <dimension ref="A2:H292"/>
+  <dimension ref="A2:H302"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="2" spans="1:4">
@@ -8265,7 +8265,7 @@
     </row>
     <row r="245" spans="1:3">
       <c r="A245">
-        <f t="shared" ref="A245:A292" si="10">A244+1</f>
+        <f t="shared" ref="A245:A305" si="10">A244+1</f>
         <v>153</v>
       </c>
       <c r="B245" t="s">
@@ -8836,6 +8836,125 @@
         <v>11</v>
       </c>
       <c r="C292">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="293" spans="1:3">
+      <c r="A293">
+        <v>101</v>
+      </c>
+      <c r="B293" t="s">
+        <v>8</v>
+      </c>
+      <c r="C293">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="294" spans="1:3">
+      <c r="A294">
+        <f t="shared" si="10"/>
+        <v>102</v>
+      </c>
+      <c r="B294" t="s">
+        <v>8</v>
+      </c>
+      <c r="C294">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="295" spans="1:3">
+      <c r="A295">
+        <f t="shared" si="10"/>
+        <v>103</v>
+      </c>
+      <c r="B295" t="s">
+        <v>10</v>
+      </c>
+      <c r="C295">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="296" spans="1:3">
+      <c r="A296">
+        <f t="shared" si="10"/>
+        <v>104</v>
+      </c>
+      <c r="B296" t="s">
+        <v>11</v>
+      </c>
+      <c r="C296">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="297" spans="1:3">
+      <c r="A297">
+        <f t="shared" si="10"/>
+        <v>105</v>
+      </c>
+      <c r="B297" t="s">
+        <v>10</v>
+      </c>
+      <c r="C297">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="298" spans="1:3">
+      <c r="A298">
+        <f t="shared" si="10"/>
+        <v>106</v>
+      </c>
+      <c r="B298" t="s">
+        <v>10</v>
+      </c>
+      <c r="C298">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="299" spans="1:3">
+      <c r="A299">
+        <f t="shared" si="10"/>
+        <v>107</v>
+      </c>
+      <c r="B299" t="s">
+        <v>9</v>
+      </c>
+      <c r="C299">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="300" spans="1:3">
+      <c r="A300">
+        <f t="shared" si="10"/>
+        <v>108</v>
+      </c>
+      <c r="B300" t="s">
+        <v>8</v>
+      </c>
+      <c r="C300">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="301" spans="1:3">
+      <c r="A301">
+        <f t="shared" si="10"/>
+        <v>109</v>
+      </c>
+      <c r="B301" t="s">
+        <v>9</v>
+      </c>
+      <c r="C301">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="302" spans="1:3">
+      <c r="A302">
+        <f t="shared" si="10"/>
+        <v>110</v>
+      </c>
+      <c r="B302" t="s">
+        <v>11</v>
+      </c>
+      <c r="C302">
         <v>1</v>
       </c>
     </row>

--- a/l_r/1st.xlsx
+++ b/l_r/1st.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\l_r\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF14C653-AE89-4D32-A833-863D2E660631}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BA5BCC8-AA78-4856-8AD9-E35C1DC06F75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6375" yWindow="1020" windowWidth="25455" windowHeight="14280" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="3" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="433" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="449" uniqueCount="66">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -5389,7 +5389,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C7A3EDD-6597-4754-A609-A225833ECC81}">
-  <dimension ref="A2:H302"/>
+  <dimension ref="A2:H318"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="2" spans="1:4">
@@ -8265,7 +8265,7 @@
     </row>
     <row r="245" spans="1:3">
       <c r="A245">
-        <f t="shared" ref="A245:A305" si="10">A244+1</f>
+        <f t="shared" ref="A245:A308" si="10">A244+1</f>
         <v>153</v>
       </c>
       <c r="B245" t="s">
@@ -8955,6 +8955,192 @@
         <v>11</v>
       </c>
       <c r="C302">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="303" spans="1:3">
+      <c r="A303">
+        <f t="shared" si="10"/>
+        <v>111</v>
+      </c>
+      <c r="B303" t="s">
+        <v>9</v>
+      </c>
+      <c r="C303">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="304" spans="1:3">
+      <c r="A304">
+        <f t="shared" si="10"/>
+        <v>112</v>
+      </c>
+      <c r="B304" t="s">
+        <v>10</v>
+      </c>
+      <c r="C304">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="305" spans="1:3">
+      <c r="A305">
+        <f t="shared" si="10"/>
+        <v>113</v>
+      </c>
+      <c r="B305" t="s">
+        <v>9</v>
+      </c>
+      <c r="C305">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="306" spans="1:3">
+      <c r="A306">
+        <f t="shared" si="10"/>
+        <v>114</v>
+      </c>
+      <c r="B306" t="s">
+        <v>8</v>
+      </c>
+      <c r="C306">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="307" spans="1:3">
+      <c r="A307">
+        <f t="shared" si="10"/>
+        <v>115</v>
+      </c>
+      <c r="B307" t="s">
+        <v>9</v>
+      </c>
+      <c r="C307">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="308" spans="1:3">
+      <c r="A308">
+        <f t="shared" si="10"/>
+        <v>116</v>
+      </c>
+      <c r="B308" t="s">
+        <v>10</v>
+      </c>
+      <c r="C308">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="309" spans="1:3">
+      <c r="A309">
+        <f t="shared" ref="A309:A312" si="11">A308+1</f>
+        <v>117</v>
+      </c>
+      <c r="B309" t="s">
+        <v>9</v>
+      </c>
+      <c r="C309">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="310" spans="1:3">
+      <c r="A310">
+        <f t="shared" si="11"/>
+        <v>118</v>
+      </c>
+      <c r="B310" t="s">
+        <v>8</v>
+      </c>
+      <c r="C310">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="311" spans="1:3">
+      <c r="A311">
+        <f t="shared" si="11"/>
+        <v>119</v>
+      </c>
+      <c r="B311" t="s">
+        <v>8</v>
+      </c>
+      <c r="C311">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="312" spans="1:3">
+      <c r="A312">
+        <f t="shared" si="11"/>
+        <v>120</v>
+      </c>
+      <c r="B312" t="s">
+        <v>10</v>
+      </c>
+      <c r="C312">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="313" spans="1:3">
+      <c r="A313">
+        <v>103</v>
+      </c>
+      <c r="B313" t="s">
+        <v>11</v>
+      </c>
+      <c r="C313">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="314" spans="1:3">
+      <c r="A314">
+        <v>104</v>
+      </c>
+      <c r="B314" t="s">
+        <v>9</v>
+      </c>
+      <c r="C314">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="315" spans="1:3">
+      <c r="A315">
+        <v>107</v>
+      </c>
+      <c r="B315" t="s">
+        <v>11</v>
+      </c>
+      <c r="C315">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="316" spans="1:3">
+      <c r="A316">
+        <v>111</v>
+      </c>
+      <c r="B316" t="s">
+        <v>8</v>
+      </c>
+      <c r="C316">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="317" spans="1:3">
+      <c r="A317">
+        <v>116</v>
+      </c>
+      <c r="B317" t="s">
+        <v>10</v>
+      </c>
+      <c r="C317">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="318" spans="1:3">
+      <c r="A318">
+        <v>117</v>
+      </c>
+      <c r="B318" t="s">
+        <v>11</v>
+      </c>
+      <c r="C318">
         <v>1</v>
       </c>
     </row>

--- a/l_r/1st.xlsx
+++ b/l_r/1st.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\l_r\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BA5BCC8-AA78-4856-8AD9-E35C1DC06F75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49BDDD26-CE5B-464C-81E7-19F216275C84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6375" yWindow="1020" windowWidth="25455" windowHeight="14280" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-420" yWindow="615" windowWidth="17265" windowHeight="14280" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="3" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="449" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="457" uniqueCount="66">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -5389,7 +5389,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C7A3EDD-6597-4754-A609-A225833ECC81}">
-  <dimension ref="A2:H318"/>
+  <dimension ref="A2:H326"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="2" spans="1:4">
@@ -9141,6 +9141,101 @@
         <v>11</v>
       </c>
       <c r="C318">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="319" spans="1:3">
+      <c r="A319">
+        <v>131</v>
+      </c>
+      <c r="B319" t="s">
+        <v>9</v>
+      </c>
+      <c r="C319">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="320" spans="1:3">
+      <c r="A320">
+        <f t="shared" ref="A320:A326" si="12">A319+1</f>
+        <v>132</v>
+      </c>
+      <c r="B320" t="s">
+        <v>8</v>
+      </c>
+      <c r="C320">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="321" spans="1:3">
+      <c r="A321">
+        <f t="shared" si="12"/>
+        <v>133</v>
+      </c>
+      <c r="B321" t="s">
+        <v>8</v>
+      </c>
+      <c r="C321">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="322" spans="1:3">
+      <c r="A322">
+        <f t="shared" si="12"/>
+        <v>134</v>
+      </c>
+      <c r="B322" t="s">
+        <v>10</v>
+      </c>
+      <c r="C322">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="323" spans="1:3">
+      <c r="A323">
+        <f t="shared" si="12"/>
+        <v>135</v>
+      </c>
+      <c r="B323" t="s">
+        <v>9</v>
+      </c>
+      <c r="C323">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="324" spans="1:3">
+      <c r="A324">
+        <f t="shared" si="12"/>
+        <v>136</v>
+      </c>
+      <c r="B324" t="s">
+        <v>10</v>
+      </c>
+      <c r="C324">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="325" spans="1:3">
+      <c r="A325">
+        <f t="shared" si="12"/>
+        <v>137</v>
+      </c>
+      <c r="B325" t="s">
+        <v>11</v>
+      </c>
+      <c r="C325">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="326" spans="1:3">
+      <c r="A326">
+        <f t="shared" si="12"/>
+        <v>138</v>
+      </c>
+      <c r="B326" t="s">
+        <v>11</v>
+      </c>
+      <c r="C326">
         <v>1</v>
       </c>
     </row>

--- a/l_r/1st.xlsx
+++ b/l_r/1st.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\l_r\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49BDDD26-CE5B-464C-81E7-19F216275C84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48E94837-9CE2-41AF-A9FA-FFAC8E1C1CB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-420" yWindow="615" windowWidth="17265" windowHeight="14280" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="615" windowWidth="17265" windowHeight="14280" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="3" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="457" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="465" uniqueCount="66">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -5389,7 +5389,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C7A3EDD-6597-4754-A609-A225833ECC81}">
-  <dimension ref="A2:H326"/>
+  <dimension ref="A2:H334"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="2" spans="1:4">
@@ -9157,7 +9157,7 @@
     </row>
     <row r="320" spans="1:3">
       <c r="A320">
-        <f t="shared" ref="A320:A326" si="12">A319+1</f>
+        <f t="shared" ref="A320:A334" si="12">A319+1</f>
         <v>132</v>
       </c>
       <c r="B320" t="s">
@@ -9236,6 +9236,102 @@
         <v>11</v>
       </c>
       <c r="C326">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="327" spans="1:3">
+      <c r="A327">
+        <f t="shared" si="12"/>
+        <v>139</v>
+      </c>
+      <c r="B327" t="s">
+        <v>8</v>
+      </c>
+      <c r="C327">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="328" spans="1:3">
+      <c r="A328">
+        <f t="shared" si="12"/>
+        <v>140</v>
+      </c>
+      <c r="B328" t="s">
+        <v>11</v>
+      </c>
+      <c r="C328">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="329" spans="1:3">
+      <c r="A329">
+        <f t="shared" si="12"/>
+        <v>141</v>
+      </c>
+      <c r="B329" t="s">
+        <v>10</v>
+      </c>
+      <c r="C329">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="330" spans="1:3">
+      <c r="A330">
+        <f t="shared" si="12"/>
+        <v>142</v>
+      </c>
+      <c r="B330" t="s">
+        <v>8</v>
+      </c>
+      <c r="C330">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="331" spans="1:3">
+      <c r="A331">
+        <f t="shared" si="12"/>
+        <v>143</v>
+      </c>
+      <c r="B331" t="s">
+        <v>10</v>
+      </c>
+      <c r="C331">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="332" spans="1:3">
+      <c r="A332">
+        <f t="shared" si="12"/>
+        <v>144</v>
+      </c>
+      <c r="B332" t="s">
+        <v>10</v>
+      </c>
+      <c r="C332">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="333" spans="1:3">
+      <c r="A333">
+        <f t="shared" si="12"/>
+        <v>145</v>
+      </c>
+      <c r="B333" t="s">
+        <v>8</v>
+      </c>
+      <c r="C333">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="334" spans="1:3">
+      <c r="A334">
+        <f t="shared" si="12"/>
+        <v>146</v>
+      </c>
+      <c r="B334" t="s">
+        <v>11</v>
+      </c>
+      <c r="C334">
         <v>1</v>
       </c>
     </row>

--- a/l_r/1st.xlsx
+++ b/l_r/1st.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\l_r\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48E94837-9CE2-41AF-A9FA-FFAC8E1C1CB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FC249CB-6C24-478F-B480-6C7033C8B15C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="615" windowWidth="17265" windowHeight="14280" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2190" yWindow="105" windowWidth="17265" windowHeight="14280" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="3" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="465" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="469" uniqueCount="66">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -5389,7 +5389,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C7A3EDD-6597-4754-A609-A225833ECC81}">
-  <dimension ref="A2:H334"/>
+  <dimension ref="A2:H338"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="2" spans="1:4">
@@ -9157,7 +9157,7 @@
     </row>
     <row r="320" spans="1:3">
       <c r="A320">
-        <f t="shared" ref="A320:A334" si="12">A319+1</f>
+        <f t="shared" ref="A320:A338" si="12">A319+1</f>
         <v>132</v>
       </c>
       <c r="B320" t="s">
@@ -9332,6 +9332,54 @@
         <v>11</v>
       </c>
       <c r="C334">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="335" spans="1:3">
+      <c r="A335">
+        <f t="shared" si="12"/>
+        <v>147</v>
+      </c>
+      <c r="B335" t="s">
+        <v>9</v>
+      </c>
+      <c r="C335">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="336" spans="1:3">
+      <c r="A336">
+        <f t="shared" si="12"/>
+        <v>148</v>
+      </c>
+      <c r="B336" t="s">
+        <v>10</v>
+      </c>
+      <c r="C336">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="337" spans="1:3">
+      <c r="A337">
+        <f t="shared" si="12"/>
+        <v>149</v>
+      </c>
+      <c r="B337" t="s">
+        <v>11</v>
+      </c>
+      <c r="C337">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="338" spans="1:3">
+      <c r="A338">
+        <f t="shared" si="12"/>
+        <v>150</v>
+      </c>
+      <c r="B338" t="s">
+        <v>8</v>
+      </c>
+      <c r="C338">
         <v>1</v>
       </c>
     </row>

--- a/l_r/1st.xlsx
+++ b/l_r/1st.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\l_r\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FC249CB-6C24-478F-B480-6C7033C8B15C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E78D9153-F02F-48FD-8581-975136B6FD3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2190" yWindow="105" windowWidth="17265" windowHeight="14280" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8550" yWindow="1260" windowWidth="17265" windowHeight="14280" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="3" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="469" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="479" uniqueCount="66">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -5389,7 +5389,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C7A3EDD-6597-4754-A609-A225833ECC81}">
-  <dimension ref="A2:H338"/>
+  <dimension ref="A2:H348"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="2" spans="1:4">
@@ -9157,7 +9157,7 @@
     </row>
     <row r="320" spans="1:3">
       <c r="A320">
-        <f t="shared" ref="A320:A338" si="12">A319+1</f>
+        <f t="shared" ref="A320:A348" si="12">A319+1</f>
         <v>132</v>
       </c>
       <c r="B320" t="s">
@@ -9380,6 +9380,126 @@
         <v>8</v>
       </c>
       <c r="C338">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="339" spans="1:3">
+      <c r="A339">
+        <f t="shared" si="12"/>
+        <v>151</v>
+      </c>
+      <c r="B339" t="s">
+        <v>11</v>
+      </c>
+      <c r="C339">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="340" spans="1:3">
+      <c r="A340">
+        <f t="shared" si="12"/>
+        <v>152</v>
+      </c>
+      <c r="B340" t="s">
+        <v>8</v>
+      </c>
+      <c r="C340">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="341" spans="1:3">
+      <c r="A341">
+        <f t="shared" si="12"/>
+        <v>153</v>
+      </c>
+      <c r="B341" t="s">
+        <v>10</v>
+      </c>
+      <c r="C341">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="342" spans="1:3">
+      <c r="A342">
+        <f t="shared" si="12"/>
+        <v>154</v>
+      </c>
+      <c r="B342" t="s">
+        <v>11</v>
+      </c>
+      <c r="C342">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="343" spans="1:3">
+      <c r="A343">
+        <f t="shared" si="12"/>
+        <v>155</v>
+      </c>
+      <c r="B343" t="s">
+        <v>9</v>
+      </c>
+      <c r="C343">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="344" spans="1:3">
+      <c r="A344">
+        <f t="shared" si="12"/>
+        <v>156</v>
+      </c>
+      <c r="B344" t="s">
+        <v>8</v>
+      </c>
+      <c r="C344">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="345" spans="1:3">
+      <c r="A345">
+        <f t="shared" si="12"/>
+        <v>157</v>
+      </c>
+      <c r="B345" t="s">
+        <v>10</v>
+      </c>
+      <c r="C345">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="346" spans="1:3">
+      <c r="A346">
+        <f t="shared" si="12"/>
+        <v>158</v>
+      </c>
+      <c r="B346" t="s">
+        <v>11</v>
+      </c>
+      <c r="C346">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="347" spans="1:3">
+      <c r="A347">
+        <f t="shared" si="12"/>
+        <v>159</v>
+      </c>
+      <c r="B347" t="s">
+        <v>9</v>
+      </c>
+      <c r="C347">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="348" spans="1:3">
+      <c r="A348">
+        <f t="shared" si="12"/>
+        <v>160</v>
+      </c>
+      <c r="B348" t="s">
+        <v>11</v>
+      </c>
+      <c r="C348">
         <v>1</v>
       </c>
     </row>

--- a/l_r/1st.xlsx
+++ b/l_r/1st.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\l_r\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E78D9153-F02F-48FD-8581-975136B6FD3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B750CBCB-BFB9-4464-8013-0592C7D404B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8550" yWindow="1260" windowWidth="17265" windowHeight="14280" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8550" yWindow="1200" windowWidth="17265" windowHeight="14280" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="3" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="479" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="486" uniqueCount="66">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -5389,7 +5389,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C7A3EDD-6597-4754-A609-A225833ECC81}">
-  <dimension ref="A2:H348"/>
+  <dimension ref="A2:H355"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="2" spans="1:4">
@@ -9157,7 +9157,7 @@
     </row>
     <row r="320" spans="1:3">
       <c r="A320">
-        <f t="shared" ref="A320:A348" si="12">A319+1</f>
+        <f t="shared" ref="A320:A355" si="12">A319+1</f>
         <v>132</v>
       </c>
       <c r="B320" t="s">
@@ -9500,6 +9500,90 @@
         <v>11</v>
       </c>
       <c r="C348">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="349" spans="1:3">
+      <c r="A349">
+        <f t="shared" si="12"/>
+        <v>161</v>
+      </c>
+      <c r="B349" t="s">
+        <v>11</v>
+      </c>
+      <c r="C349">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="350" spans="1:3">
+      <c r="A350">
+        <f t="shared" si="12"/>
+        <v>162</v>
+      </c>
+      <c r="B350" t="s">
+        <v>9</v>
+      </c>
+      <c r="C350">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="351" spans="1:3">
+      <c r="A351">
+        <f t="shared" si="12"/>
+        <v>163</v>
+      </c>
+      <c r="B351" t="s">
+        <v>8</v>
+      </c>
+      <c r="C351">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="352" spans="1:3">
+      <c r="A352">
+        <f t="shared" si="12"/>
+        <v>164</v>
+      </c>
+      <c r="B352" t="s">
+        <v>11</v>
+      </c>
+      <c r="C352">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="353" spans="1:3">
+      <c r="A353">
+        <f t="shared" si="12"/>
+        <v>165</v>
+      </c>
+      <c r="B353" t="s">
+        <v>10</v>
+      </c>
+      <c r="C353">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="354" spans="1:3">
+      <c r="A354">
+        <f t="shared" si="12"/>
+        <v>166</v>
+      </c>
+      <c r="B354" t="s">
+        <v>10</v>
+      </c>
+      <c r="C354">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="355" spans="1:3">
+      <c r="A355">
+        <f t="shared" si="12"/>
+        <v>167</v>
+      </c>
+      <c r="B355" t="s">
+        <v>9</v>
+      </c>
+      <c r="C355">
         <v>1</v>
       </c>
     </row>

--- a/l_r/1st.xlsx
+++ b/l_r/1st.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\l_r\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B750CBCB-BFB9-4464-8013-0592C7D404B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D94332C4-5BD9-4D0C-B504-C9B6F10A8B02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8550" yWindow="1200" windowWidth="17265" windowHeight="14280" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2385" yWindow="420" windowWidth="17265" windowHeight="14280" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="3" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="486" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="490" uniqueCount="66">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -5389,7 +5389,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C7A3EDD-6597-4754-A609-A225833ECC81}">
-  <dimension ref="A2:H355"/>
+  <dimension ref="A2:H359"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="2" spans="1:4">
@@ -9157,7 +9157,7 @@
     </row>
     <row r="320" spans="1:3">
       <c r="A320">
-        <f t="shared" ref="A320:A355" si="12">A319+1</f>
+        <f t="shared" ref="A320:A359" si="12">A319+1</f>
         <v>132</v>
       </c>
       <c r="B320" t="s">
@@ -9585,6 +9585,54 @@
       </c>
       <c r="C355">
         <v>1</v>
+      </c>
+    </row>
+    <row r="356" spans="1:3">
+      <c r="A356">
+        <f t="shared" si="12"/>
+        <v>168</v>
+      </c>
+      <c r="B356" t="s">
+        <v>10</v>
+      </c>
+      <c r="C356">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="357" spans="1:3">
+      <c r="A357">
+        <f t="shared" si="12"/>
+        <v>169</v>
+      </c>
+      <c r="B357" t="s">
+        <v>11</v>
+      </c>
+      <c r="C357">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="358" spans="1:3">
+      <c r="A358">
+        <f t="shared" si="12"/>
+        <v>170</v>
+      </c>
+      <c r="B358" t="s">
+        <v>9</v>
+      </c>
+      <c r="C358">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="359" spans="1:3">
+      <c r="A359">
+        <f t="shared" si="12"/>
+        <v>171</v>
+      </c>
+      <c r="B359" t="s">
+        <v>11</v>
+      </c>
+      <c r="C359">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/l_r/1st.xlsx
+++ b/l_r/1st.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\l_r\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D94332C4-5BD9-4D0C-B504-C9B6F10A8B02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F720D6D9-C05F-496D-B65B-286436A6E687}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2385" yWindow="420" windowWidth="17265" windowHeight="14280" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="870" yWindow="450" windowWidth="17265" windowHeight="14280" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="3" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="490" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="494" uniqueCount="66">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -5389,7 +5389,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C7A3EDD-6597-4754-A609-A225833ECC81}">
-  <dimension ref="A2:H359"/>
+  <dimension ref="A2:H363"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="2" spans="1:4">
@@ -9157,7 +9157,7 @@
     </row>
     <row r="320" spans="1:3">
       <c r="A320">
-        <f t="shared" ref="A320:A359" si="12">A319+1</f>
+        <f t="shared" ref="A320:A363" si="12">A319+1</f>
         <v>132</v>
       </c>
       <c r="B320" t="s">
@@ -9633,6 +9633,54 @@
       </c>
       <c r="C359">
         <v>0</v>
+      </c>
+    </row>
+    <row r="360" spans="1:3">
+      <c r="A360">
+        <f t="shared" si="12"/>
+        <v>172</v>
+      </c>
+      <c r="B360" t="s">
+        <v>8</v>
+      </c>
+      <c r="C360">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="361" spans="1:3">
+      <c r="A361">
+        <f t="shared" si="12"/>
+        <v>173</v>
+      </c>
+      <c r="B361" t="s">
+        <v>8</v>
+      </c>
+      <c r="C361">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="362" spans="1:3">
+      <c r="A362">
+        <f t="shared" si="12"/>
+        <v>174</v>
+      </c>
+      <c r="B362" t="s">
+        <v>8</v>
+      </c>
+      <c r="C362">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="363" spans="1:3">
+      <c r="A363">
+        <f t="shared" si="12"/>
+        <v>175</v>
+      </c>
+      <c r="B363" t="s">
+        <v>11</v>
+      </c>
+      <c r="C363">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/l_r/1st.xlsx
+++ b/l_r/1st.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\l_r\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F720D6D9-C05F-496D-B65B-286436A6E687}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9010001B-0A9A-4A6D-A65F-3089A8DAAE85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="870" yWindow="450" windowWidth="17265" windowHeight="14280" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1950" yWindow="1950" windowWidth="21600" windowHeight="11295" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="3" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="494" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="499" uniqueCount="66">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -5389,7 +5389,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C7A3EDD-6597-4754-A609-A225833ECC81}">
-  <dimension ref="A2:H363"/>
+  <dimension ref="A2:H368"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="2" spans="1:4">
@@ -9157,7 +9157,7 @@
     </row>
     <row r="320" spans="1:3">
       <c r="A320">
-        <f t="shared" ref="A320:A363" si="12">A319+1</f>
+        <f t="shared" ref="A320:A368" si="12">A319+1</f>
         <v>132</v>
       </c>
       <c r="B320" t="s">
@@ -9680,6 +9680,66 @@
         <v>11</v>
       </c>
       <c r="C363">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="364" spans="1:3">
+      <c r="A364">
+        <f t="shared" si="12"/>
+        <v>176</v>
+      </c>
+      <c r="B364" t="s">
+        <v>10</v>
+      </c>
+      <c r="C364">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="365" spans="1:3">
+      <c r="A365">
+        <f t="shared" si="12"/>
+        <v>177</v>
+      </c>
+      <c r="B365" t="s">
+        <v>8</v>
+      </c>
+      <c r="C365">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="366" spans="1:3">
+      <c r="A366">
+        <f t="shared" si="12"/>
+        <v>178</v>
+      </c>
+      <c r="B366" t="s">
+        <v>9</v>
+      </c>
+      <c r="C366">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="367" spans="1:3">
+      <c r="A367">
+        <f t="shared" si="12"/>
+        <v>179</v>
+      </c>
+      <c r="B367" t="s">
+        <v>8</v>
+      </c>
+      <c r="C367">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="368" spans="1:3">
+      <c r="A368">
+        <f t="shared" si="12"/>
+        <v>180</v>
+      </c>
+      <c r="B368" t="s">
+        <v>9</v>
+      </c>
+      <c r="C368">
         <v>1</v>
       </c>
     </row>

--- a/l_r/1st.xlsx
+++ b/l_r/1st.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\l_r\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9010001B-0A9A-4A6D-A65F-3089A8DAAE85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DED5637-4B02-4679-848F-C0A681191415}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1950" yWindow="1950" windowWidth="21600" windowHeight="11295" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="735" yWindow="510" windowWidth="15330" windowHeight="14310" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="3" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="499" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="504" uniqueCount="66">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -5389,7 +5389,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C7A3EDD-6597-4754-A609-A225833ECC81}">
-  <dimension ref="A2:H368"/>
+  <dimension ref="A2:H373"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="2" spans="1:4">
@@ -9157,7 +9157,7 @@
     </row>
     <row r="320" spans="1:3">
       <c r="A320">
-        <f t="shared" ref="A320:A368" si="12">A319+1</f>
+        <f t="shared" ref="A320:A373" si="12">A319+1</f>
         <v>132</v>
       </c>
       <c r="B320" t="s">
@@ -9740,6 +9740,66 @@
         <v>9</v>
       </c>
       <c r="C368">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="369" spans="1:3">
+      <c r="A369">
+        <f t="shared" si="12"/>
+        <v>181</v>
+      </c>
+      <c r="B369" t="s">
+        <v>9</v>
+      </c>
+      <c r="C369">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="370" spans="1:3">
+      <c r="A370">
+        <f t="shared" si="12"/>
+        <v>182</v>
+      </c>
+      <c r="B370" t="s">
+        <v>11</v>
+      </c>
+      <c r="C370">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="371" spans="1:3">
+      <c r="A371">
+        <f t="shared" si="12"/>
+        <v>183</v>
+      </c>
+      <c r="B371" t="s">
+        <v>8</v>
+      </c>
+      <c r="C371">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="372" spans="1:3">
+      <c r="A372">
+        <f t="shared" si="12"/>
+        <v>184</v>
+      </c>
+      <c r="B372" t="s">
+        <v>11</v>
+      </c>
+      <c r="C372">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="373" spans="1:3">
+      <c r="A373">
+        <f t="shared" si="12"/>
+        <v>185</v>
+      </c>
+      <c r="B373" t="s">
+        <v>10</v>
+      </c>
+      <c r="C373">
         <v>1</v>
       </c>
     </row>

--- a/l_r/1st.xlsx
+++ b/l_r/1st.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\l_r\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DED5637-4B02-4679-848F-C0A681191415}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A596514-CDD3-4349-AC7E-11778D0B086E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="735" yWindow="510" windowWidth="15330" windowHeight="14310" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="15750" yWindow="1395" windowWidth="15330" windowHeight="14310" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="3" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="504" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="509" uniqueCount="66">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -5389,7 +5389,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C7A3EDD-6597-4754-A609-A225833ECC81}">
-  <dimension ref="A2:H373"/>
+  <dimension ref="A2:H378"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="2" spans="1:4">
@@ -9157,7 +9157,7 @@
     </row>
     <row r="320" spans="1:3">
       <c r="A320">
-        <f t="shared" ref="A320:A373" si="12">A319+1</f>
+        <f t="shared" ref="A320:A378" si="12">A319+1</f>
         <v>132</v>
       </c>
       <c r="B320" t="s">
@@ -9800,6 +9800,66 @@
         <v>10</v>
       </c>
       <c r="C373">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="374" spans="1:3">
+      <c r="A374">
+        <f t="shared" si="12"/>
+        <v>186</v>
+      </c>
+      <c r="B374" t="s">
+        <v>8</v>
+      </c>
+      <c r="C374">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="375" spans="1:3">
+      <c r="A375">
+        <f t="shared" si="12"/>
+        <v>187</v>
+      </c>
+      <c r="B375" t="s">
+        <v>11</v>
+      </c>
+      <c r="C375">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="376" spans="1:3">
+      <c r="A376">
+        <f t="shared" si="12"/>
+        <v>188</v>
+      </c>
+      <c r="B376" t="s">
+        <v>8</v>
+      </c>
+      <c r="C376">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="377" spans="1:3">
+      <c r="A377">
+        <f t="shared" si="12"/>
+        <v>189</v>
+      </c>
+      <c r="B377" t="s">
+        <v>9</v>
+      </c>
+      <c r="C377">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="378" spans="1:3">
+      <c r="A378">
+        <f t="shared" si="12"/>
+        <v>190</v>
+      </c>
+      <c r="B378" t="s">
+        <v>10</v>
+      </c>
+      <c r="C378">
         <v>1</v>
       </c>
     </row>

--- a/l_r/1st.xlsx
+++ b/l_r/1st.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\l_r\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A596514-CDD3-4349-AC7E-11778D0B086E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8561080-86C1-4B31-825C-D0B6C49F9F38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15750" yWindow="1395" windowWidth="15330" windowHeight="14310" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3075" yWindow="1170" windowWidth="15330" windowHeight="14310" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="3" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="509" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="514" uniqueCount="66">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -5389,7 +5389,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C7A3EDD-6597-4754-A609-A225833ECC81}">
-  <dimension ref="A2:H378"/>
+  <dimension ref="A2:H383"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="2" spans="1:4">
@@ -9157,7 +9157,7 @@
     </row>
     <row r="320" spans="1:3">
       <c r="A320">
-        <f t="shared" ref="A320:A378" si="12">A319+1</f>
+        <f t="shared" ref="A320:A383" si="12">A319+1</f>
         <v>132</v>
       </c>
       <c r="B320" t="s">
@@ -9860,6 +9860,66 @@
         <v>10</v>
       </c>
       <c r="C378">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="379" spans="1:3">
+      <c r="A379">
+        <f t="shared" si="12"/>
+        <v>191</v>
+      </c>
+      <c r="B379" t="s">
+        <v>10</v>
+      </c>
+      <c r="C379">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="380" spans="1:3">
+      <c r="A380">
+        <f t="shared" si="12"/>
+        <v>192</v>
+      </c>
+      <c r="B380" t="s">
+        <v>11</v>
+      </c>
+      <c r="C380">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="381" spans="1:3">
+      <c r="A381">
+        <f t="shared" si="12"/>
+        <v>193</v>
+      </c>
+      <c r="B381" t="s">
+        <v>9</v>
+      </c>
+      <c r="C381">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="382" spans="1:3">
+      <c r="A382">
+        <f t="shared" si="12"/>
+        <v>194</v>
+      </c>
+      <c r="B382" t="s">
+        <v>11</v>
+      </c>
+      <c r="C382">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="383" spans="1:3">
+      <c r="A383">
+        <f t="shared" si="12"/>
+        <v>195</v>
+      </c>
+      <c r="B383" t="s">
+        <v>8</v>
+      </c>
+      <c r="C383">
         <v>1</v>
       </c>
     </row>

--- a/l_r/1st.xlsx
+++ b/l_r/1st.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\l_r\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8561080-86C1-4B31-825C-D0B6C49F9F38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99F4079A-092D-446C-BEEF-10F2F57E92B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3075" yWindow="1170" windowWidth="15330" windowHeight="14310" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="514" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="524" uniqueCount="66">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -5389,7 +5389,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C7A3EDD-6597-4754-A609-A225833ECC81}">
-  <dimension ref="A2:H383"/>
+  <dimension ref="A2:H393"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="2" spans="1:4">
@@ -9157,7 +9157,7 @@
     </row>
     <row r="320" spans="1:3">
       <c r="A320">
-        <f t="shared" ref="A320:A383" si="12">A319+1</f>
+        <f t="shared" ref="A320:A385" si="12">A319+1</f>
         <v>132</v>
       </c>
       <c r="B320" t="s">
@@ -9920,6 +9920,125 @@
         <v>8</v>
       </c>
       <c r="C383">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="384" spans="1:3">
+      <c r="A384">
+        <v>101</v>
+      </c>
+      <c r="B384" t="s">
+        <v>8</v>
+      </c>
+      <c r="C384">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="385" spans="1:3">
+      <c r="A385">
+        <f t="shared" si="12"/>
+        <v>102</v>
+      </c>
+      <c r="B385" t="s">
+        <v>8</v>
+      </c>
+      <c r="C385">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="386" spans="1:3">
+      <c r="A386">
+        <f t="shared" ref="A386:A394" si="13">A385+1</f>
+        <v>103</v>
+      </c>
+      <c r="B386" t="s">
+        <v>10</v>
+      </c>
+      <c r="C386">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="387" spans="1:3">
+      <c r="A387">
+        <f t="shared" si="13"/>
+        <v>104</v>
+      </c>
+      <c r="B387" t="s">
+        <v>9</v>
+      </c>
+      <c r="C387">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="388" spans="1:3">
+      <c r="A388">
+        <f t="shared" si="13"/>
+        <v>105</v>
+      </c>
+      <c r="B388" t="s">
+        <v>10</v>
+      </c>
+      <c r="C388">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="389" spans="1:3">
+      <c r="A389">
+        <f t="shared" si="13"/>
+        <v>106</v>
+      </c>
+      <c r="B389" t="s">
+        <v>10</v>
+      </c>
+      <c r="C389">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="390" spans="1:3">
+      <c r="A390">
+        <f t="shared" si="13"/>
+        <v>107</v>
+      </c>
+      <c r="B390" t="s">
+        <v>11</v>
+      </c>
+      <c r="C390">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="391" spans="1:3">
+      <c r="A391">
+        <f t="shared" si="13"/>
+        <v>108</v>
+      </c>
+      <c r="B391" t="s">
+        <v>10</v>
+      </c>
+      <c r="C391">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="392" spans="1:3">
+      <c r="A392">
+        <f t="shared" si="13"/>
+        <v>109</v>
+      </c>
+      <c r="B392" t="s">
+        <v>9</v>
+      </c>
+      <c r="C392">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="393" spans="1:3">
+      <c r="A393">
+        <f t="shared" si="13"/>
+        <v>110</v>
+      </c>
+      <c r="B393" t="s">
+        <v>11</v>
+      </c>
+      <c r="C393">
         <v>1</v>
       </c>
     </row>

--- a/l_r/1st.xlsx
+++ b/l_r/1st.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\l_r\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99F4079A-092D-446C-BEEF-10F2F57E92B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{549EFA4E-0034-4A52-AA0B-6EAA29FAD795}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3075" yWindow="1170" windowWidth="15330" windowHeight="14310" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="3" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="524" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="534" uniqueCount="66">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -5389,7 +5389,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C7A3EDD-6597-4754-A609-A225833ECC81}">
-  <dimension ref="A2:H393"/>
+  <dimension ref="A2:H403"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="2" spans="1:4">
@@ -9948,7 +9948,7 @@
     </row>
     <row r="386" spans="1:3">
       <c r="A386">
-        <f t="shared" ref="A386:A394" si="13">A385+1</f>
+        <f t="shared" ref="A386:A403" si="13">A385+1</f>
         <v>103</v>
       </c>
       <c r="B386" t="s">
@@ -10040,6 +10040,126 @@
       </c>
       <c r="C393">
         <v>1</v>
+      </c>
+    </row>
+    <row r="394" spans="1:3">
+      <c r="A394">
+        <f t="shared" si="13"/>
+        <v>111</v>
+      </c>
+      <c r="B394" t="s">
+        <v>10</v>
+      </c>
+      <c r="C394">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="395" spans="1:3">
+      <c r="A395">
+        <f t="shared" si="13"/>
+        <v>112</v>
+      </c>
+      <c r="B395" t="s">
+        <v>10</v>
+      </c>
+      <c r="C395">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="396" spans="1:3">
+      <c r="A396">
+        <f t="shared" si="13"/>
+        <v>113</v>
+      </c>
+      <c r="B396" t="s">
+        <v>11</v>
+      </c>
+      <c r="C396">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="397" spans="1:3">
+      <c r="A397">
+        <f t="shared" si="13"/>
+        <v>114</v>
+      </c>
+      <c r="B397" t="s">
+        <v>10</v>
+      </c>
+      <c r="C397">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="398" spans="1:3">
+      <c r="A398">
+        <f t="shared" si="13"/>
+        <v>115</v>
+      </c>
+      <c r="B398" t="s">
+        <v>11</v>
+      </c>
+      <c r="C398">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="399" spans="1:3">
+      <c r="A399">
+        <f t="shared" si="13"/>
+        <v>116</v>
+      </c>
+      <c r="B399" t="s">
+        <v>8</v>
+      </c>
+      <c r="C399">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="400" spans="1:3">
+      <c r="A400">
+        <f t="shared" si="13"/>
+        <v>117</v>
+      </c>
+      <c r="B400" t="s">
+        <v>8</v>
+      </c>
+      <c r="C400">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="401" spans="1:3">
+      <c r="A401">
+        <f t="shared" si="13"/>
+        <v>118</v>
+      </c>
+      <c r="B401" t="s">
+        <v>10</v>
+      </c>
+      <c r="C401">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="402" spans="1:3">
+      <c r="A402">
+        <f t="shared" si="13"/>
+        <v>119</v>
+      </c>
+      <c r="B402" t="s">
+        <v>11</v>
+      </c>
+      <c r="C402">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="403" spans="1:3">
+      <c r="A403">
+        <f t="shared" si="13"/>
+        <v>120</v>
+      </c>
+      <c r="B403" t="s">
+        <v>10</v>
+      </c>
+      <c r="C403">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/l_r/1st.xlsx
+++ b/l_r/1st.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\l_r\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{549EFA4E-0034-4A52-AA0B-6EAA29FAD795}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8071834-6183-4340-8BE1-1754F8A09BA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="534" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="544" uniqueCount="66">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -5389,7 +5389,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C7A3EDD-6597-4754-A609-A225833ECC81}">
-  <dimension ref="A2:H403"/>
+  <dimension ref="A2:H413"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="2" spans="1:4">
@@ -9948,7 +9948,7 @@
     </row>
     <row r="386" spans="1:3">
       <c r="A386">
-        <f t="shared" ref="A386:A403" si="13">A385+1</f>
+        <f t="shared" ref="A386:A414" si="13">A385+1</f>
         <v>103</v>
       </c>
       <c r="B386" t="s">
@@ -10159,6 +10159,126 @@
         <v>10</v>
       </c>
       <c r="C403">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="404" spans="1:3">
+      <c r="A404">
+        <f t="shared" si="13"/>
+        <v>121</v>
+      </c>
+      <c r="B404" t="s">
+        <v>11</v>
+      </c>
+      <c r="C404">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="405" spans="1:3">
+      <c r="A405">
+        <f t="shared" si="13"/>
+        <v>122</v>
+      </c>
+      <c r="B405" t="s">
+        <v>9</v>
+      </c>
+      <c r="C405">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="406" spans="1:3">
+      <c r="A406">
+        <f t="shared" si="13"/>
+        <v>123</v>
+      </c>
+      <c r="B406" t="s">
+        <v>10</v>
+      </c>
+      <c r="C406">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="407" spans="1:3">
+      <c r="A407">
+        <f t="shared" si="13"/>
+        <v>124</v>
+      </c>
+      <c r="B407" t="s">
+        <v>8</v>
+      </c>
+      <c r="C407">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="408" spans="1:3">
+      <c r="A408">
+        <f t="shared" si="13"/>
+        <v>125</v>
+      </c>
+      <c r="B408" t="s">
+        <v>11</v>
+      </c>
+      <c r="C408">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="409" spans="1:3">
+      <c r="A409">
+        <f t="shared" si="13"/>
+        <v>126</v>
+      </c>
+      <c r="B409" t="s">
+        <v>10</v>
+      </c>
+      <c r="C409">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="410" spans="1:3">
+      <c r="A410">
+        <f t="shared" si="13"/>
+        <v>127</v>
+      </c>
+      <c r="B410" t="s">
+        <v>9</v>
+      </c>
+      <c r="C410">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="411" spans="1:3">
+      <c r="A411">
+        <f t="shared" si="13"/>
+        <v>128</v>
+      </c>
+      <c r="B411" t="s">
+        <v>8</v>
+      </c>
+      <c r="C411">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="412" spans="1:3">
+      <c r="A412">
+        <f t="shared" si="13"/>
+        <v>129</v>
+      </c>
+      <c r="B412" t="s">
+        <v>11</v>
+      </c>
+      <c r="C412">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="413" spans="1:3">
+      <c r="A413">
+        <f t="shared" si="13"/>
+        <v>130</v>
+      </c>
+      <c r="B413" t="s">
+        <v>8</v>
+      </c>
+      <c r="C413">
         <v>0</v>
       </c>
     </row>

--- a/l_r/1st.xlsx
+++ b/l_r/1st.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\l_r\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8071834-6183-4340-8BE1-1754F8A09BA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59F081C0-CD11-4F6B-8142-8054EFD27684}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="544" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="552" uniqueCount="66">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -5389,7 +5389,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C7A3EDD-6597-4754-A609-A225833ECC81}">
-  <dimension ref="A2:H413"/>
+  <dimension ref="A2:H421"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="2" spans="1:4">
@@ -9948,7 +9948,7 @@
     </row>
     <row r="386" spans="1:3">
       <c r="A386">
-        <f t="shared" ref="A386:A414" si="13">A385+1</f>
+        <f t="shared" ref="A386:A421" si="13">A385+1</f>
         <v>103</v>
       </c>
       <c r="B386" t="s">
@@ -10280,6 +10280,102 @@
       </c>
       <c r="C413">
         <v>0</v>
+      </c>
+    </row>
+    <row r="414" spans="1:3">
+      <c r="A414">
+        <f t="shared" si="13"/>
+        <v>131</v>
+      </c>
+      <c r="B414" t="s">
+        <v>9</v>
+      </c>
+      <c r="C414">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="415" spans="1:3">
+      <c r="A415">
+        <f t="shared" si="13"/>
+        <v>132</v>
+      </c>
+      <c r="B415" t="s">
+        <v>8</v>
+      </c>
+      <c r="C415">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="416" spans="1:3">
+      <c r="A416">
+        <f t="shared" si="13"/>
+        <v>133</v>
+      </c>
+      <c r="B416" t="s">
+        <v>8</v>
+      </c>
+      <c r="C416">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="417" spans="1:3">
+      <c r="A417">
+        <f t="shared" si="13"/>
+        <v>134</v>
+      </c>
+      <c r="B417" t="s">
+        <v>10</v>
+      </c>
+      <c r="C417">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="418" spans="1:3">
+      <c r="A418">
+        <f t="shared" si="13"/>
+        <v>135</v>
+      </c>
+      <c r="B418" t="s">
+        <v>9</v>
+      </c>
+      <c r="C418">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="419" spans="1:3">
+      <c r="A419">
+        <f t="shared" si="13"/>
+        <v>136</v>
+      </c>
+      <c r="B419" t="s">
+        <v>10</v>
+      </c>
+      <c r="C419">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="420" spans="1:3">
+      <c r="A420">
+        <f t="shared" si="13"/>
+        <v>137</v>
+      </c>
+      <c r="B420" t="s">
+        <v>11</v>
+      </c>
+      <c r="C420">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="421" spans="1:3">
+      <c r="A421">
+        <f t="shared" si="13"/>
+        <v>138</v>
+      </c>
+      <c r="B421" t="s">
+        <v>11</v>
+      </c>
+      <c r="C421">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/l_r/1st.xlsx
+++ b/l_r/1st.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\l_r\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59F081C0-CD11-4F6B-8142-8054EFD27684}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F46191FB-5C42-4B27-9C59-DBCDA8284479}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="552" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="560" uniqueCount="66">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -5389,7 +5389,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C7A3EDD-6597-4754-A609-A225833ECC81}">
-  <dimension ref="A2:H421"/>
+  <dimension ref="A2:H429"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="2" spans="1:4">
@@ -9948,7 +9948,7 @@
     </row>
     <row r="386" spans="1:3">
       <c r="A386">
-        <f t="shared" ref="A386:A421" si="13">A385+1</f>
+        <f t="shared" ref="A386:A429" si="13">A385+1</f>
         <v>103</v>
       </c>
       <c r="B386" t="s">
@@ -10375,6 +10375,102 @@
         <v>11</v>
       </c>
       <c r="C421">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="422" spans="1:3">
+      <c r="A422">
+        <f t="shared" si="13"/>
+        <v>139</v>
+      </c>
+      <c r="B422" t="s">
+        <v>8</v>
+      </c>
+      <c r="C422">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="423" spans="1:3">
+      <c r="A423">
+        <f t="shared" si="13"/>
+        <v>140</v>
+      </c>
+      <c r="B423" t="s">
+        <v>10</v>
+      </c>
+      <c r="C423">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="424" spans="1:3">
+      <c r="A424">
+        <f t="shared" si="13"/>
+        <v>141</v>
+      </c>
+      <c r="B424" t="s">
+        <v>9</v>
+      </c>
+      <c r="C424">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="425" spans="1:3">
+      <c r="A425">
+        <f t="shared" si="13"/>
+        <v>142</v>
+      </c>
+      <c r="B425" t="s">
+        <v>8</v>
+      </c>
+      <c r="C425">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="426" spans="1:3">
+      <c r="A426">
+        <f t="shared" si="13"/>
+        <v>143</v>
+      </c>
+      <c r="B426" t="s">
+        <v>10</v>
+      </c>
+      <c r="C426">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="427" spans="1:3">
+      <c r="A427">
+        <f t="shared" si="13"/>
+        <v>144</v>
+      </c>
+      <c r="B427" t="s">
+        <v>10</v>
+      </c>
+      <c r="C427">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="428" spans="1:3">
+      <c r="A428">
+        <f t="shared" si="13"/>
+        <v>145</v>
+      </c>
+      <c r="B428" t="s">
+        <v>8</v>
+      </c>
+      <c r="C428">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="429" spans="1:3">
+      <c r="A429">
+        <f t="shared" si="13"/>
+        <v>146</v>
+      </c>
+      <c r="B429" t="s">
+        <v>11</v>
+      </c>
+      <c r="C429">
         <v>1</v>
       </c>
     </row>

--- a/l_r/1st.xlsx
+++ b/l_r/1st.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\l_r\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F46191FB-5C42-4B27-9C59-DBCDA8284479}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{511F648D-A986-472F-B5C7-2DAD7C6C2B1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="270" yWindow="0" windowWidth="15120" windowHeight="15585" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="3" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="560" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="564" uniqueCount="66">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -5389,7 +5389,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C7A3EDD-6597-4754-A609-A225833ECC81}">
-  <dimension ref="A2:H429"/>
+  <dimension ref="A2:H433"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="2" spans="1:4">
@@ -9948,7 +9948,7 @@
     </row>
     <row r="386" spans="1:3">
       <c r="A386">
-        <f t="shared" ref="A386:A429" si="13">A385+1</f>
+        <f t="shared" ref="A386:A433" si="13">A385+1</f>
         <v>103</v>
       </c>
       <c r="B386" t="s">
@@ -10472,6 +10472,42 @@
       </c>
       <c r="C429">
         <v>1</v>
+      </c>
+    </row>
+    <row r="430" spans="1:3">
+      <c r="A430">
+        <f t="shared" si="13"/>
+        <v>147</v>
+      </c>
+      <c r="B430" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="431" spans="1:3">
+      <c r="A431">
+        <f t="shared" si="13"/>
+        <v>148</v>
+      </c>
+      <c r="B431" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="432" spans="1:3">
+      <c r="A432">
+        <f t="shared" si="13"/>
+        <v>149</v>
+      </c>
+      <c r="B432" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="433" spans="1:2">
+      <c r="A433">
+        <f t="shared" si="13"/>
+        <v>150</v>
+      </c>
+      <c r="B433" t="s">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
